--- a/data/rateBuildUp/File1/RPT_RPT7156946910381YQ_rateBuildUp.xlsx
+++ b/data/rateBuildUp/File1/RPT_RPT7156946910381YQ_rateBuildUp.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="580" windowWidth="29920" windowHeight="18760" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="RateBuildUp" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RateBuildUp" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -2970,7 +2970,7 @@
         <v>22576.04277835388</v>
       </c>
       <c r="H11" s="371" t="n">
-        <v>7.761100220022192</v>
+        <v>7.761100220022191</v>
       </c>
       <c r="I11" s="372" t="n">
         <v>2.931419663211911</v>
@@ -2985,7 +2985,7 @@
         <v>1.647935614197367</v>
       </c>
       <c r="M11" s="371" t="n">
-        <v>7.723846962299837</v>
+        <v>7.723846962299836</v>
       </c>
       <c r="N11" s="372" t="n">
         <v>2.911509283748617</v>
@@ -3020,7 +3020,7 @@
         <v>22576.04277835388</v>
       </c>
       <c r="Y11" s="377" t="n">
-        <v>7.761100220022192</v>
+        <v>7.761100220022191</v>
       </c>
       <c r="Z11" s="372" t="n">
         <v>2.931419663211911</v>
@@ -3035,7 +3035,7 @@
         <v>1.647935614197367</v>
       </c>
       <c r="AD11" s="377" t="n">
-        <v>7.723846962299837</v>
+        <v>7.723846962299836</v>
       </c>
       <c r="AE11" s="372" t="n">
         <v>2.911509283748617</v>
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="BB11" s="383" t="n">
-        <v>26351.48216982735</v>
+        <v>26351.48216982734</v>
       </c>
       <c r="BC11" s="384" t="n">
         <v>25038.33755863324</v>
@@ -3129,7 +3129,7 @@
         <v>11.84683480014153</v>
       </c>
       <c r="BJ11" s="372" t="n">
-        <v>9.798754511136686</v>
+        <v>9.798754511136687</v>
       </c>
       <c r="BK11" s="387" t="n">
         <v>8.344508632115225</v>
@@ -3155,67 +3155,67 @@
         </is>
       </c>
       <c r="BS11" s="391" t="n">
-        <v>26198.60817143321</v>
+        <v>26198.6081714332</v>
       </c>
       <c r="BT11" s="375" t="n">
-        <v>24909.12870060275</v>
+        <v>24909.12870060274</v>
       </c>
       <c r="BU11" s="375" t="n">
-        <v>26539.93282039779</v>
+        <v>26539.93282039778</v>
       </c>
       <c r="BV11" s="375" t="n">
         <v>25920.71737475279</v>
       </c>
       <c r="BW11" s="392" t="n">
-        <v>26207.86114920854</v>
+        <v>26207.86114920852</v>
       </c>
       <c r="BX11" s="386" t="n">
-        <v>29.06346128541953</v>
+        <v>29.06346128541952</v>
       </c>
       <c r="BY11" s="372" t="n">
         <v>12.93325813107621</v>
       </c>
       <c r="BZ11" s="372" t="n">
-        <v>11.75360713701505</v>
+        <v>11.75360713701504</v>
       </c>
       <c r="CA11" s="372" t="n">
-        <v>9.716298370749909</v>
+        <v>9.716298370749907</v>
       </c>
       <c r="CB11" s="387" t="n">
-        <v>8.273045295813482</v>
+        <v>8.273045295813478</v>
       </c>
       <c r="CC11" s="388" t="n">
-        <v>28.62013109797843</v>
+        <v>28.62013109797842</v>
       </c>
       <c r="CD11" s="389" t="n">
         <v>12.61536042613422</v>
       </c>
       <c r="CE11" s="389" t="n">
-        <v>11.31085694480148</v>
+        <v>11.31085694480147</v>
       </c>
       <c r="CF11" s="389" t="n">
-        <v>9.362594739250378</v>
+        <v>9.362594739250376</v>
       </c>
       <c r="CG11" s="390" t="n">
-        <v>7.99824980305196</v>
+        <v>7.998249803051956</v>
       </c>
       <c r="CW11" s="91" t="n">
-        <v>0.01960206557254196</v>
+        <v>0.01960206557254907</v>
       </c>
       <c r="CX11" s="92" t="n">
-        <v>0.1034158876016509</v>
+        <v>0.1034158876016544</v>
       </c>
       <c r="CY11" s="92" t="n">
-        <v>0.09322766312648412</v>
+        <v>0.09322766312648767</v>
       </c>
       <c r="CZ11" s="92" t="n">
-        <v>0.08245614038677651</v>
+        <v>0.08245614038678006</v>
       </c>
       <c r="DA11" s="93" t="n">
-        <v>0.0714633363017434</v>
+        <v>0.07146333630174695</v>
       </c>
       <c r="DC11" s="393" t="n">
-        <v>0.007228790260420207</v>
+        <v>0.007228790260420208</v>
       </c>
       <c r="DD11" s="394" t="n">
         <v>0.007628852866560994</v>
@@ -3227,7 +3227,7 @@
         <v>0.008028176757755748</v>
       </c>
       <c r="DG11" s="395" t="n">
-        <v>0.008141014872206944</v>
+        <v>0.008141014872206942</v>
       </c>
     </row>
     <row r="12">
@@ -3240,34 +3240,34 @@
         <v>21513.34772147486</v>
       </c>
       <c r="D12" s="368" t="n">
-        <v>20634.18556412617</v>
+        <v>20634.18556412618</v>
       </c>
       <c r="E12" s="368" t="n">
         <v>23195.920397535</v>
       </c>
       <c r="F12" s="368" t="n">
-        <v>26161.20129784458</v>
+        <v>26161.20129784457</v>
       </c>
       <c r="G12" s="370" t="n">
-        <v>28299.44189527074</v>
+        <v>28299.44189527073</v>
       </c>
       <c r="H12" s="371" t="n">
-        <v>85.02205633810692</v>
+        <v>85.02205633810694</v>
       </c>
       <c r="I12" s="372" t="n">
         <v>48.60506797411139</v>
       </c>
       <c r="J12" s="372" t="n">
-        <v>48.43431448055416</v>
+        <v>48.43431448055417</v>
       </c>
       <c r="K12" s="372" t="n">
         <v>47.1858589007192</v>
       </c>
       <c r="L12" s="373" t="n">
-        <v>43.70113579309972</v>
+        <v>43.70113579309971</v>
       </c>
       <c r="M12" s="371" t="n">
-        <v>77.64223742448905</v>
+        <v>77.64223742448907</v>
       </c>
       <c r="N12" s="372" t="n">
         <v>43.80714602457297</v>
@@ -3279,7 +3279,7 @@
         <v>41.80661445744698</v>
       </c>
       <c r="Q12" s="373" t="n">
-        <v>39.07415789224062</v>
+        <v>39.07415789224061</v>
       </c>
       <c r="S12" s="99" t="inlineStr">
         <is>
@@ -3290,34 +3290,34 @@
         <v>21513.34772147486</v>
       </c>
       <c r="U12" s="375" t="n">
-        <v>20634.18556412617</v>
+        <v>20634.18556412618</v>
       </c>
       <c r="V12" s="375" t="n">
         <v>23195.920397535</v>
       </c>
       <c r="W12" s="375" t="n">
-        <v>26161.20129784458</v>
+        <v>26161.20129784457</v>
       </c>
       <c r="X12" s="376" t="n">
-        <v>28299.44189527074</v>
+        <v>28299.44189527073</v>
       </c>
       <c r="Y12" s="377" t="n">
-        <v>85.02205633810692</v>
+        <v>85.02205633810694</v>
       </c>
       <c r="Z12" s="372" t="n">
         <v>48.60506797411139</v>
       </c>
       <c r="AA12" s="372" t="n">
-        <v>48.43431448055416</v>
+        <v>48.43431448055417</v>
       </c>
       <c r="AB12" s="372" t="n">
         <v>47.1858589007192</v>
       </c>
       <c r="AC12" s="378" t="n">
-        <v>43.70113579309972</v>
+        <v>43.70113579309971</v>
       </c>
       <c r="AD12" s="377" t="n">
-        <v>77.64223742448905</v>
+        <v>77.64223742448907</v>
       </c>
       <c r="AE12" s="372" t="n">
         <v>43.80714602457297</v>
@@ -3329,7 +3329,7 @@
         <v>41.80661445744698</v>
       </c>
       <c r="AH12" s="378" t="n">
-        <v>39.07415789224062</v>
+        <v>39.07415789224061</v>
       </c>
       <c r="AJ12" s="100" t="inlineStr">
         <is>
@@ -3340,16 +3340,16 @@
         <v>21513.34772147486</v>
       </c>
       <c r="AL12" s="368" t="n">
-        <v>20634.18556412617</v>
+        <v>20634.18556412618</v>
       </c>
       <c r="AM12" s="368" t="n">
         <v>23195.920397535</v>
       </c>
       <c r="AN12" s="368" t="n">
-        <v>26161.20129784458</v>
+        <v>26161.20129784457</v>
       </c>
       <c r="AO12" s="380" t="n">
-        <v>28299.44189527074</v>
+        <v>28299.44189527073</v>
       </c>
       <c r="AP12" s="381" t="n">
         <v>142.6157121981156</v>
@@ -3358,10 +3358,10 @@
         <v>117.5849669349315</v>
       </c>
       <c r="AR12" s="372" t="n">
-        <v>130.6718745273437</v>
+        <v>130.6718745273438</v>
       </c>
       <c r="AS12" s="372" t="n">
-        <v>135.1836135108711</v>
+        <v>135.183613510871</v>
       </c>
       <c r="AT12" s="382" t="n">
         <v>131.5717271779875</v>
@@ -3370,16 +3370,16 @@
         <v>120.8912045704102</v>
       </c>
       <c r="AV12" s="372" t="n">
-        <v>91.68070187940798</v>
+        <v>91.68070187940799</v>
       </c>
       <c r="AW12" s="372" t="n">
-        <v>94.54366504470519</v>
+        <v>94.54366504470521</v>
       </c>
       <c r="AX12" s="372" t="n">
-        <v>97.6182416614639</v>
+        <v>97.61824166146388</v>
       </c>
       <c r="AY12" s="382" t="n">
-        <v>95.95531583833852</v>
+        <v>95.95531583833851</v>
       </c>
       <c r="BA12" s="101" t="inlineStr">
         <is>
@@ -3396,10 +3396,10 @@
         <v>25512.02919072224</v>
       </c>
       <c r="BE12" s="384" t="n">
-        <v>29559.11465242036</v>
+        <v>29559.11465242037</v>
       </c>
       <c r="BF12" s="385" t="n">
-        <v>32791.72935423009</v>
+        <v>32791.7293542301</v>
       </c>
       <c r="BG12" s="386" t="n">
         <v>147.6625874216905</v>
@@ -3414,7 +3414,7 @@
         <v>152.7417600362848</v>
       </c>
       <c r="BK12" s="387" t="n">
-        <v>152.4575814694839</v>
+        <v>152.457581469484</v>
       </c>
       <c r="BL12" s="386" t="n">
         <v>125.1692943803673</v>
@@ -3461,7 +3461,7 @@
         <v>143.2977451395557</v>
       </c>
       <c r="CA12" s="372" t="n">
-        <v>152.3124872651065</v>
+        <v>152.3124872651066</v>
       </c>
       <c r="CB12" s="387" t="n">
         <v>152.1157564838712</v>
@@ -3482,28 +3482,28 @@
         <v>111.840659449201</v>
       </c>
       <c r="CW12" s="102" t="n">
-        <v>0.1387068419064974</v>
+        <v>0.1387068419065258</v>
       </c>
       <c r="CX12" s="103" t="n">
         <v>0.3881823835003502</v>
       </c>
       <c r="CY12" s="103" t="n">
-        <v>0.4216943228359753</v>
+        <v>0.4216943228360037</v>
       </c>
       <c r="CZ12" s="103" t="n">
         <v>0.4292727711782618</v>
       </c>
       <c r="DA12" s="104" t="n">
-        <v>0.3418249856127602</v>
+        <v>0.3418249856127886</v>
       </c>
       <c r="DC12" s="396" t="n">
         <v>0.002321834056615353</v>
       </c>
       <c r="DD12" s="397" t="n">
-        <v>0.002251743842844422</v>
+        <v>0.002251743842844421</v>
       </c>
       <c r="DE12" s="397" t="n">
-        <v>0.002098746103403244</v>
+        <v>0.002098746103403243</v>
       </c>
       <c r="DF12" s="397" t="n">
         <v>0.001947812748621549</v>
@@ -3519,13 +3519,13 @@
         </is>
       </c>
       <c r="C13" s="369" t="n">
-        <v>39440.70190063955</v>
+        <v>39440.70190063954</v>
       </c>
       <c r="D13" s="368" t="n">
-        <v>43593.55950295802</v>
+        <v>43593.55950295803</v>
       </c>
       <c r="E13" s="368" t="n">
-        <v>50756.37805639652</v>
+        <v>50756.37805639651</v>
       </c>
       <c r="F13" s="368" t="n">
         <v>59687.99695787529</v>
@@ -3537,7 +3537,7 @@
         <v>163.8007665957055</v>
       </c>
       <c r="I13" s="372" t="n">
-        <v>99.59530597046084</v>
+        <v>99.59530597046086</v>
       </c>
       <c r="J13" s="372" t="n">
         <v>101.2407273404656</v>
@@ -3552,13 +3552,13 @@
         <v>153.2686370389475</v>
       </c>
       <c r="N13" s="372" t="n">
-        <v>93.48559344646634</v>
+        <v>93.48559344646635</v>
       </c>
       <c r="O13" s="372" t="n">
-        <v>93.01800358039037</v>
+        <v>93.01800358039036</v>
       </c>
       <c r="P13" s="372" t="n">
-        <v>93.88451418630076</v>
+        <v>93.88451418630078</v>
       </c>
       <c r="Q13" s="373" t="n">
         <v>86.61450650418848</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="T13" s="374" t="n">
-        <v>39440.70190063955</v>
+        <v>39440.70190063954</v>
       </c>
       <c r="U13" s="375" t="n">
-        <v>43593.55950295802</v>
+        <v>43593.55950295803</v>
       </c>
       <c r="V13" s="375" t="n">
-        <v>50756.37805639652</v>
+        <v>50756.37805639651</v>
       </c>
       <c r="W13" s="375" t="n">
         <v>59687.99695787529</v>
@@ -3587,7 +3587,7 @@
         <v>163.8007665957055</v>
       </c>
       <c r="Z13" s="372" t="n">
-        <v>99.59530597046084</v>
+        <v>99.59530597046086</v>
       </c>
       <c r="AA13" s="372" t="n">
         <v>101.2407273404656</v>
@@ -3602,13 +3602,13 @@
         <v>153.2686370389475</v>
       </c>
       <c r="AE13" s="372" t="n">
-        <v>93.48559344646634</v>
+        <v>93.48559344646635</v>
       </c>
       <c r="AF13" s="372" t="n">
-        <v>93.01800358039037</v>
+        <v>93.01800358039036</v>
       </c>
       <c r="AG13" s="372" t="n">
-        <v>93.88451418630076</v>
+        <v>93.88451418630078</v>
       </c>
       <c r="AH13" s="378" t="n">
         <v>86.61450650418848</v>
@@ -3619,22 +3619,22 @@
         </is>
       </c>
       <c r="AK13" s="379" t="n">
-        <v>40353.86742421877</v>
+        <v>40353.86742421878</v>
       </c>
       <c r="AL13" s="368" t="n">
         <v>43976.3503288433</v>
       </c>
       <c r="AM13" s="368" t="n">
-        <v>51065.77533142248</v>
+        <v>51065.77533142247</v>
       </c>
       <c r="AN13" s="368" t="n">
-        <v>59932.20549313851</v>
+        <v>59932.2054931385</v>
       </c>
       <c r="AO13" s="380" t="n">
-        <v>64011.67748918975</v>
+        <v>64011.67748918976</v>
       </c>
       <c r="AP13" s="381" t="n">
-        <v>298.1965215839988</v>
+        <v>298.1965215839989</v>
       </c>
       <c r="AQ13" s="372" t="n">
         <v>250.4226493662642</v>
@@ -3658,7 +3658,7 @@
         <v>224.1772094171507</v>
       </c>
       <c r="AX13" s="372" t="n">
-        <v>235.4875807644806</v>
+        <v>235.4875807644805</v>
       </c>
       <c r="AY13" s="382" t="n">
         <v>223.5406118006513</v>
@@ -3678,7 +3678,7 @@
         <v>55924.15283488185</v>
       </c>
       <c r="BE13" s="384" t="n">
-        <v>67485.43947806671</v>
+        <v>67485.43947806669</v>
       </c>
       <c r="BF13" s="385" t="n">
         <v>73868.81020102857</v>
@@ -3687,7 +3687,7 @@
         <v>307.3051522628174</v>
       </c>
       <c r="BH13" s="372" t="n">
-        <v>265.6277937976782</v>
+        <v>265.6277937976781</v>
       </c>
       <c r="BI13" s="372" t="n">
         <v>304.8076214542658</v>
@@ -3728,7 +3728,7 @@
         <v>56170.65521150504</v>
       </c>
       <c r="BV13" s="375" t="n">
-        <v>67885.43870174914</v>
+        <v>67885.43870174912</v>
       </c>
       <c r="BW13" s="392" t="n">
         <v>74413.25004244293</v>
@@ -3743,7 +3743,7 @@
         <v>304.7626318059581</v>
       </c>
       <c r="CA13" s="372" t="n">
-        <v>341.7608589849468</v>
+        <v>341.7608589849467</v>
       </c>
       <c r="CB13" s="387" t="n">
         <v>338.7294552555375</v>
@@ -3767,7 +3767,7 @@
         <v>-0.4071193850408008</v>
       </c>
       <c r="CX13" s="103" t="n">
-        <v>0.04688105152109756</v>
+        <v>0.04688105152104072</v>
       </c>
       <c r="CY13" s="103" t="n">
         <v>0.04498964830770547</v>
@@ -3779,16 +3779,16 @@
         <v>0.05607020784765382</v>
       </c>
       <c r="DC13" s="396" t="n">
-        <v>0.000384370482554896</v>
+        <v>0.0003843704825548959</v>
       </c>
       <c r="DD13" s="397" t="n">
-        <v>0.0003655210514032195</v>
+        <v>0.0003655210514032196</v>
       </c>
       <c r="DE13" s="397" t="n">
-        <v>0.0003150209318953225</v>
+        <v>0.0003150209318953226</v>
       </c>
       <c r="DF13" s="397" t="n">
-        <v>0.0002740094642132658</v>
+        <v>0.0002740094642132659</v>
       </c>
       <c r="DG13" s="398" t="n">
         <v>0.0002648606592070789</v>
@@ -4004,13 +4004,13 @@
         <v>687.6601186702486</v>
       </c>
       <c r="BT14" s="420" t="n">
-        <v>771.0902486687166</v>
+        <v>771.0902486687164</v>
       </c>
       <c r="BU14" s="420" t="n">
-        <v>869.281073896229</v>
+        <v>869.2810738962288</v>
       </c>
       <c r="BV14" s="420" t="n">
-        <v>957.4795767063711</v>
+        <v>957.4795767063708</v>
       </c>
       <c r="BW14" s="421" t="n">
         <v>1052.062863383992</v>
@@ -4022,10 +4022,10 @@
         <v>101.9262551993843</v>
       </c>
       <c r="BZ14" s="417" t="n">
-        <v>112.8247865600319</v>
+        <v>112.8247865600318</v>
       </c>
       <c r="CA14" s="417" t="n">
-        <v>121.1482847990558</v>
+        <v>121.1482847990557</v>
       </c>
       <c r="CB14" s="418" t="n">
         <v>129.3107001526823</v>
@@ -4037,10 +4037,10 @@
         <v>101.9262551993843</v>
       </c>
       <c r="CE14" s="417" t="n">
-        <v>112.8247865600319</v>
+        <v>112.8247865600318</v>
       </c>
       <c r="CF14" s="417" t="n">
-        <v>121.1482847990558</v>
+        <v>121.1482847990557</v>
       </c>
       <c r="CG14" s="418" t="n">
         <v>129.3107001526823</v>
@@ -4049,16 +4049,16 @@
         <v>0.4317330834502258</v>
       </c>
       <c r="CX14" s="133" t="n">
-        <v>0.5397637059620308</v>
+        <v>0.5397637059620592</v>
       </c>
       <c r="CY14" s="133" t="n">
-        <v>0.5963543019979198</v>
+        <v>0.5963543019979483</v>
       </c>
       <c r="CZ14" s="133" t="n">
-        <v>0.6409081959648546</v>
+        <v>0.6409081959648972</v>
       </c>
       <c r="DA14" s="134" t="n">
-        <v>0.685071409381294</v>
+        <v>0.6850714093813224</v>
       </c>
       <c r="DC14" s="422" t="n">
         <v>0</v>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="C15" s="425" t="n">
-        <v>87054.89916619584</v>
+        <v>87054.89916619583</v>
       </c>
       <c r="D15" s="425" t="n">
-        <v>88288.66723237108</v>
+        <v>88288.66723237111</v>
       </c>
       <c r="E15" s="425" t="n">
         <v>98816.77292604014</v>
@@ -4101,31 +4101,31 @@
         <v>23.03174053733933</v>
       </c>
       <c r="I15" s="427" t="n">
-        <v>9.994995455743462</v>
+        <v>9.994995455743465</v>
       </c>
       <c r="J15" s="427" t="n">
         <v>9.350722312571557</v>
       </c>
       <c r="K15" s="427" t="n">
-        <v>8.706051845429036</v>
+        <v>8.706051845429034</v>
       </c>
       <c r="L15" s="428" t="n">
-        <v>7.730404969590541</v>
+        <v>7.73040496959054</v>
       </c>
       <c r="M15" s="427" t="n">
         <v>22.69310446651396</v>
       </c>
       <c r="N15" s="427" t="n">
-        <v>9.850515169678836</v>
+        <v>9.85051516967884</v>
       </c>
       <c r="O15" s="427" t="n">
         <v>9.171239498706534</v>
       </c>
       <c r="P15" s="427" t="n">
-        <v>8.541148811955361</v>
+        <v>8.54114881195536</v>
       </c>
       <c r="Q15" s="428" t="n">
-        <v>7.592258406256295</v>
+        <v>7.592258406256294</v>
       </c>
       <c r="S15" s="143" t="inlineStr">
         <is>
@@ -4133,10 +4133,10 @@
         </is>
       </c>
       <c r="T15" s="429" t="n">
-        <v>87054.89916619584</v>
+        <v>87054.89916619583</v>
       </c>
       <c r="U15" s="430" t="n">
-        <v>88288.66723237108</v>
+        <v>88288.66723237111</v>
       </c>
       <c r="V15" s="430" t="n">
         <v>98816.77292604014</v>
@@ -4151,31 +4151,31 @@
         <v>23.03174053733933</v>
       </c>
       <c r="Z15" s="433" t="n">
-        <v>9.994995455743462</v>
+        <v>9.994995455743465</v>
       </c>
       <c r="AA15" s="433" t="n">
         <v>9.350722312571557</v>
       </c>
       <c r="AB15" s="433" t="n">
-        <v>8.706051845429036</v>
+        <v>8.706051845429034</v>
       </c>
       <c r="AC15" s="434" t="n">
-        <v>7.730404969590541</v>
+        <v>7.73040496959054</v>
       </c>
       <c r="AD15" s="433" t="n">
         <v>22.69310446651396</v>
       </c>
       <c r="AE15" s="433" t="n">
-        <v>9.850515169678836</v>
+        <v>9.85051516967884</v>
       </c>
       <c r="AF15" s="433" t="n">
         <v>9.171239498706534</v>
       </c>
       <c r="AG15" s="433" t="n">
-        <v>8.541148811955361</v>
+        <v>8.54114881195536</v>
       </c>
       <c r="AH15" s="434" t="n">
-        <v>7.592258406256295</v>
+        <v>7.592258406256294</v>
       </c>
       <c r="AJ15" s="150" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="AK15" s="435" t="n">
-        <v>87968.06468977506</v>
+        <v>87968.06468977507</v>
       </c>
       <c r="AL15" s="408" t="n">
         <v>88671.45805825636</v>
@@ -4198,7 +4198,7 @@
         <v>115776.9673300603</v>
       </c>
       <c r="AP15" s="436" t="n">
-        <v>73.25241386005487</v>
+        <v>73.25241386005489</v>
       </c>
       <c r="AQ15" s="437" t="n">
         <v>38.90342809245882</v>
@@ -4213,7 +4213,7 @@
         <v>32.24980724680013</v>
       </c>
       <c r="AU15" s="437" t="n">
-        <v>69.79650869487811</v>
+        <v>69.79650869487813</v>
       </c>
       <c r="AV15" s="437" t="n">
         <v>36.76387591143335</v>
@@ -4257,7 +4257,7 @@
         <v>41.62000973455422</v>
       </c>
       <c r="BJ15" s="443" t="n">
-        <v>40.61738327003068</v>
+        <v>40.61738327003067</v>
       </c>
       <c r="BK15" s="444" t="n">
         <v>37.32410199783979</v>
@@ -4286,7 +4286,7 @@
         <v>90786.47095502257</v>
       </c>
       <c r="BT15" s="440" t="n">
-        <v>94496.35629231627</v>
+        <v>94496.35629231625</v>
       </c>
       <c r="BU15" s="440" t="n">
         <v>109145.8081992293</v>
@@ -4301,13 +4301,13 @@
         <v>75.89417816631915</v>
       </c>
       <c r="BY15" s="443" t="n">
-        <v>41.34127517246637</v>
+        <v>41.34127517246636</v>
       </c>
       <c r="BZ15" s="443" t="n">
-        <v>41.52477957589833</v>
+        <v>41.52477957589832</v>
       </c>
       <c r="CA15" s="443" t="n">
-        <v>40.54345786920423</v>
+        <v>40.54345786920421</v>
       </c>
       <c r="CB15" s="444" t="n">
         <v>37.27353150655126</v>
@@ -4316,13 +4316,13 @@
         <v>72.44476821545784</v>
       </c>
       <c r="CD15" s="443" t="n">
-        <v>39.19064142543941</v>
+        <v>39.1906414254394</v>
       </c>
       <c r="CE15" s="443" t="n">
-        <v>38.60702661544716</v>
+        <v>38.60702661544715</v>
       </c>
       <c r="CF15" s="443" t="n">
-        <v>37.72024445483262</v>
+        <v>37.72024445483261</v>
       </c>
       <c r="CG15" s="444" t="n">
         <v>34.82942512433012</v>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
       <c r="BS20" s="391" t="n">
-        <v>4326.533035412036</v>
+        <v>4326.533035412035</v>
       </c>
       <c r="BT20" s="375" t="n">
         <v>0</v>
@@ -5261,7 +5261,7 @@
         <v>0</v>
       </c>
       <c r="BX20" s="386" t="n">
-        <v>4.799645254128302</v>
+        <v>4.799645254128301</v>
       </c>
       <c r="BY20" s="372" t="n">
         <v>0</v>
@@ -5276,7 +5276,7 @@
         <v>0</v>
       </c>
       <c r="CC20" s="388" t="n">
-        <v>4.726432101391021</v>
+        <v>4.72643210139102</v>
       </c>
       <c r="CD20" s="389" t="n">
         <v>0</v>
@@ -5291,7 +5291,7 @@
         <v>0</v>
       </c>
       <c r="CW20" s="91" t="n">
-        <v>0.005749963029404448</v>
+        <v>0.005749963029405336</v>
       </c>
       <c r="CX20" s="92" t="n">
         <v>0</v>
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="BS21" s="391" t="n">
-        <v>510.2510503017754</v>
+        <v>510.2510503017753</v>
       </c>
       <c r="BT21" s="375" t="n">
         <v>0</v>
@@ -5543,7 +5543,7 @@
         <v>0</v>
       </c>
       <c r="BX21" s="386" t="n">
-        <v>3.383657686580601</v>
+        <v>3.3836576865806</v>
       </c>
       <c r="BY21" s="372" t="n">
         <v>0</v>
@@ -5558,7 +5558,7 @@
         <v>0</v>
       </c>
       <c r="CC21" s="386" t="n">
-        <v>2.873833781895742</v>
+        <v>2.873833781895741</v>
       </c>
       <c r="CD21" s="372" t="n">
         <v>0</v>
@@ -5573,7 +5573,7 @@
         <v>0</v>
       </c>
       <c r="CW21" s="102" t="n">
-        <v>0.02930111296263993</v>
+        <v>0.02930111296264082</v>
       </c>
       <c r="CX21" s="103" t="n">
         <v>0</v>
@@ -7336,7 +7336,7 @@
         </is>
       </c>
       <c r="BS29" s="391" t="n">
-        <v>9.772854192859578</v>
+        <v>9.772854192859574</v>
       </c>
       <c r="BT29" s="375" t="n">
         <v>0</v>
@@ -7381,7 +7381,7 @@
         <v>0</v>
       </c>
       <c r="CW29" s="91" t="n">
-        <v>-7.11118479403243e-05</v>
+        <v>-7.111184794031909e-05</v>
       </c>
       <c r="CX29" s="92" t="n">
         <v>0</v>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="BS30" s="391" t="n">
-        <v>55.984431488026</v>
+        <v>55.98443148802599</v>
       </c>
       <c r="BT30" s="375" t="n">
         <v>0</v>
@@ -7633,7 +7633,7 @@
         <v>0</v>
       </c>
       <c r="BX30" s="386" t="n">
-        <v>0.3712528407756716</v>
+        <v>0.3712528407756715</v>
       </c>
       <c r="BY30" s="372" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>0</v>
       </c>
       <c r="CC30" s="386" t="n">
-        <v>0.3153152754420838</v>
+        <v>0.3153152754420837</v>
       </c>
       <c r="CD30" s="372" t="n">
         <v>0</v>
@@ -7663,7 +7663,7 @@
         <v>0</v>
       </c>
       <c r="CW30" s="102" t="n">
-        <v>-0.0005137337332007386</v>
+        <v>-0.0005137337332006831</v>
       </c>
       <c r="CX30" s="103" t="n">
         <v>0</v>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="BS33" s="439" t="n">
-        <v>65.75728568088559</v>
+        <v>65.75728568088556</v>
       </c>
       <c r="BT33" s="440" t="n">
         <v>0</v>
@@ -8479,7 +8479,7 @@
         <v>0</v>
       </c>
       <c r="BX33" s="442" t="n">
-        <v>0.05497069224853027</v>
+        <v>0.05497069224853025</v>
       </c>
       <c r="BY33" s="443" t="n">
         <v>0</v>
@@ -8494,7 +8494,7 @@
         <v>0</v>
       </c>
       <c r="CC33" s="443" t="n">
-        <v>0.05247226012331142</v>
+        <v>0.0524722601233114</v>
       </c>
       <c r="CD33" s="443" t="n">
         <v>0</v>
@@ -9382,7 +9382,7 @@
         <v>70.62874672220298</v>
       </c>
       <c r="BD38" s="375" t="n">
-        <v>32.45283468400486</v>
+        <v>32.45283468400487</v>
       </c>
       <c r="BE38" s="375" t="n">
         <v>14.61425526447144</v>
@@ -9400,7 +9400,7 @@
         <v>0.01442865926428061</v>
       </c>
       <c r="BJ38" s="372" t="n">
-        <v>0.005505546010806096</v>
+        <v>0.005505546010806097</v>
       </c>
       <c r="BK38" s="387" t="n">
         <v>0.005090021898555216</v>
@@ -9415,7 +9415,7 @@
         <v>0.01382755585669179</v>
       </c>
       <c r="BO38" s="389" t="n">
-        <v>0.005277638981293085</v>
+        <v>0.005277638981293086</v>
       </c>
       <c r="BP38" s="390" t="n">
         <v>0.004890440496648021</v>
@@ -9426,10 +9426,10 @@
         </is>
       </c>
       <c r="BS38" s="391" t="n">
-        <v>132.6378209519391</v>
+        <v>132.637820951939</v>
       </c>
       <c r="BT38" s="375" t="n">
-        <v>70.55321621334858</v>
+        <v>70.55321621334855</v>
       </c>
       <c r="BU38" s="375" t="n">
         <v>32.33056940568208</v>
@@ -9441,52 +9441,52 @@
         <v>15.8487641383771</v>
       </c>
       <c r="BX38" s="386" t="n">
-        <v>0.147141945442066</v>
+        <v>0.1471419454420659</v>
       </c>
       <c r="BY38" s="372" t="n">
-        <v>0.03663247190347482</v>
+        <v>0.03663247190347481</v>
       </c>
       <c r="BZ38" s="372" t="n">
         <v>0.01431807736221277</v>
       </c>
       <c r="CA38" s="372" t="n">
-        <v>0.005411602615854709</v>
+        <v>0.005411602615854708</v>
       </c>
       <c r="CB38" s="387" t="n">
-        <v>0.005002985281895764</v>
+        <v>0.005002985281895763</v>
       </c>
       <c r="CC38" s="388" t="n">
         <v>0.1448974617030969</v>
       </c>
       <c r="CD38" s="389" t="n">
-        <v>0.03573205078557531</v>
+        <v>0.03573205078557529</v>
       </c>
       <c r="CE38" s="389" t="n">
         <v>0.01377872536326052</v>
       </c>
       <c r="CF38" s="389" t="n">
-        <v>0.005214603365273601</v>
+        <v>0.0052146033652736</v>
       </c>
       <c r="CG38" s="390" t="n">
-        <v>0.004836807320013591</v>
+        <v>0.004836807320013589</v>
       </c>
       <c r="CW38" s="91" t="n">
-        <v>-0.0004475955687685551</v>
+        <v>-0.0004475955687684996</v>
       </c>
       <c r="CX38" s="92" t="n">
-        <v>0.0001416927234271989</v>
+        <v>0.0001416927234272128</v>
       </c>
       <c r="CY38" s="92" t="n">
-        <v>0.0001105819020678373</v>
+        <v>0.000110581902067846</v>
       </c>
       <c r="CZ38" s="92" t="n">
-        <v>9.394339495138668e-05</v>
+        <v>9.394339495138841e-05</v>
       </c>
       <c r="DA38" s="93" t="n">
-        <v>8.703661665945221e-05</v>
+        <v>8.703661665945394e-05</v>
       </c>
       <c r="DC38" s="393" t="n">
-        <v>0.003528009884850774</v>
+        <v>0.003528009884850775</v>
       </c>
       <c r="DD38" s="394" t="n">
         <v>0.003547964645490739</v>
@@ -9708,7 +9708,7 @@
         </is>
       </c>
       <c r="BS39" s="391" t="n">
-        <v>127.4348547561338</v>
+        <v>127.4348547561337</v>
       </c>
       <c r="BT39" s="375" t="n">
         <v>66.89145973609607</v>
@@ -9717,13 +9717,13 @@
         <v>75.30150517013892</v>
       </c>
       <c r="BV39" s="375" t="n">
-        <v>82.51644042166787</v>
+        <v>82.51644042166785</v>
       </c>
       <c r="BW39" s="392" t="n">
-        <v>90.30068098406998</v>
+        <v>90.30068098406997</v>
       </c>
       <c r="BX39" s="386" t="n">
-        <v>0.845066219028563</v>
+        <v>0.8450662190285628</v>
       </c>
       <c r="BY39" s="372" t="n">
         <v>0.3798975964538547</v>
@@ -9732,13 +9732,13 @@
         <v>0.4220668701846503</v>
       </c>
       <c r="CA39" s="372" t="n">
-        <v>0.4236427786325577</v>
+        <v>0.4236427786325576</v>
       </c>
       <c r="CB39" s="387" t="n">
-        <v>0.4165487326267491</v>
+        <v>0.416548732626749</v>
       </c>
       <c r="CC39" s="386" t="n">
-        <v>0.7177380436013975</v>
+        <v>0.7177380436013974</v>
       </c>
       <c r="CD39" s="372" t="n">
         <v>0.297315247957744</v>
@@ -9753,7 +9753,7 @@
         <v>0.3062607452808095</v>
       </c>
       <c r="CW39" s="102" t="n">
-        <v>0.009281067173605217</v>
+        <v>0.00928106717360544</v>
       </c>
       <c r="CX39" s="103" t="n">
         <v>0.009522293896881528</v>
@@ -9762,10 +9762,10 @@
         <v>0.01057700857021598</v>
       </c>
       <c r="CZ39" s="103" t="n">
-        <v>0.01062830486053545</v>
+        <v>0.01062830486053556</v>
       </c>
       <c r="DA39" s="104" t="n">
-        <v>0.01049088975052281</v>
+        <v>0.01049088975052292</v>
       </c>
       <c r="DC39" s="396" t="n">
         <v>0.01223209394752628</v>
@@ -9946,7 +9946,7 @@
         <v>66.76208474063301</v>
       </c>
       <c r="BD40" s="375" t="n">
-        <v>59.40875543046739</v>
+        <v>59.4087554304674</v>
       </c>
       <c r="BE40" s="375" t="n">
         <v>58.18455529240203</v>
@@ -9961,7 +9961,7 @@
         <v>0.3801756628948547</v>
       </c>
       <c r="BI40" s="372" t="n">
-        <v>0.3238000133821287</v>
+        <v>0.3238000133821288</v>
       </c>
       <c r="BJ40" s="372" t="n">
         <v>0.2946992680127917</v>
@@ -9976,7 +9976,7 @@
         <v>0.3269210894268252</v>
       </c>
       <c r="BN40" s="372" t="n">
-        <v>0.2608026397506416</v>
+        <v>0.2608026397506417</v>
       </c>
       <c r="BO40" s="372" t="n">
         <v>0.2286206564721465</v>
@@ -9996,7 +9996,7 @@
         <v>66.17075728781755</v>
       </c>
       <c r="BU40" s="375" t="n">
-        <v>58.79476078607205</v>
+        <v>58.79476078607207</v>
       </c>
       <c r="BV40" s="375" t="n">
         <v>57.56892998018633</v>
@@ -10011,7 +10011,7 @@
         <v>0.3756597890879749</v>
       </c>
       <c r="BZ40" s="372" t="n">
-        <v>0.3190001249957816</v>
+        <v>0.3190001249957817</v>
       </c>
       <c r="CA40" s="372" t="n">
         <v>0.2898236696578319</v>
@@ -10026,7 +10026,7 @@
         <v>0.3241456711598434</v>
       </c>
       <c r="CE40" s="372" t="n">
-        <v>0.258192513684695</v>
+        <v>0.2581925136846951</v>
       </c>
       <c r="CF40" s="372" t="n">
         <v>0.2262686132195627</v>
@@ -10272,64 +10272,64 @@
         </is>
       </c>
       <c r="BS41" s="419" t="n">
-        <v>67.54914673800951</v>
+        <v>67.5491467380095</v>
       </c>
       <c r="BT41" s="420" t="n">
-        <v>72.21928580121335</v>
+        <v>72.21928580121333</v>
       </c>
       <c r="BU41" s="420" t="n">
-        <v>77.49861864591595</v>
+        <v>77.49861864591594</v>
       </c>
       <c r="BV41" s="420" t="n">
-        <v>82.5476181488975</v>
+        <v>82.54761814889748</v>
       </c>
       <c r="BW41" s="421" t="n">
-        <v>87.95482401348623</v>
+        <v>87.95482401348622</v>
       </c>
       <c r="BX41" s="416" t="n">
-        <v>7.825390701591194</v>
+        <v>7.825390701591192</v>
       </c>
       <c r="BY41" s="417" t="n">
-        <v>9.546277323050761</v>
+        <v>9.546277323050759</v>
       </c>
       <c r="BZ41" s="417" t="n">
         <v>10.05861667760935</v>
       </c>
       <c r="CA41" s="417" t="n">
-        <v>10.44461166199181</v>
+        <v>10.4446116619918</v>
       </c>
       <c r="CB41" s="418" t="n">
         <v>10.810665665364</v>
       </c>
       <c r="CC41" s="417" t="n">
-        <v>7.825390701591194</v>
+        <v>7.825390701591192</v>
       </c>
       <c r="CD41" s="417" t="n">
-        <v>9.546277323050761</v>
+        <v>9.546277323050759</v>
       </c>
       <c r="CE41" s="417" t="n">
         <v>10.05861667760935</v>
       </c>
       <c r="CF41" s="417" t="n">
-        <v>10.44461166199181</v>
+        <v>10.4446116619918</v>
       </c>
       <c r="CG41" s="418" t="n">
         <v>10.810665665364</v>
       </c>
       <c r="CW41" s="132" t="n">
-        <v>0.04240932491770177</v>
+        <v>0.04240932491770355</v>
       </c>
       <c r="CX41" s="133" t="n">
-        <v>0.05055354987732841</v>
+        <v>0.05055354987733018</v>
       </c>
       <c r="CY41" s="133" t="n">
-        <v>0.05316650277595514</v>
+        <v>0.05316650277595691</v>
       </c>
       <c r="CZ41" s="133" t="n">
-        <v>0.05525490706652292</v>
+        <v>0.05525490706652647</v>
       </c>
       <c r="DA41" s="134" t="n">
-        <v>0.0572735122072352</v>
+        <v>0.05727351220723698</v>
       </c>
       <c r="DC41" s="422" t="n">
         <v>0</v>
@@ -10525,7 +10525,7 @@
         <v>0.1221401862986807</v>
       </c>
       <c r="BI42" s="443" t="n">
-        <v>0.09421184570543925</v>
+        <v>0.09421184570543928</v>
       </c>
       <c r="BJ42" s="443" t="n">
         <v>0.07856840792347995</v>
@@ -10540,7 +10540,7 @@
         <v>0.1154229041772921</v>
       </c>
       <c r="BN42" s="443" t="n">
-        <v>0.08721788522360291</v>
+        <v>0.08721788522360292</v>
       </c>
       <c r="BO42" s="443" t="n">
         <v>0.07270664370413407</v>
@@ -10554,10 +10554,10 @@
         </is>
       </c>
       <c r="BS42" s="439" t="n">
-        <v>379.5906223633204</v>
+        <v>379.5906223633203</v>
       </c>
       <c r="BT42" s="440" t="n">
-        <v>275.8347190384756</v>
+        <v>275.8347190384755</v>
       </c>
       <c r="BU42" s="440" t="n">
         <v>243.925454007809</v>
@@ -10569,34 +10569,34 @@
         <v>257.7355819292745</v>
       </c>
       <c r="BX42" s="442" t="n">
-        <v>0.3173239142446481</v>
+        <v>0.317323914244648</v>
       </c>
       <c r="BY42" s="443" t="n">
         <v>0.1206751188015574</v>
       </c>
       <c r="BZ42" s="443" t="n">
-        <v>0.09280201299289764</v>
+        <v>0.09280201299289766</v>
       </c>
       <c r="CA42" s="443" t="n">
-        <v>0.07724477957220312</v>
+        <v>0.0772447795722031</v>
       </c>
       <c r="CB42" s="444" t="n">
-        <v>0.07134620487753214</v>
+        <v>0.07134620487753213</v>
       </c>
       <c r="CC42" s="443" t="n">
-        <v>0.3029014605876229</v>
+        <v>0.3029014605876228</v>
       </c>
       <c r="CD42" s="443" t="n">
         <v>0.1143974221935446</v>
       </c>
       <c r="CE42" s="443" t="n">
-        <v>0.08628124753884052</v>
+        <v>0.08628124753884053</v>
       </c>
       <c r="CF42" s="443" t="n">
-        <v>0.07186589702641839</v>
+        <v>0.07186589702641838</v>
       </c>
       <c r="CG42" s="444" t="n">
-        <v>0.06666787933014513</v>
+        <v>0.06666787933014512</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" thickBot="1">
@@ -11364,7 +11364,7 @@
         <v>7.175855846984508</v>
       </c>
       <c r="AU47" s="372" t="n">
-        <v>32.46936264892265</v>
+        <v>32.46936264892264</v>
       </c>
       <c r="AV47" s="372" t="n">
         <v>11.858182792946</v>
@@ -11390,7 +11390,7 @@
         <v>25108.96630535545</v>
       </c>
       <c r="BD47" s="375" t="n">
-        <v>26678.26685355693</v>
+        <v>26678.26685355692</v>
       </c>
       <c r="BE47" s="375" t="n">
         <v>26025.02256328181</v>
@@ -11408,7 +11408,7 @@
         <v>11.86126345940581</v>
       </c>
       <c r="BJ47" s="372" t="n">
-        <v>9.804260057147491</v>
+        <v>9.804260057147493</v>
       </c>
       <c r="BK47" s="387" t="n">
         <v>8.34959865401378</v>
@@ -11434,22 +11434,22 @@
         </is>
       </c>
       <c r="BS47" s="391" t="n">
-        <v>30667.55188199005</v>
+        <v>30667.55188199003</v>
       </c>
       <c r="BT47" s="375" t="n">
-        <v>24979.6819168161</v>
+        <v>24979.68191681609</v>
       </c>
       <c r="BU47" s="375" t="n">
-        <v>26572.26338980347</v>
+        <v>26572.26338980346</v>
       </c>
       <c r="BV47" s="375" t="n">
         <v>25935.1542123835</v>
       </c>
       <c r="BW47" s="392" t="n">
-        <v>26223.70991334691</v>
+        <v>26223.7099133469</v>
       </c>
       <c r="BX47" s="386" t="n">
-        <v>34.02109001396059</v>
+        <v>34.02109001396057</v>
       </c>
       <c r="BY47" s="372" t="n">
         <v>12.96989060297969</v>
@@ -11458,25 +11458,25 @@
         <v>11.76792521437726</v>
       </c>
       <c r="CA47" s="372" t="n">
-        <v>9.721709973365764</v>
+        <v>9.721709973365762</v>
       </c>
       <c r="CB47" s="387" t="n">
-        <v>8.278048281095378</v>
+        <v>8.278048281095375</v>
       </c>
       <c r="CC47" s="388" t="n">
-        <v>33.50213681479686</v>
+        <v>33.50213681479683</v>
       </c>
       <c r="CD47" s="389" t="n">
-        <v>12.6510924769198</v>
+        <v>12.65109247691979</v>
       </c>
       <c r="CE47" s="389" t="n">
-        <v>11.32463567016474</v>
+        <v>11.32463567016473</v>
       </c>
       <c r="CF47" s="389" t="n">
         <v>9.367809342615651</v>
       </c>
       <c r="CG47" s="390" t="n">
-        <v>8.003086610371973</v>
+        <v>8.00308661037197</v>
       </c>
     </row>
     <row r="48">
@@ -11498,28 +11498,28 @@
         <v>26261.27157099299</v>
       </c>
       <c r="G48" s="455" t="n">
-        <v>28412.3764402447</v>
+        <v>28412.37644024469</v>
       </c>
       <c r="H48" s="371" t="n">
         <v>94.92008800030385</v>
       </c>
       <c r="I48" s="372" t="n">
-        <v>48.78120631869076</v>
+        <v>48.78120631869077</v>
       </c>
       <c r="J48" s="372" t="n">
-        <v>48.61761759979122</v>
+        <v>48.61761759979124</v>
       </c>
       <c r="K48" s="372" t="n">
-        <v>47.36635144520059</v>
+        <v>47.36635144520058</v>
       </c>
       <c r="L48" s="373" t="n">
-        <v>43.87553385734083</v>
+        <v>43.87553385734082</v>
       </c>
       <c r="M48" s="371" t="n">
         <v>86.68113106516144</v>
       </c>
       <c r="N48" s="372" t="n">
-        <v>43.96589733391431</v>
+        <v>43.96589733391432</v>
       </c>
       <c r="O48" s="372" t="n">
         <v>42.82965118067968</v>
@@ -11528,7 +11528,7 @@
         <v>41.96653063562768</v>
       </c>
       <c r="Q48" s="373" t="n">
-        <v>39.23009108195269</v>
+        <v>39.23009108195267</v>
       </c>
       <c r="S48" s="99" t="inlineStr">
         <is>
@@ -11548,28 +11548,28 @@
         <v>26261.27157099299</v>
       </c>
       <c r="X48" s="376" t="n">
-        <v>28412.3764402447</v>
+        <v>28412.37644024469</v>
       </c>
       <c r="Y48" s="377" t="n">
         <v>94.92008800030385</v>
       </c>
       <c r="Z48" s="372" t="n">
-        <v>48.78120631869076</v>
+        <v>48.78120631869077</v>
       </c>
       <c r="AA48" s="372" t="n">
-        <v>48.61761759979122</v>
+        <v>48.61761759979124</v>
       </c>
       <c r="AB48" s="372" t="n">
-        <v>47.36635144520059</v>
+        <v>47.36635144520058</v>
       </c>
       <c r="AC48" s="378" t="n">
-        <v>43.87553385734083</v>
+        <v>43.87553385734082</v>
       </c>
       <c r="AD48" s="377" t="n">
         <v>86.68113106516144</v>
       </c>
       <c r="AE48" s="372" t="n">
-        <v>43.96589733391431</v>
+        <v>43.96589733391432</v>
       </c>
       <c r="AF48" s="372" t="n">
         <v>42.82965118067968</v>
@@ -11578,7 +11578,7 @@
         <v>41.96653063562768</v>
       </c>
       <c r="AH48" s="378" t="n">
-        <v>39.23009108195269</v>
+        <v>39.23009108195267</v>
       </c>
       <c r="AJ48" s="100" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         </is>
       </c>
       <c r="AK48" s="379" t="n">
-        <v>22216.37355701014</v>
+        <v>22216.37355701015</v>
       </c>
       <c r="AL48" s="375" t="n">
         <v>20708.96112639768</v>
@@ -11598,7 +11598,7 @@
         <v>26261.27157099299</v>
       </c>
       <c r="AO48" s="456" t="n">
-        <v>28412.3764402447</v>
+        <v>28412.37644024469</v>
       </c>
       <c r="AP48" s="381" t="n">
         <v>147.2761923579959</v>
@@ -11619,16 +11619,16 @@
         <v>124.8417584870906</v>
       </c>
       <c r="AV48" s="372" t="n">
-        <v>92.01294063005669</v>
+        <v>92.0129406300567</v>
       </c>
       <c r="AW48" s="372" t="n">
-        <v>94.90147229133726</v>
+        <v>94.90147229133727</v>
       </c>
       <c r="AX48" s="372" t="n">
-        <v>97.99164516064251</v>
+        <v>97.99164516064249</v>
       </c>
       <c r="AY48" s="382" t="n">
-        <v>96.33824458909407</v>
+        <v>96.33824458909406</v>
       </c>
       <c r="BA48" s="101" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>29643.15629724725</v>
       </c>
       <c r="BF48" s="392" t="n">
-        <v>32883.58026505758</v>
+        <v>32883.58026505759</v>
       </c>
       <c r="BG48" s="386" t="n">
         <v>152.3006326144784</v>
@@ -11686,7 +11686,7 @@
         </is>
       </c>
       <c r="BS48" s="391" t="n">
-        <v>22940.07407560083</v>
+        <v>22940.07407560082</v>
       </c>
       <c r="BT48" s="375" t="n">
         <v>22102.16316829728</v>
@@ -11695,13 +11695,13 @@
         <v>25641.24059860039</v>
       </c>
       <c r="BV48" s="375" t="n">
-        <v>29749.69103845296</v>
+        <v>29749.69103845297</v>
       </c>
       <c r="BW48" s="392" t="n">
         <v>33066.40965214949</v>
       </c>
       <c r="BX48" s="386" t="n">
-        <v>152.1238573261689</v>
+        <v>152.1238573261688</v>
       </c>
       <c r="BY48" s="372" t="n">
         <v>125.5251222980276</v>
@@ -11725,7 +11725,7 @@
         <v>104.5457635012763</v>
       </c>
       <c r="CF48" s="372" t="n">
-        <v>111.043636242772</v>
+        <v>111.0436362427721</v>
       </c>
       <c r="CG48" s="387" t="n">
         <v>112.1469201944818</v>
@@ -11738,16 +11738,16 @@
         </is>
       </c>
       <c r="C49" s="454" t="n">
-        <v>41248.29742286654</v>
+        <v>41248.29742286653</v>
       </c>
       <c r="D49" s="375" t="n">
-        <v>43664.72019961729</v>
+        <v>43664.7201996173</v>
       </c>
       <c r="E49" s="375" t="n">
-        <v>50822.11816509515</v>
+        <v>50822.11816509514</v>
       </c>
       <c r="F49" s="375" t="n">
-        <v>59754.71047330756</v>
+        <v>59754.71047330757</v>
       </c>
       <c r="G49" s="455" t="n">
         <v>64504.55260009768</v>
@@ -11756,13 +11756,13 @@
         <v>171.3078726553709</v>
       </c>
       <c r="I49" s="372" t="n">
-        <v>99.75788208119046</v>
+        <v>99.75788208119047</v>
       </c>
       <c r="J49" s="372" t="n">
         <v>101.3718552237967</v>
       </c>
       <c r="K49" s="372" t="n">
-        <v>103.2578345471898</v>
+        <v>103.2578345471899</v>
       </c>
       <c r="L49" s="373" t="n">
         <v>95.48469259495134</v>
@@ -11771,10 +11771,10 @@
         <v>160.2930480828327</v>
       </c>
       <c r="N49" s="372" t="n">
-        <v>93.63819626287101</v>
+        <v>93.63819626287102</v>
       </c>
       <c r="O49" s="372" t="n">
-        <v>93.13848131935571</v>
+        <v>93.13848131935569</v>
       </c>
       <c r="P49" s="372" t="n">
         <v>93.98944928724644</v>
@@ -11788,16 +11788,16 @@
         </is>
       </c>
       <c r="T49" s="374" t="n">
-        <v>41248.29742286654</v>
+        <v>41248.29742286653</v>
       </c>
       <c r="U49" s="375" t="n">
-        <v>43664.72019961729</v>
+        <v>43664.7201996173</v>
       </c>
       <c r="V49" s="375" t="n">
-        <v>50822.11816509515</v>
+        <v>50822.11816509514</v>
       </c>
       <c r="W49" s="375" t="n">
-        <v>59754.71047330756</v>
+        <v>59754.71047330757</v>
       </c>
       <c r="X49" s="376" t="n">
         <v>64504.55260009768</v>
@@ -11806,13 +11806,13 @@
         <v>171.3078726553709</v>
       </c>
       <c r="Z49" s="372" t="n">
-        <v>99.75788208119046</v>
+        <v>99.75788208119047</v>
       </c>
       <c r="AA49" s="372" t="n">
         <v>101.3718552237967</v>
       </c>
       <c r="AB49" s="372" t="n">
-        <v>103.2578345471898</v>
+        <v>103.2578345471899</v>
       </c>
       <c r="AC49" s="378" t="n">
         <v>95.48469259495134</v>
@@ -11821,10 +11821,10 @@
         <v>160.2930480828327</v>
       </c>
       <c r="AE49" s="372" t="n">
-        <v>93.63819626287101</v>
+        <v>93.63819626287102</v>
       </c>
       <c r="AF49" s="372" t="n">
-        <v>93.13848131935571</v>
+        <v>93.13848131935569</v>
       </c>
       <c r="AG49" s="372" t="n">
         <v>93.98944928724644</v>
@@ -11838,7 +11838,7 @@
         </is>
       </c>
       <c r="AK49" s="379" t="n">
-        <v>40797.40802859684</v>
+        <v>40797.40802859685</v>
       </c>
       <c r="AL49" s="375" t="n">
         <v>44047.51102550256</v>
@@ -11847,7 +11847,7 @@
         <v>51131.5154401211</v>
       </c>
       <c r="AN49" s="375" t="n">
-        <v>59998.91900857078</v>
+        <v>59998.91900857077</v>
       </c>
       <c r="AO49" s="456" t="n">
         <v>64086.96718583906</v>
@@ -11859,10 +11859,10 @@
         <v>250.8278728569565</v>
       </c>
       <c r="AR49" s="372" t="n">
-        <v>278.6859489614708</v>
+        <v>278.6859489614707</v>
       </c>
       <c r="AS49" s="372" t="n">
-        <v>303.8888485875138</v>
+        <v>303.8888485875137</v>
       </c>
       <c r="AT49" s="382" t="n">
         <v>293.9229262569995</v>
@@ -11880,7 +11880,7 @@
         <v>235.7497136899114</v>
       </c>
       <c r="AY49" s="382" t="n">
-        <v>223.8035373403563</v>
+        <v>223.8035373403564</v>
       </c>
       <c r="BA49" s="111" t="inlineStr">
         <is>
@@ -11891,13 +11891,13 @@
         <v>42028.87492654035</v>
       </c>
       <c r="BC49" s="375" t="n">
-        <v>46713.26529316049</v>
+        <v>46713.26529316048</v>
       </c>
       <c r="BD49" s="375" t="n">
         <v>55983.56159031232</v>
       </c>
       <c r="BE49" s="375" t="n">
-        <v>67543.62403335911</v>
+        <v>67543.6240333591</v>
       </c>
       <c r="BF49" s="392" t="n">
         <v>73933.03042251299</v>
@@ -11947,7 +11947,7 @@
         <v>56229.44997229111</v>
       </c>
       <c r="BV49" s="375" t="n">
-        <v>67943.00763172933</v>
+        <v>67943.00763172931</v>
       </c>
       <c r="BW49" s="392" t="n">
         <v>74476.88135523627</v>
@@ -11962,7 +11962,7 @@
         <v>305.0816319309538</v>
       </c>
       <c r="CA49" s="372" t="n">
-        <v>342.0506826546046</v>
+        <v>342.0506826546045</v>
       </c>
       <c r="CB49" s="387" t="n">
         <v>339.0191052830177</v>
@@ -12193,13 +12193,13 @@
         <v>755.2092654082581</v>
       </c>
       <c r="BT50" s="420" t="n">
-        <v>843.30953446993</v>
+        <v>843.3095344699298</v>
       </c>
       <c r="BU50" s="420" t="n">
-        <v>946.779692542145</v>
+        <v>946.7796925421447</v>
       </c>
       <c r="BV50" s="420" t="n">
-        <v>1040.027194855269</v>
+        <v>1040.027194855268</v>
       </c>
       <c r="BW50" s="421" t="n">
         <v>1140.017687397478</v>
@@ -12208,7 +12208,7 @@
         <v>87.48900391299664</v>
       </c>
       <c r="BY50" s="417" t="n">
-        <v>111.4725325224351</v>
+        <v>111.472532522435</v>
       </c>
       <c r="BZ50" s="417" t="n">
         <v>122.8834032376412</v>
@@ -12223,7 +12223,7 @@
         <v>87.48900391299665</v>
       </c>
       <c r="CD50" s="417" t="n">
-        <v>111.4725325224351</v>
+        <v>111.472532522435</v>
       </c>
       <c r="CE50" s="417" t="n">
         <v>122.8834032376412</v>
@@ -12245,10 +12245,10 @@
         <v>111168.2824783235</v>
       </c>
       <c r="D51" s="425" t="n">
-        <v>88584.73087012261</v>
+        <v>88584.73087012263</v>
       </c>
       <c r="E51" s="425" t="n">
-        <v>99086.35417113696</v>
+        <v>99086.35417113695</v>
       </c>
       <c r="F51" s="425" t="n">
         <v>109859.6082924661</v>
@@ -12266,22 +12266,22 @@
         <v>9.376231943061761</v>
       </c>
       <c r="K51" s="427" t="n">
-        <v>8.727415904268092</v>
+        <v>8.72741590426809</v>
       </c>
       <c r="L51" s="428" t="n">
-        <v>7.750271164065368</v>
+        <v>7.750271164065367</v>
       </c>
       <c r="M51" s="427" t="n">
-        <v>28.97887967025681</v>
+        <v>28.9788796702568</v>
       </c>
       <c r="N51" s="427" t="n">
-        <v>9.883547487939863</v>
+        <v>9.883547487939866</v>
       </c>
       <c r="O51" s="427" t="n">
         <v>9.196259483572796</v>
       </c>
       <c r="P51" s="427" t="n">
-        <v>8.562108209970841</v>
+        <v>8.562108209970839</v>
       </c>
       <c r="Q51" s="428" t="n">
         <v>7.611769580974197</v>
@@ -12295,10 +12295,10 @@
         <v>111168.2824783235</v>
       </c>
       <c r="U51" s="430" t="n">
-        <v>88584.73087012261</v>
+        <v>88584.73087012263</v>
       </c>
       <c r="V51" s="430" t="n">
-        <v>99086.35417113696</v>
+        <v>99086.35417113695</v>
       </c>
       <c r="W51" s="430" t="n">
         <v>109859.6082924661</v>
@@ -12313,7 +12313,7 @@
         <v>10.028512268339</v>
       </c>
       <c r="AA51" s="433" t="n">
-        <v>9.376231943061763</v>
+        <v>9.376231943061761</v>
       </c>
       <c r="AB51" s="433" t="n">
         <v>8.727415904268089</v>
@@ -12322,10 +12322,10 @@
         <v>7.750271164065368</v>
       </c>
       <c r="AD51" s="433" t="n">
-        <v>28.97887967025681</v>
+        <v>28.9788796702568</v>
       </c>
       <c r="AE51" s="433" t="n">
-        <v>9.883547487939865</v>
+        <v>9.883547487939866</v>
       </c>
       <c r="AF51" s="433" t="n">
         <v>9.196259483572796</v>
@@ -12342,13 +12342,13 @@
         </is>
       </c>
       <c r="AK51" s="435" t="n">
-        <v>93680.41222049404</v>
+        <v>93680.41222049405</v>
       </c>
       <c r="AL51" s="408" t="n">
         <v>88967.5216960079</v>
       </c>
       <c r="AM51" s="408" t="n">
-        <v>99395.75144616292</v>
+        <v>99395.7514461629</v>
       </c>
       <c r="AN51" s="408" t="n">
         <v>110103.8168277293</v>
@@ -12357,13 +12357,13 @@
         <v>116075.5731069652</v>
       </c>
       <c r="AP51" s="436" t="n">
-        <v>78.00917697526442</v>
+        <v>78.00917697526444</v>
       </c>
       <c r="AQ51" s="437" t="n">
         <v>39.03332209323741</v>
       </c>
       <c r="AR51" s="437" t="n">
-        <v>37.96788269769812</v>
+        <v>37.96788269769811</v>
       </c>
       <c r="AS51" s="437" t="n">
         <v>36.06022643326553</v>
@@ -12372,7 +12372,7 @@
         <v>32.3329842289758</v>
       </c>
       <c r="AU51" s="437" t="n">
-        <v>74.32885705904914</v>
+        <v>74.32885705904916</v>
       </c>
       <c r="AV51" s="437" t="n">
         <v>36.88662619747279</v>
@@ -12384,7 +12384,7 @@
         <v>33.36987606681937</v>
       </c>
       <c r="AY51" s="438" t="n">
-        <v>30.01963044887223</v>
+        <v>30.01963044887224</v>
       </c>
       <c r="BA51" s="155" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         </is>
       </c>
       <c r="BB51" s="439" t="n">
-        <v>96611.24087174267</v>
+        <v>96611.24087174266</v>
       </c>
       <c r="BC51" s="440" t="n">
         <v>94768.06363341994</v>
@@ -12401,13 +12401,13 @@
         <v>109203.2556298702</v>
       </c>
       <c r="BE51" s="440" t="n">
-        <v>124258.2216579226</v>
+        <v>124258.2216579225</v>
       </c>
       <c r="BF51" s="441" t="n">
         <v>134254.3041707362</v>
       </c>
       <c r="BG51" s="442" t="n">
-        <v>80.44972484989701</v>
+        <v>80.449724849897</v>
       </c>
       <c r="BH51" s="443" t="n">
         <v>41.57823306121928</v>
@@ -12416,13 +12416,13 @@
         <v>41.71422158025966</v>
       </c>
       <c r="BJ51" s="443" t="n">
-        <v>40.69595167795416</v>
+        <v>40.69595167795415</v>
       </c>
       <c r="BK51" s="444" t="n">
         <v>37.39669064932712</v>
       </c>
       <c r="BL51" s="443" t="n">
-        <v>76.65426467329497</v>
+        <v>76.65426467329496</v>
       </c>
       <c r="BM51" s="443" t="n">
         <v>39.29157598262212</v>
@@ -12431,7 +12431,7 @@
         <v>38.61750253098985</v>
       </c>
       <c r="BO51" s="443" t="n">
-        <v>37.65974310859647</v>
+        <v>37.65974310859646</v>
       </c>
       <c r="BP51" s="444" t="n">
         <v>34.72103983205875</v>
@@ -12442,7 +12442,7 @@
         </is>
       </c>
       <c r="BS51" s="439" t="n">
-        <v>96456.52564291806</v>
+        <v>96456.52564291804</v>
       </c>
       <c r="BT51" s="440" t="n">
         <v>94772.19101135473</v>
@@ -12451,19 +12451,19 @@
         <v>109389.7336532371</v>
       </c>
       <c r="BV51" s="440" t="n">
-        <v>124667.8800774211</v>
+        <v>124667.880077421</v>
       </c>
       <c r="BW51" s="441" t="n">
         <v>134907.0186081302</v>
       </c>
       <c r="BX51" s="416" t="n">
-        <v>80.63413706293828</v>
+        <v>80.63413706293827</v>
       </c>
       <c r="BY51" s="417" t="n">
         <v>41.46195029126793</v>
       </c>
       <c r="BZ51" s="417" t="n">
-        <v>41.61758158889122</v>
+        <v>41.61758158889121</v>
       </c>
       <c r="CA51" s="417" t="n">
         <v>40.62070264877642</v>
@@ -12478,10 +12478,10 @@
         <v>39.30503884763295</v>
       </c>
       <c r="CE51" s="417" t="n">
-        <v>38.693307862986</v>
+        <v>38.69330786298599</v>
       </c>
       <c r="CF51" s="417" t="n">
-        <v>37.79211035185904</v>
+        <v>37.79211035185903</v>
       </c>
       <c r="CG51" s="418" t="n">
         <v>34.89609300366028</v>
@@ -13653,13 +13653,13 @@
         <v>6817</v>
       </c>
       <c r="CW58" s="91" t="n">
-        <v>6.492663762398189</v>
+        <v>6.492663762398188</v>
       </c>
       <c r="CX58" s="92" t="n">
         <v>0.5582212223740186</v>
       </c>
       <c r="CY58" s="92" t="n">
-        <v>0.5560499977934451</v>
+        <v>0.5560499977934452</v>
       </c>
       <c r="CZ58" s="92" t="n">
         <v>0.5496802400906833</v>
@@ -13668,13 +13668,13 @@
         <v>0.5365263753544579</v>
       </c>
       <c r="DC58" s="393" t="n">
-        <v>0.006431830911075008</v>
+        <v>0.006431830911075007</v>
       </c>
       <c r="DD58" s="394" t="n">
         <v>0.0002644457974553584</v>
       </c>
       <c r="DE58" s="394" t="n">
-        <v>0.0002248425944801536</v>
+        <v>0.0002248425944801537</v>
       </c>
       <c r="DF58" s="394" t="n">
         <v>0.0001893475001931816</v>
@@ -13968,7 +13968,7 @@
         <v>0.08078411315882889</v>
       </c>
       <c r="CY59" s="103" t="n">
-        <v>0.08279381105870623</v>
+        <v>0.08279381105870622</v>
       </c>
       <c r="CZ59" s="103" t="n">
         <v>0.08509236834521014</v>
@@ -14274,7 +14274,7 @@
         <v>0.2641001573489116</v>
       </c>
       <c r="CX60" s="103" t="n">
-        <v>0.07572616131653596</v>
+        <v>0.07572616131653595</v>
       </c>
       <c r="CY60" s="103" t="n">
         <v>0.07524928641776088</v>
@@ -14532,7 +14532,7 @@
         <v>7.704699476065055</v>
       </c>
       <c r="CA61" s="212" t="n">
-        <v>7.903368820239653</v>
+        <v>7.903368820239654</v>
       </c>
       <c r="CB61" s="213" t="n">
         <v>8.135930453874115</v>
@@ -14547,7 +14547,7 @@
         <v>7.704699476065055</v>
       </c>
       <c r="CF61" s="212" t="n">
-        <v>7.903368820239653</v>
+        <v>7.903368820239654</v>
       </c>
       <c r="CG61" s="213" t="n">
         <v>8.135930453874115</v>
@@ -14580,19 +14580,19 @@
         <v>948</v>
       </c>
       <c r="CW61" s="132" t="n">
-        <v>0.006234181061802669</v>
+        <v>0.006234181061802452</v>
       </c>
       <c r="CX61" s="133" t="n">
-        <v>0.006396145085788302</v>
+        <v>0.00639614508578808</v>
       </c>
       <c r="CY61" s="133" t="n">
-        <v>0.006590523934945408</v>
+        <v>0.006590523934945178</v>
       </c>
       <c r="CZ61" s="133" t="n">
-        <v>0.006724179760346101</v>
+        <v>0.006724179760345867</v>
       </c>
       <c r="DA61" s="134" t="n">
-        <v>0.006860546125885921</v>
+        <v>0.006860546125885682</v>
       </c>
       <c r="DC61" s="422" t="n">
         <v>0</v>
@@ -14889,19 +14889,19 @@
         <v>28924</v>
       </c>
       <c r="CW62" s="132" t="n">
-        <v>7.168619082311844</v>
+        <v>7.168619082311841</v>
       </c>
       <c r="CX62" s="133" t="n">
-        <v>0.7211276419351718</v>
+        <v>0.7211276419351715</v>
       </c>
       <c r="CY62" s="133" t="n">
-        <v>0.7206836192048576</v>
+        <v>0.7206836192048575</v>
       </c>
       <c r="CZ62" s="133" t="n">
-        <v>0.7167354601309138</v>
+        <v>0.7167354601309136</v>
       </c>
       <c r="DA62" s="134" t="n">
-        <v>0.692223460378683</v>
+        <v>0.6922234603786828</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1" thickBot="1">
@@ -15754,7 +15754,7 @@
         </is>
       </c>
       <c r="BS67" s="236" t="n">
-        <v>755.3202508115061</v>
+        <v>755.320250811506</v>
       </c>
       <c r="BT67" s="237" t="n">
         <v>56.33223463137914</v>
@@ -15763,13 +15763,13 @@
         <v>55.6562685015753</v>
       </c>
       <c r="BV67" s="237" t="n">
-        <v>51.23859989215606</v>
+        <v>51.23859989215605</v>
       </c>
       <c r="BW67" s="238" t="n">
         <v>45.51792185462426</v>
       </c>
       <c r="BX67" s="462" t="n">
-        <v>0.8324179598605015</v>
+        <v>0.8324179598605014</v>
       </c>
       <c r="BY67" s="463" t="n">
         <v>0.02904908370918016</v>
@@ -15784,7 +15784,7 @@
         <v>0.01428902418466365</v>
       </c>
       <c r="CC67" s="199" t="n">
-        <v>750.3645815300658</v>
+        <v>750.3645815300657</v>
       </c>
       <c r="CD67" s="200" t="n">
         <v>55.94780197017064</v>
@@ -15796,7 +15796,7 @@
         <v>50.95617596709134</v>
       </c>
       <c r="CG67" s="201" t="n">
-        <v>45.26564866976529</v>
+        <v>45.26564866976531</v>
       </c>
       <c r="CW67" s="465" t="n"/>
       <c r="CX67" s="465" t="n"/>
@@ -16017,7 +16017,7 @@
         </is>
       </c>
       <c r="BS68" s="236" t="n">
-        <v>51.13856851003993</v>
+        <v>51.13856851003994</v>
       </c>
       <c r="BT68" s="237" t="n">
         <v>16.0958098959233</v>
@@ -16044,7 +16044,7 @@
         <v>0.09748899078933781</v>
       </c>
       <c r="CB68" s="464" t="n">
-        <v>0.091558827428478</v>
+        <v>0.09155882742847801</v>
       </c>
       <c r="CC68" s="197" t="n">
         <v>50.85360417009777</v>
@@ -16059,7 +16059,7 @@
         <v>18.9887445413396</v>
       </c>
       <c r="CG68" s="198" t="n">
-        <v>19.848396644392</v>
+        <v>19.84839664439201</v>
       </c>
       <c r="CW68" s="465" t="n"/>
       <c r="CX68" s="465" t="n"/>
@@ -16280,49 +16280,49 @@
         </is>
       </c>
       <c r="BS69" s="236" t="n">
-        <v>84.40848126919826</v>
+        <v>84.40848126919823</v>
       </c>
       <c r="BT69" s="237" t="n">
         <v>46.47854001102073</v>
       </c>
       <c r="BU69" s="237" t="n">
-        <v>50.45142226201709</v>
+        <v>50.45142226201708</v>
       </c>
       <c r="BV69" s="237" t="n">
-        <v>55.5139983432603</v>
+        <v>55.51399834326029</v>
       </c>
       <c r="BW69" s="238" t="n">
-        <v>55.46093120356363</v>
+        <v>55.4609312035636</v>
       </c>
       <c r="BX69" s="462" t="n">
-        <v>0.6230057710226439</v>
+        <v>0.6230057710226437</v>
       </c>
       <c r="BY69" s="463" t="n">
         <v>0.2643552069928728</v>
       </c>
       <c r="BZ69" s="463" t="n">
-        <v>0.2746831767837289</v>
+        <v>0.2746831767837288</v>
       </c>
       <c r="CA69" s="463" t="n">
-        <v>0.2809008726198392</v>
+        <v>0.2809008726198391</v>
       </c>
       <c r="CB69" s="464" t="n">
-        <v>0.2541075764162454</v>
+        <v>0.2541075764162452</v>
       </c>
       <c r="CC69" s="197" t="n">
-        <v>84.33383880616789</v>
+        <v>84.33383880616786</v>
       </c>
       <c r="CD69" s="190" t="n">
         <v>46.56496316032273</v>
       </c>
       <c r="CE69" s="190" t="n">
-        <v>50.62672521263509</v>
+        <v>50.62672521263508</v>
       </c>
       <c r="CF69" s="190" t="n">
-        <v>55.79655618299419</v>
+        <v>55.79655618299417</v>
       </c>
       <c r="CG69" s="198" t="n">
-        <v>55.82322507877655</v>
+        <v>55.82322507877652</v>
       </c>
       <c r="CW69" s="465" t="n"/>
       <c r="CX69" s="465" t="n"/>
@@ -16567,10 +16567,10 @@
         <v>0.2969919616361677</v>
       </c>
       <c r="CA70" s="467" t="n">
-        <v>0.2953979810389686</v>
+        <v>0.2953979810389685</v>
       </c>
       <c r="CB70" s="468" t="n">
-        <v>0.2927736033686234</v>
+        <v>0.2927736033686235</v>
       </c>
       <c r="CC70" s="212" t="n">
         <v>2.164511354735448</v>
@@ -16806,7 +16806,7 @@
         </is>
       </c>
       <c r="BS71" s="271" t="n">
-        <v>893.0380461265414</v>
+        <v>893.0380461265413</v>
       </c>
       <c r="BT71" s="272" t="n">
         <v>121.1337260431404</v>
@@ -16815,28 +16815,28 @@
         <v>125.8143879751312</v>
       </c>
       <c r="BV71" s="272" t="n">
-        <v>128.0366376123743</v>
+        <v>128.0366376123742</v>
       </c>
       <c r="BW71" s="273" t="n">
         <v>123.1276364700726</v>
       </c>
       <c r="BX71" s="466" t="n">
-        <v>0.7420986433893344</v>
+        <v>0.7420986433893343</v>
       </c>
       <c r="BY71" s="467" t="n">
         <v>0.05285345347093779</v>
       </c>
       <c r="BZ71" s="467" t="n">
-        <v>0.04781252069995719</v>
+        <v>0.04781252069995717</v>
       </c>
       <c r="CA71" s="467" t="n">
-        <v>0.04173121269501603</v>
+        <v>0.04173121269501602</v>
       </c>
       <c r="CB71" s="468" t="n">
         <v>0.03413716042992707</v>
       </c>
       <c r="CC71" s="212" t="n">
-        <v>887.716535861067</v>
+        <v>887.7165358610667</v>
       </c>
       <c r="CD71" s="212" t="n">
         <v>120.8104672541753</v>
@@ -20987,10 +20987,10 @@
         <v>1322.396479809194</v>
       </c>
       <c r="AU96" s="379" t="n">
-        <v>992343.7025608228</v>
+        <v>992343.7025608227</v>
       </c>
       <c r="AV96" s="375" t="n">
-        <v>57819.84417732574</v>
+        <v>57819.84417732573</v>
       </c>
       <c r="AW96" s="375" t="n">
         <v>60662.44851795745</v>
@@ -21087,19 +21087,19 @@
         <v>0</v>
       </c>
       <c r="DC96" s="391" t="n">
-        <v>242214.1477819244</v>
+        <v>242214.1477819243</v>
       </c>
       <c r="DD96" s="375" t="n">
-        <v>45650.8171468788</v>
+        <v>45650.81714687879</v>
       </c>
       <c r="DE96" s="375" t="n">
-        <v>48240.88012252497</v>
+        <v>48240.88012252495</v>
       </c>
       <c r="DF96" s="375" t="n">
         <v>47894.66624533237</v>
       </c>
       <c r="DG96" s="392" t="n">
-        <v>47466.23510528405</v>
+        <v>47466.23510528403</v>
       </c>
       <c r="DI96" s="368" t="n"/>
       <c r="DJ96" s="368" t="n"/>
@@ -21223,7 +21223,7 @@
         <v>49502.12565485341</v>
       </c>
       <c r="AX97" s="375" t="n">
-        <v>56261.10047610577</v>
+        <v>56261.10047610578</v>
       </c>
       <c r="AY97" s="456" t="n">
         <v>62226.25224586704</v>
@@ -21323,10 +21323,10 @@
         <v>41783.40242300271</v>
       </c>
       <c r="DF97" s="375" t="n">
-        <v>47538.68160722342</v>
+        <v>47538.68160722341</v>
       </c>
       <c r="DG97" s="392" t="n">
-        <v>52637.13038052491</v>
+        <v>52637.1303805249</v>
       </c>
       <c r="DI97" s="368" t="n"/>
       <c r="DJ97" s="368" t="n"/>
@@ -21553,7 +21553,7 @@
         <v>143492.4846284909</v>
       </c>
       <c r="DG98" s="392" t="n">
-        <v>167538.8087529218</v>
+        <v>167538.8087529217</v>
       </c>
       <c r="DI98" s="368" t="n"/>
       <c r="DJ98" s="368" t="n"/>
@@ -21768,19 +21768,19 @@
         <v>0</v>
       </c>
       <c r="DC99" s="419" t="n">
-        <v>4415.54584678577</v>
+        <v>4415.545846785769</v>
       </c>
       <c r="DD99" s="420" t="n">
-        <v>4762.243435349772</v>
+        <v>4762.243435349771</v>
       </c>
       <c r="DE99" s="420" t="n">
         <v>5162.60207409034</v>
       </c>
       <c r="DF99" s="420" t="n">
-        <v>5542.300576123017</v>
+        <v>5542.300576123016</v>
       </c>
       <c r="DG99" s="421" t="n">
-        <v>5946.33072039547</v>
+        <v>5946.330720395469</v>
       </c>
       <c r="DI99" s="368" t="n"/>
       <c r="DJ99" s="368" t="n"/>
@@ -21997,19 +21997,19 @@
         <v>0</v>
       </c>
       <c r="DC100" s="439" t="n">
-        <v>414274.0719449044</v>
+        <v>414274.0719449043</v>
       </c>
       <c r="DD100" s="440" t="n">
-        <v>185369.1882893765</v>
+        <v>185369.1882893764</v>
       </c>
       <c r="DE100" s="440" t="n">
         <v>213077.5907853029</v>
       </c>
       <c r="DF100" s="440" t="n">
-        <v>244468.1330571697</v>
+        <v>244468.1330571696</v>
       </c>
       <c r="DG100" s="441" t="n">
-        <v>273588.5049591262</v>
+        <v>273588.5049591261</v>
       </c>
       <c r="DI100" s="368" t="n"/>
       <c r="DJ100" s="368" t="n"/>
@@ -23138,13 +23138,13 @@
         <v>500</v>
       </c>
       <c r="CW108" s="199" t="n">
-        <v>6.492663762398189</v>
+        <v>6.492663762398188</v>
       </c>
       <c r="CX108" s="200" t="n">
         <v>0.5582212223740186</v>
       </c>
       <c r="CY108" s="200" t="n">
-        <v>0.5560499977934451</v>
+        <v>0.5560499977934452</v>
       </c>
       <c r="CZ108" s="200" t="n">
         <v>0.5496802400906833</v>
@@ -23439,7 +23439,7 @@
         <v>0.08078411315882889</v>
       </c>
       <c r="CY109" s="190" t="n">
-        <v>0.08279381105870623</v>
+        <v>0.08279381105870622</v>
       </c>
       <c r="CZ109" s="190" t="n">
         <v>0.08509236834521014</v>
@@ -23731,7 +23731,7 @@
         <v>0.2641001573489116</v>
       </c>
       <c r="CX110" s="190" t="n">
-        <v>0.07572616131653596</v>
+        <v>0.07572616131653595</v>
       </c>
       <c r="CY110" s="190" t="n">
         <v>0.07524928641776088</v>
@@ -24023,19 +24023,19 @@
         <v>1590</v>
       </c>
       <c r="CW111" s="211" t="n">
-        <v>0.006234181061802669</v>
+        <v>0.006234181061802452</v>
       </c>
       <c r="CX111" s="212" t="n">
-        <v>0.006396145085788302</v>
+        <v>0.00639614508578808</v>
       </c>
       <c r="CY111" s="212" t="n">
-        <v>0.006590523934945408</v>
+        <v>0.006590523934945178</v>
       </c>
       <c r="CZ111" s="212" t="n">
-        <v>0.006724179760346101</v>
+        <v>0.006724179760345867</v>
       </c>
       <c r="DA111" s="213" t="n">
-        <v>0.006860546125885921</v>
+        <v>0.006860546125885682</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1" thickBot="1">
@@ -24318,19 +24318,19 @@
         <v>10886</v>
       </c>
       <c r="CW112" s="211" t="n">
-        <v>7.168619082311844</v>
+        <v>7.168619082311841</v>
       </c>
       <c r="CX112" s="212" t="n">
-        <v>0.7211276419351718</v>
+        <v>0.7211276419351715</v>
       </c>
       <c r="CY112" s="212" t="n">
-        <v>0.7206836192048576</v>
+        <v>0.7206836192048575</v>
       </c>
       <c r="CZ112" s="212" t="n">
-        <v>0.7167354601309138</v>
+        <v>0.7167354601309136</v>
       </c>
       <c r="DA112" s="213" t="n">
-        <v>0.692223460378683</v>
+        <v>0.6922234603786828</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1" thickBot="1">
@@ -27911,10 +27911,10 @@
         <v>0.03894904327765471</v>
       </c>
       <c r="I130" s="495" t="n">
-        <v>0.04990992972982684</v>
+        <v>0.04990992972982685</v>
       </c>
       <c r="J130" s="495" t="n">
-        <v>0.09650278609956181</v>
+        <v>0.09650278609956182</v>
       </c>
       <c r="K130" s="495" t="n">
         <v>0.1208318545291325</v>
@@ -27923,13 +27923,13 @@
         <v>0.1241408936973136</v>
       </c>
       <c r="M130" s="495" t="n">
-        <v>0.03855360841168162</v>
+        <v>0.03855360841168161</v>
       </c>
       <c r="N130" s="495" t="n">
-        <v>0.04927652132790297</v>
+        <v>0.04927652132790298</v>
       </c>
       <c r="O130" s="495" t="n">
-        <v>0.0956303036239939</v>
+        <v>0.09563030362399393</v>
       </c>
       <c r="P130" s="495" t="n">
         <v>0.119718701186977</v>
@@ -27961,10 +27961,10 @@
         <v>0.03894904327765471</v>
       </c>
       <c r="Z130" s="498" t="n">
-        <v>0.04990992972982684</v>
+        <v>0.04990992972982685</v>
       </c>
       <c r="AA130" s="498" t="n">
-        <v>0.09650278609956181</v>
+        <v>0.09650278609956182</v>
       </c>
       <c r="AB130" s="498" t="n">
         <v>0.1208318545291325</v>
@@ -27973,13 +27973,13 @@
         <v>0.1241408936973136</v>
       </c>
       <c r="AD130" s="498" t="n">
-        <v>0.03855360841168162</v>
+        <v>0.03855360841168161</v>
       </c>
       <c r="AE130" s="498" t="n">
-        <v>0.04927652132790297</v>
+        <v>0.04927652132790298</v>
       </c>
       <c r="AF130" s="498" t="n">
-        <v>0.0956303036239939</v>
+        <v>0.09563030362399393</v>
       </c>
       <c r="AG130" s="498" t="n">
         <v>0.119718701186977</v>
@@ -30329,10 +30329,10 @@
         <v>7800.981532165264</v>
       </c>
       <c r="CX146" s="512" t="n">
-        <v>716.9772907122675</v>
+        <v>716.9772907122674</v>
       </c>
       <c r="CY146" s="512" t="n">
-        <v>726.0615485215985</v>
+        <v>726.0615485215986</v>
       </c>
       <c r="CZ146" s="512" t="n">
         <v>722.9752591706751</v>
@@ -30902,19 +30902,19 @@
         <v>18302.44144493353</v>
       </c>
       <c r="CW149" s="419" t="n">
-        <v>219.8088544235453</v>
+        <v>219.8088544235377</v>
       </c>
       <c r="CX149" s="420" t="n">
-        <v>202.9991592293412</v>
+        <v>202.9991592293341</v>
       </c>
       <c r="CY149" s="420" t="n">
-        <v>212.5341257203996</v>
+        <v>212.5341257203921</v>
       </c>
       <c r="CZ149" s="420" t="n">
-        <v>223.7561512059142</v>
+        <v>223.7561512059064</v>
       </c>
       <c r="DA149" s="421" t="n">
-        <v>236.3659703246933</v>
+        <v>236.365970324685</v>
       </c>
     </row>
     <row r="150" ht="15.75" customHeight="1" thickBot="1">
@@ -30927,7 +30927,7 @@
         <v>427119.3209384317</v>
       </c>
       <c r="D150" s="425" t="n">
-        <v>457098.1422544294</v>
+        <v>457098.1422544293</v>
       </c>
       <c r="E150" s="425" t="n">
         <v>361598.9702909656</v>
@@ -30962,7 +30962,7 @@
         <v>427119.3209384317</v>
       </c>
       <c r="U150" s="430" t="n">
-        <v>457098.1422544294</v>
+        <v>457098.1422544293</v>
       </c>
       <c r="V150" s="430" t="n">
         <v>361598.9702909656</v>
@@ -31094,19 +31094,19 @@
         <v>2699.955785208391</v>
       </c>
       <c r="CW150" s="419" t="n">
-        <v>9585.864518077329</v>
+        <v>9585.86451807732</v>
       </c>
       <c r="CX150" s="420" t="n">
-        <v>1334.342029653239</v>
+        <v>1334.342029653232</v>
       </c>
       <c r="CY150" s="420" t="n">
-        <v>1383.269446486624</v>
+        <v>1383.269446486617</v>
       </c>
       <c r="CZ150" s="420" t="n">
-        <v>1421.219736516749</v>
+        <v>1421.219736516741</v>
       </c>
       <c r="DA150" s="421" t="n">
-        <v>1397.977953458658</v>
+        <v>1397.97795345865</v>
       </c>
     </row>
     <row r="151">
@@ -35135,7 +35135,7 @@
         <v>7.704699170064885</v>
       </c>
       <c r="CA175" s="212" t="n">
-        <v>7.903368641240074</v>
+        <v>7.903368641240075</v>
       </c>
       <c r="CB175" s="213" t="n">
         <v>8.135930074873956</v>
@@ -35150,7 +35150,7 @@
         <v>7.704699170064885</v>
       </c>
       <c r="CF175" s="212" t="n">
-        <v>7.903368641240074</v>
+        <v>7.903368641240075</v>
       </c>
       <c r="CG175" s="213" t="n">
         <v>8.135930074873956</v>
@@ -38461,34 +38461,34 @@
         <v>128.501482714</v>
       </c>
       <c r="AP190" s="194" t="n">
-        <v>906.0765657566789</v>
+        <v>906.0765657566794</v>
       </c>
       <c r="AQ190" s="179" t="n">
-        <v>1920.607781175104</v>
+        <v>1920.607781175106</v>
       </c>
       <c r="AR190" s="179" t="n">
-        <v>2249.19267206588</v>
+        <v>2249.192672065879</v>
       </c>
       <c r="AS190" s="179" t="n">
-        <v>2654.460653987201</v>
+        <v>2654.460653987202</v>
       </c>
       <c r="AT190" s="195" t="n">
-        <v>3148.734546452975</v>
+        <v>3148.734546452976</v>
       </c>
       <c r="AU190" s="190" t="n">
-        <v>921.8835847439331</v>
+        <v>921.8835847439336</v>
       </c>
       <c r="AV190" s="190" t="n">
-        <v>1975.066111716584</v>
+        <v>1975.066111716585</v>
       </c>
       <c r="AW190" s="190" t="n">
-        <v>2346.968258259807</v>
+        <v>2346.968258259806</v>
       </c>
       <c r="AX190" s="190" t="n">
         <v>2769.089609236199</v>
       </c>
       <c r="AY190" s="196" t="n">
-        <v>3277.236029166532</v>
+        <v>3277.236029166533</v>
       </c>
       <c r="BA190" s="83" t="inlineStr">
         <is>
@@ -38511,34 +38511,34 @@
         <v>128.501482714</v>
       </c>
       <c r="BG190" s="197" t="n">
-        <v>906.0765657566789</v>
+        <v>906.0765657566794</v>
       </c>
       <c r="BH190" s="190" t="n">
-        <v>1920.607781175104</v>
+        <v>1920.607781175106</v>
       </c>
       <c r="BI190" s="190" t="n">
-        <v>2249.19267206588</v>
+        <v>2249.192672065879</v>
       </c>
       <c r="BJ190" s="190" t="n">
-        <v>2654.460653987201</v>
+        <v>2654.460653987202</v>
       </c>
       <c r="BK190" s="198" t="n">
-        <v>3148.734546452975</v>
+        <v>3148.734546452976</v>
       </c>
       <c r="BL190" s="199" t="n">
-        <v>921.8835847436789</v>
+        <v>921.8835847436794</v>
       </c>
       <c r="BM190" s="200" t="n">
-        <v>1975.066111716104</v>
+        <v>1975.066111716106</v>
       </c>
       <c r="BN190" s="200" t="n">
-        <v>2346.96825825988</v>
+        <v>2346.968258259879</v>
       </c>
       <c r="BO190" s="200" t="n">
-        <v>2769.089609236201</v>
+        <v>2769.089609236202</v>
       </c>
       <c r="BP190" s="201" t="n">
-        <v>3277.236029166975</v>
+        <v>3277.236029166976</v>
       </c>
       <c r="BR190" s="83" t="inlineStr">
         <is>
@@ -38561,25 +38561,25 @@
         <v>108.838066539</v>
       </c>
       <c r="BX190" s="197" t="n">
-        <v>901.427669163768</v>
+        <v>901.4276691637685</v>
       </c>
       <c r="BY190" s="190" t="n">
-        <v>1925.974758287879</v>
+        <v>1925.97475828788</v>
       </c>
       <c r="BZ190" s="190" t="n">
-        <v>2258.024495101126</v>
+        <v>2258.024495101125</v>
       </c>
       <c r="CA190" s="190" t="n">
-        <v>2667.756421793291</v>
+        <v>2667.756421793292</v>
       </c>
       <c r="CB190" s="198" t="n">
         <v>3167.861436252623</v>
       </c>
       <c r="CC190" s="199" t="n">
-        <v>915.390920981768</v>
+        <v>915.3909209817685</v>
       </c>
       <c r="CD190" s="200" t="n">
-        <v>1974.507890493879</v>
+        <v>1974.50789049388</v>
       </c>
       <c r="CE190" s="200" t="n">
         <v>2346.412208262126</v>
@@ -38618,13 +38618,13 @@
         <v>6817</v>
       </c>
       <c r="CW190" s="91" t="n">
-        <v>6.492663762398207</v>
+        <v>6.492663762398206</v>
       </c>
       <c r="CX190" s="92" t="n">
         <v>0.5582212223740151</v>
       </c>
       <c r="CY190" s="92" t="n">
-        <v>0.5560499977934461</v>
+        <v>0.5560499977934462</v>
       </c>
       <c r="CZ190" s="92" t="n">
         <v>0.5496802400906827</v>
@@ -38633,13 +38633,13 @@
         <v>0.5365263753544433</v>
       </c>
       <c r="DC190" s="393" t="n">
-        <v>0.006431830912802235</v>
+        <v>0.00643183091280223</v>
       </c>
       <c r="DD190" s="394" t="n">
-        <v>0.0002644457974312485</v>
+        <v>0.0002644457974312483</v>
       </c>
       <c r="DE190" s="394" t="n">
-        <v>0.0002248425944735679</v>
+        <v>0.000224842594473568</v>
       </c>
       <c r="DF190" s="394" t="n">
         <v>0.0001893475001940946</v>
@@ -38776,13 +38776,13 @@
         <v>175.4831942698608</v>
       </c>
       <c r="AR191" s="179" t="n">
-        <v>177.512724265385</v>
+        <v>177.5127242653849</v>
       </c>
       <c r="AS191" s="179" t="n">
-        <v>193.5234654579763</v>
+        <v>193.5234654579764</v>
       </c>
       <c r="AT191" s="195" t="n">
-        <v>215.0875607908826</v>
+        <v>215.0875607908825</v>
       </c>
       <c r="AU191" s="190" t="n">
         <v>177.9562690168208</v>
@@ -38791,10 +38791,10 @@
         <v>225.065746285599</v>
       </c>
       <c r="AW191" s="190" t="n">
-        <v>245.3461097797302</v>
+        <v>245.3461097797301</v>
       </c>
       <c r="AX191" s="190" t="n">
-        <v>267.9950068499835</v>
+        <v>267.9950068499836</v>
       </c>
       <c r="AY191" s="196" t="n">
         <v>294.9231277870304</v>
@@ -38826,13 +38826,13 @@
         <v>175.4831942698608</v>
       </c>
       <c r="BI191" s="190" t="n">
-        <v>177.512724265385</v>
+        <v>177.5127242653849</v>
       </c>
       <c r="BJ191" s="190" t="n">
-        <v>193.5234654579763</v>
+        <v>193.5234654579764</v>
       </c>
       <c r="BK191" s="198" t="n">
-        <v>215.0875607908826</v>
+        <v>215.0875607908825</v>
       </c>
       <c r="BL191" s="197" t="n">
         <v>177.9562690169142</v>
@@ -38841,10 +38841,10 @@
         <v>225.0657462858608</v>
       </c>
       <c r="BN191" s="190" t="n">
-        <v>245.346109779385</v>
+        <v>245.3461097793849</v>
       </c>
       <c r="BO191" s="190" t="n">
-        <v>267.9950068499763</v>
+        <v>267.9950068499764</v>
       </c>
       <c r="BP191" s="198" t="n">
         <v>294.9231277868826</v>
@@ -38876,13 +38876,13 @@
         <v>176.0776073955597</v>
       </c>
       <c r="BZ191" s="190" t="n">
-        <v>178.411314893444</v>
+        <v>178.4113148934439</v>
       </c>
       <c r="CA191" s="190" t="n">
-        <v>194.7783481238813</v>
+        <v>194.7783481238814</v>
       </c>
       <c r="CB191" s="198" t="n">
-        <v>216.7829927773281</v>
+        <v>216.782992777328</v>
       </c>
       <c r="CC191" s="197" t="n">
         <v>177.5506480354451</v>
@@ -38891,13 +38891,13 @@
         <v>224.9849621725596</v>
       </c>
       <c r="CE191" s="190" t="n">
-        <v>245.263315968444</v>
+        <v>245.2633159684439</v>
       </c>
       <c r="CF191" s="190" t="n">
-        <v>267.9099144818813</v>
+        <v>267.9099144818815</v>
       </c>
       <c r="CG191" s="198" t="n">
-        <v>294.8490210063281</v>
+        <v>294.849021006328</v>
       </c>
       <c r="CI191" s="197" t="n">
         <v>0</v>
@@ -38939,19 +38939,19 @@
         <v>0.08509236834482972</v>
       </c>
       <c r="DA191" s="104" t="n">
-        <v>0.07410678027584618</v>
+        <v>0.07410678027584619</v>
       </c>
       <c r="DC191" s="396" t="n">
-        <v>0.002257409169410833</v>
+        <v>0.002257409169410834</v>
       </c>
       <c r="DD191" s="397" t="n">
         <v>0.0003435461093416543</v>
       </c>
       <c r="DE191" s="397" t="n">
-        <v>0.000340820874314146</v>
+        <v>0.0003408208743141462</v>
       </c>
       <c r="DF191" s="397" t="n">
-        <v>0.0003139086487703765</v>
+        <v>0.0003139086487703762</v>
       </c>
       <c r="DG191" s="398" t="n">
         <v>0.0002265054046529094</v>
@@ -39085,16 +39085,16 @@
         <v>175.6085183659754</v>
       </c>
       <c r="AR192" s="179" t="n">
-        <v>183.473604220412</v>
+        <v>183.4736042204119</v>
       </c>
       <c r="AS192" s="179" t="n">
         <v>197.4370540006157</v>
       </c>
       <c r="AT192" s="195" t="n">
-        <v>218.040042079689</v>
+        <v>218.0400420796891</v>
       </c>
       <c r="AU192" s="190" t="n">
-        <v>151.872364552633</v>
+        <v>151.8723645526329</v>
       </c>
       <c r="AV192" s="190" t="n">
         <v>204.2146775417666</v>
@@ -39106,7 +39106,7 @@
         <v>254.5026166542022</v>
       </c>
       <c r="AY192" s="196" t="n">
-        <v>286.3536830776261</v>
+        <v>286.3536830776262</v>
       </c>
       <c r="BA192" s="111" t="inlineStr">
         <is>
@@ -39135,13 +39135,13 @@
         <v>175.6085183659754</v>
       </c>
       <c r="BI192" s="190" t="n">
-        <v>183.473604220412</v>
+        <v>183.4736042204119</v>
       </c>
       <c r="BJ192" s="190" t="n">
         <v>197.4370540006157</v>
       </c>
       <c r="BK192" s="198" t="n">
-        <v>218.040042079689</v>
+        <v>218.0400420796891</v>
       </c>
       <c r="BL192" s="197" t="n">
         <v>151.8723645531072</v>
@@ -39150,13 +39150,13 @@
         <v>204.2146775419754</v>
       </c>
       <c r="BN192" s="190" t="n">
-        <v>227.792002199412</v>
+        <v>227.7920021994119</v>
       </c>
       <c r="BO192" s="190" t="n">
         <v>254.5026166546157</v>
       </c>
       <c r="BP192" s="198" t="n">
-        <v>286.353683077689</v>
+        <v>286.3536830776891</v>
       </c>
       <c r="BR192" s="111" t="inlineStr">
         <is>
@@ -39179,13 +39179,13 @@
         <v>66.5955189</v>
       </c>
       <c r="BX192" s="197" t="n">
-        <v>135.3660632898644</v>
+        <v>135.3660632898643</v>
       </c>
       <c r="BY192" s="190" t="n">
         <v>176.1454362372849</v>
       </c>
       <c r="BZ192" s="190" t="n">
-        <v>184.309522942792</v>
+        <v>184.3095229427919</v>
       </c>
       <c r="CA192" s="190" t="n">
         <v>198.6343284119542</v>
@@ -39194,19 +39194,19 @@
         <v>219.6834344195326</v>
       </c>
       <c r="CC192" s="197" t="n">
-        <v>151.6082643958644</v>
+        <v>151.6082643958643</v>
       </c>
       <c r="CD192" s="190" t="n">
         <v>204.1389513802849</v>
       </c>
       <c r="CE192" s="190" t="n">
-        <v>227.716752912792</v>
+        <v>227.7167529127919</v>
       </c>
       <c r="CF192" s="190" t="n">
         <v>254.4273779829542</v>
       </c>
       <c r="CG192" s="198" t="n">
-        <v>286.2789533195325</v>
+        <v>286.2789533195326</v>
       </c>
       <c r="CI192" s="197" t="n">
         <v>0</v>
@@ -39236,7 +39236,7 @@
         <v>8351</v>
       </c>
       <c r="CW192" s="102" t="n">
-        <v>0.2641001573490654</v>
+        <v>0.2641001573490653</v>
       </c>
       <c r="CX192" s="103" t="n">
         <v>0.07572616131645396</v>
@@ -39251,13 +39251,13 @@
         <v>0.07472975862258897</v>
       </c>
       <c r="DC192" s="396" t="n">
-        <v>0.001826142066693256</v>
+        <v>0.001826142066693257</v>
       </c>
       <c r="DD192" s="397" t="n">
         <v>0.0003783503650440781</v>
       </c>
       <c r="DE192" s="397" t="n">
-        <v>0.0003547374436696241</v>
+        <v>0.0003547374436696243</v>
       </c>
       <c r="DF192" s="397" t="n">
         <v>0.0003240615051177905</v>
@@ -39388,34 +39388,34 @@
         <v>0</v>
       </c>
       <c r="AP193" s="206" t="n">
-        <v>8.638281980360059</v>
+        <v>8.638281980360063</v>
       </c>
       <c r="AQ193" s="207" t="n">
-        <v>7.57157414661857</v>
+        <v>7.571574146618563</v>
       </c>
       <c r="AR193" s="207" t="n">
         <v>7.711289693800254</v>
       </c>
       <c r="AS193" s="207" t="n">
-        <v>7.910092821495514</v>
+        <v>7.910092821495521</v>
       </c>
       <c r="AT193" s="208" t="n">
-        <v>8.142790620811347</v>
+        <v>8.142790620811343</v>
       </c>
       <c r="AU193" s="209" t="n">
-        <v>8.638281980360059</v>
+        <v>8.638281980360063</v>
       </c>
       <c r="AV193" s="209" t="n">
-        <v>7.57157414661857</v>
+        <v>7.571574146618563</v>
       </c>
       <c r="AW193" s="209" t="n">
         <v>7.711289693800254</v>
       </c>
       <c r="AX193" s="209" t="n">
-        <v>7.910092821495514</v>
+        <v>7.910092821495521</v>
       </c>
       <c r="AY193" s="210" t="n">
-        <v>8.142790620811347</v>
+        <v>8.142790620811343</v>
       </c>
       <c r="BA193" s="111" t="inlineStr">
         <is>
@@ -39438,34 +39438,34 @@
         <v>0</v>
       </c>
       <c r="BG193" s="211" t="n">
-        <v>8.638281980360059</v>
+        <v>8.638281980360063</v>
       </c>
       <c r="BH193" s="212" t="n">
-        <v>7.57157414661857</v>
+        <v>7.571574146618563</v>
       </c>
       <c r="BI193" s="212" t="n">
         <v>7.711289693800254</v>
       </c>
       <c r="BJ193" s="212" t="n">
-        <v>7.910092821495514</v>
+        <v>7.910092821495521</v>
       </c>
       <c r="BK193" s="213" t="n">
-        <v>8.142790620811347</v>
+        <v>8.142790620811343</v>
       </c>
       <c r="BL193" s="212" t="n">
-        <v>8.638281980360059</v>
+        <v>8.638281980360063</v>
       </c>
       <c r="BM193" s="212" t="n">
-        <v>7.57157414661857</v>
+        <v>7.571574146618563</v>
       </c>
       <c r="BN193" s="212" t="n">
         <v>7.711289693800254</v>
       </c>
       <c r="BO193" s="212" t="n">
-        <v>7.910092821495514</v>
+        <v>7.910092821495521</v>
       </c>
       <c r="BP193" s="213" t="n">
-        <v>8.142790620811347</v>
+        <v>8.142790620811343</v>
       </c>
       <c r="BR193" s="111" t="inlineStr">
         <is>
@@ -39488,34 +39488,34 @@
         <v>0</v>
       </c>
       <c r="BX193" s="211" t="n">
-        <v>8.632047799298256</v>
+        <v>8.63204779929826</v>
       </c>
       <c r="BY193" s="212" t="n">
-        <v>7.565178001532781</v>
+        <v>7.565178001532774</v>
       </c>
       <c r="BZ193" s="212" t="n">
         <v>7.704699169865308</v>
       </c>
       <c r="CA193" s="212" t="n">
-        <v>7.903368641735168</v>
+        <v>7.903368641735176</v>
       </c>
       <c r="CB193" s="213" t="n">
-        <v>8.135930074685461</v>
+        <v>8.135930074685458</v>
       </c>
       <c r="CC193" s="212" t="n">
-        <v>8.632047799298256</v>
+        <v>8.63204779929826</v>
       </c>
       <c r="CD193" s="212" t="n">
-        <v>7.565178001532781</v>
+        <v>7.565178001532774</v>
       </c>
       <c r="CE193" s="212" t="n">
         <v>7.704699169865308</v>
       </c>
       <c r="CF193" s="212" t="n">
-        <v>7.903368641735168</v>
+        <v>7.903368641735176</v>
       </c>
       <c r="CG193" s="213" t="n">
-        <v>8.135930074685461</v>
+        <v>8.135930074685458</v>
       </c>
       <c r="CI193" s="211" t="n">
         <v>0</v>
@@ -39545,19 +39545,19 @@
         <v>948</v>
       </c>
       <c r="CW193" s="132" t="n">
-        <v>0.00623418106180267</v>
+        <v>0.006234181061802453</v>
       </c>
       <c r="CX193" s="133" t="n">
-        <v>0.006396145085788303</v>
+        <v>0.00639614508578808</v>
       </c>
       <c r="CY193" s="133" t="n">
-        <v>0.006590523934945408</v>
+        <v>0.006590523934945179</v>
       </c>
       <c r="CZ193" s="133" t="n">
-        <v>0.006724179760346102</v>
+        <v>0.006724179760345868</v>
       </c>
       <c r="DA193" s="134" t="n">
-        <v>0.006860546125885922</v>
+        <v>0.006860546125885682</v>
       </c>
       <c r="DC193" s="422" t="n">
         <v>0</v>
@@ -39697,34 +39697,34 @@
         <v>276.650690708</v>
       </c>
       <c r="AP194" s="206" t="n">
-        <v>1200.88963646106</v>
+        <v>1200.889636461061</v>
       </c>
       <c r="AQ194" s="207" t="n">
-        <v>2279.271067957559</v>
+        <v>2279.27106795756</v>
       </c>
       <c r="AR194" s="207" t="n">
-        <v>2617.890290245477</v>
+        <v>2617.890290245476</v>
       </c>
       <c r="AS194" s="207" t="n">
         <v>3053.331266267289</v>
       </c>
       <c r="AT194" s="208" t="n">
-        <v>3590.004939944358</v>
+        <v>3590.004939944359</v>
       </c>
       <c r="AU194" s="207" t="n">
         <v>1260.350500293747</v>
       </c>
       <c r="AV194" s="207" t="n">
-        <v>2411.918109690568</v>
+        <v>2411.918109690569</v>
       </c>
       <c r="AW194" s="207" t="n">
-        <v>2827.817659932743</v>
+        <v>2827.817659932742</v>
       </c>
       <c r="AX194" s="207" t="n">
-        <v>3299.49732556188</v>
+        <v>3299.497325561881</v>
       </c>
       <c r="AY194" s="208" t="n">
-        <v>3866.655630652</v>
+        <v>3866.655630652001</v>
       </c>
       <c r="BA194" s="155" t="inlineStr">
         <is>
@@ -39747,28 +39747,28 @@
         <v>276.650690708</v>
       </c>
       <c r="BG194" s="221" t="n">
-        <v>1200.88963646106</v>
+        <v>1200.889636461061</v>
       </c>
       <c r="BH194" s="222" t="n">
-        <v>2279.271067957559</v>
+        <v>2279.27106795756</v>
       </c>
       <c r="BI194" s="222" t="n">
-        <v>2617.890290245477</v>
+        <v>2617.890290245476</v>
       </c>
       <c r="BJ194" s="222" t="n">
         <v>3053.331266267289</v>
       </c>
       <c r="BK194" s="214" t="n">
-        <v>3590.004939944358</v>
+        <v>3590.004939944359</v>
       </c>
       <c r="BL194" s="222" t="n">
-        <v>1260.35050029406</v>
+        <v>1260.350500294061</v>
       </c>
       <c r="BM194" s="222" t="n">
         <v>2411.91810969056</v>
       </c>
       <c r="BN194" s="222" t="n">
-        <v>2827.817659932477</v>
+        <v>2827.817659932476</v>
       </c>
       <c r="BO194" s="222" t="n">
         <v>3299.497325562289</v>
@@ -39800,13 +39800,13 @@
         <v>1196.224441815376</v>
       </c>
       <c r="BY194" s="222" t="n">
-        <v>2285.762979922256</v>
+        <v>2285.762979922257</v>
       </c>
       <c r="BZ194" s="222" t="n">
-        <v>2628.450032107227</v>
+        <v>2628.450032107226</v>
       </c>
       <c r="CA194" s="222" t="n">
-        <v>3069.072466970862</v>
+        <v>3069.072466970863</v>
       </c>
       <c r="CB194" s="214" t="n">
         <v>3612.463793524169</v>
@@ -39815,10 +39815,10 @@
         <v>1253.181881212376</v>
       </c>
       <c r="CD194" s="222" t="n">
-        <v>2411.196982048256</v>
+        <v>2411.196982048258</v>
       </c>
       <c r="CE194" s="222" t="n">
-        <v>2827.096976313228</v>
+        <v>2827.096976313227</v>
       </c>
       <c r="CF194" s="222" t="n">
         <v>3298.780590102862</v>
@@ -39854,19 +39854,19 @@
         <v>28924</v>
       </c>
       <c r="CW194" s="132" t="n">
-        <v>7.168619082312015</v>
+        <v>7.168619082312014</v>
       </c>
       <c r="CX194" s="133" t="n">
-        <v>0.7211276419349758</v>
+        <v>0.7211276419349756</v>
       </c>
       <c r="CY194" s="133" t="n">
-        <v>0.7206836192045893</v>
+        <v>0.7206836192045892</v>
       </c>
       <c r="CZ194" s="133" t="n">
-        <v>0.7167354601305401</v>
+        <v>0.7167354601305398</v>
       </c>
       <c r="DA194" s="134" t="n">
-        <v>0.6922234603787643</v>
+        <v>0.692223460378764</v>
       </c>
     </row>
     <row r="195" ht="15.75" customHeight="1" thickBot="1">
@@ -40822,31 +40822,31 @@
         <v>0.006</v>
       </c>
       <c r="AP199" s="233" t="n">
-        <v>1.843767169487866</v>
+        <v>1.843767169487867</v>
       </c>
       <c r="AQ199" s="190" t="n">
-        <v>5.925198335149751</v>
+        <v>5.925198335149755</v>
       </c>
       <c r="AR199" s="190" t="n">
-        <v>9.387873033039227</v>
+        <v>9.387873033039225</v>
       </c>
       <c r="AS199" s="190" t="n">
-        <v>13.84544804618099</v>
+        <v>13.845448046181</v>
       </c>
       <c r="AT199" s="196" t="n">
         <v>19.6634161749992</v>
       </c>
       <c r="AU199" s="190" t="n">
-        <v>907.9203329261667</v>
+        <v>907.9203329261672</v>
       </c>
       <c r="AV199" s="190" t="n">
-        <v>1926.532979510254</v>
+        <v>1926.532979510255</v>
       </c>
       <c r="AW199" s="190" t="n">
         <v>2258.580545098919</v>
       </c>
       <c r="AX199" s="190" t="n">
-        <v>2668.306102033382</v>
+        <v>2668.306102033383</v>
       </c>
       <c r="AY199" s="196" t="n">
         <v>3168.397962627975</v>
@@ -40872,31 +40872,31 @@
         <v>0.006</v>
       </c>
       <c r="BG199" s="197" t="n">
-        <v>1.843767169487358</v>
+        <v>1.843767169487359</v>
       </c>
       <c r="BH199" s="190" t="n">
-        <v>5.925198335148314</v>
+        <v>5.925198335148317</v>
       </c>
       <c r="BI199" s="190" t="n">
-        <v>9.387873033039519</v>
+        <v>9.387873033039517</v>
       </c>
       <c r="BJ199" s="190" t="n">
-        <v>13.845448046181</v>
+        <v>13.84544804618101</v>
       </c>
       <c r="BK199" s="198" t="n">
         <v>19.66341617500185</v>
       </c>
       <c r="BL199" s="199" t="n">
-        <v>907.9203329261662</v>
+        <v>907.9203329261668</v>
       </c>
       <c r="BM199" s="200" t="n">
-        <v>1926.532979510253</v>
+        <v>1926.532979510254</v>
       </c>
       <c r="BN199" s="200" t="n">
         <v>2258.580545098919</v>
       </c>
       <c r="BO199" s="200" t="n">
-        <v>2668.306102033382</v>
+        <v>2668.306102033383</v>
       </c>
       <c r="BP199" s="201" t="n">
         <v>3168.397962627977</v>
@@ -40907,7 +40907,7 @@
         </is>
       </c>
       <c r="BS199" s="335" t="n">
-        <v>755.3202508115061</v>
+        <v>755.320250811506</v>
       </c>
       <c r="BT199" s="336" t="n">
         <v>56.33223463137914</v>
@@ -40916,19 +40916,19 @@
         <v>55.6562685015753</v>
       </c>
       <c r="BV199" s="336" t="n">
-        <v>51.23859989215606</v>
+        <v>51.23859989215605</v>
       </c>
       <c r="BW199" s="337" t="n">
         <v>45.51792185462426</v>
       </c>
       <c r="BX199" s="462" t="n">
-        <v>0.8324179600856521</v>
+        <v>0.8324179600856514</v>
       </c>
       <c r="BY199" s="463" t="n">
-        <v>0.02904908370653094</v>
+        <v>0.02904908370653092</v>
       </c>
       <c r="BZ199" s="463" t="n">
-        <v>0.02450483665019173</v>
+        <v>0.02450483665019174</v>
       </c>
       <c r="CA199" s="463" t="n">
         <v>0.01910076030585958</v>
@@ -40937,13 +40937,13 @@
         <v>0.01428902418260769</v>
       </c>
       <c r="CC199" s="199" t="n">
-        <v>750.3645815300678</v>
+        <v>750.3645815300677</v>
       </c>
       <c r="CD199" s="200" t="n">
         <v>55.94780197017028</v>
       </c>
       <c r="CE199" s="200" t="n">
-        <v>55.33252140458475</v>
+        <v>55.33252140458476</v>
       </c>
       <c r="CF199" s="200" t="n">
         <v>50.95617596709129</v>
@@ -41135,16 +41135,16 @@
         <v>0.006</v>
       </c>
       <c r="AP200" s="233" t="n">
-        <v>0.3559125380336417</v>
+        <v>0.3559125380336416</v>
       </c>
       <c r="AQ200" s="190" t="n">
         <v>0.6751972388567971</v>
       </c>
       <c r="AR200" s="190" t="n">
-        <v>0.9813844391189208</v>
+        <v>0.9813844391189203</v>
       </c>
       <c r="AS200" s="190" t="n">
-        <v>1.339975034249917</v>
+        <v>1.339975034249918</v>
       </c>
       <c r="AT200" s="196" t="n">
         <v>1.769538766722182</v>
@@ -41156,13 +41156,13 @@
         <v>176.1583915087176</v>
       </c>
       <c r="AW200" s="190" t="n">
-        <v>178.494108704504</v>
+        <v>178.4941087045038</v>
       </c>
       <c r="AX200" s="190" t="n">
-        <v>194.8634404922262</v>
+        <v>194.8634404922263</v>
       </c>
       <c r="AY200" s="196" t="n">
-        <v>216.8570995576048</v>
+        <v>216.8570995576047</v>
       </c>
       <c r="BA200" s="101" t="inlineStr">
         <is>
@@ -41191,13 +41191,13 @@
         <v>0.6751972388575824</v>
       </c>
       <c r="BI200" s="190" t="n">
-        <v>0.9813844391175401</v>
+        <v>0.9813844391175396</v>
       </c>
       <c r="BJ200" s="190" t="n">
         <v>1.339975034249882</v>
       </c>
       <c r="BK200" s="198" t="n">
-        <v>1.769538766721296</v>
+        <v>1.769538766721295</v>
       </c>
       <c r="BL200" s="197" t="n">
         <v>151.204282543948</v>
@@ -41206,13 +41206,13 @@
         <v>176.1583915087184</v>
       </c>
       <c r="BN200" s="190" t="n">
-        <v>178.4941087045026</v>
+        <v>178.4941087045025</v>
       </c>
       <c r="BO200" s="190" t="n">
-        <v>194.8634404922261</v>
+        <v>194.8634404922263</v>
       </c>
       <c r="BP200" s="198" t="n">
-        <v>216.8570995576039</v>
+        <v>216.8570995576038</v>
       </c>
       <c r="BR200" s="101" t="inlineStr">
         <is>
@@ -41220,7 +41220,7 @@
         </is>
       </c>
       <c r="BS200" s="335" t="n">
-        <v>51.13856851003993</v>
+        <v>51.13856851003994</v>
       </c>
       <c r="BT200" s="336" t="n">
         <v>16.0958098959233</v>
@@ -41235,19 +41235,19 @@
         <v>19.75993719002158</v>
       </c>
       <c r="BX200" s="462" t="n">
-        <v>0.337228484942749</v>
+        <v>0.3372284849427492</v>
       </c>
       <c r="BY200" s="463" t="n">
         <v>0.09130608373051921</v>
       </c>
       <c r="BZ200" s="463" t="n">
-        <v>0.0976694843542965</v>
+        <v>0.09766948435429658</v>
       </c>
       <c r="CA200" s="463" t="n">
-        <v>0.09748899055852782</v>
+        <v>0.09748899055852776</v>
       </c>
       <c r="CB200" s="464" t="n">
-        <v>0.09155882751752584</v>
+        <v>0.09155882751752591</v>
       </c>
       <c r="CC200" s="197" t="n">
         <v>50.85360417009773</v>
@@ -41262,7 +41262,7 @@
         <v>18.98874454125471</v>
       </c>
       <c r="CG200" s="198" t="n">
-        <v>19.84839664443243</v>
+        <v>19.84839664443244</v>
       </c>
       <c r="CI200" s="396" t="n">
         <v>0.9999999996515252</v>
@@ -41311,7 +41311,7 @@
         <v>1.000000000030032</v>
       </c>
       <c r="CY200" s="396" t="n">
-        <v>1.00000000130491</v>
+        <v>1.000000001304909</v>
       </c>
       <c r="CZ200" s="397" t="n">
         <v>0.999999998569393</v>
@@ -41448,13 +41448,13 @@
         <v>0.006</v>
       </c>
       <c r="AP201" s="233" t="n">
-        <v>0.303744729105266</v>
+        <v>0.3037447291052658</v>
       </c>
       <c r="AQ201" s="190" t="n">
         <v>0.6126440326252998</v>
       </c>
       <c r="AR201" s="190" t="n">
-        <v>0.9111680087976228</v>
+        <v>0.9111680087976226</v>
       </c>
       <c r="AS201" s="190" t="n">
         <v>1.272513083271011</v>
@@ -41463,13 +41463,13 @@
         <v>1.718122098465757</v>
       </c>
       <c r="AU201" s="190" t="n">
-        <v>135.6301634472125</v>
+        <v>135.6301634472124</v>
       </c>
       <c r="AV201" s="190" t="n">
         <v>176.2211623986007</v>
       </c>
       <c r="AW201" s="190" t="n">
-        <v>184.3847722292096</v>
+        <v>184.3847722292095</v>
       </c>
       <c r="AX201" s="190" t="n">
         <v>198.7095670838868</v>
@@ -41498,19 +41498,19 @@
         <v>0.006</v>
       </c>
       <c r="BG201" s="197" t="n">
-        <v>0.3037447291062144</v>
+        <v>0.3037447291062143</v>
       </c>
       <c r="BH201" s="190" t="n">
         <v>0.6126440326259264</v>
       </c>
       <c r="BI201" s="190" t="n">
-        <v>0.9111680087976479</v>
+        <v>0.9111680087976476</v>
       </c>
       <c r="BJ201" s="190" t="n">
         <v>1.272513083273079</v>
       </c>
       <c r="BK201" s="198" t="n">
-        <v>1.718122098466134</v>
+        <v>1.718122098466135</v>
       </c>
       <c r="BL201" s="197" t="n">
         <v>135.6301634472134</v>
@@ -41519,7 +41519,7 @@
         <v>176.2211623986014</v>
       </c>
       <c r="BN201" s="190" t="n">
-        <v>184.3847722292096</v>
+        <v>184.3847722292095</v>
       </c>
       <c r="BO201" s="190" t="n">
         <v>198.7095670838888</v>
@@ -41542,22 +41542,22 @@
         <v>50.4514222620171</v>
       </c>
       <c r="BV201" s="336" t="n">
-        <v>55.51399834326029</v>
+        <v>55.5139983432603</v>
       </c>
       <c r="BW201" s="337" t="n">
         <v>55.46093120356361</v>
       </c>
       <c r="BX201" s="462" t="n">
-        <v>0.6230057723229329</v>
+        <v>0.6230057723229331</v>
       </c>
       <c r="BY201" s="463" t="n">
         <v>0.2643552064417088</v>
       </c>
       <c r="BZ201" s="463" t="n">
-        <v>0.2746831764536095</v>
+        <v>0.2746831764536097</v>
       </c>
       <c r="CA201" s="463" t="n">
-        <v>0.2809008726189627</v>
+        <v>0.2809008726189628</v>
       </c>
       <c r="CB201" s="464" t="n">
         <v>0.2541075763233427</v>
@@ -41569,13 +41569,13 @@
         <v>46.56496316027231</v>
       </c>
       <c r="CE201" s="190" t="n">
-        <v>50.62672521257551</v>
+        <v>50.62672521257552</v>
       </c>
       <c r="CF201" s="190" t="n">
-        <v>55.79655618299955</v>
+        <v>55.79655618299956</v>
       </c>
       <c r="CG201" s="198" t="n">
-        <v>55.82322507873542</v>
+        <v>55.82322507873543</v>
       </c>
       <c r="CI201" s="422" t="n">
         <v>1</v>
@@ -41608,25 +41608,25 @@
         <v>1.000000046583507</v>
       </c>
       <c r="CT201" s="422" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU201" s="423" t="n">
         <v>0.9999999999999999</v>
-      </c>
-      <c r="CU201" s="423" t="n">
-        <v>1</v>
       </c>
       <c r="CV201" s="423" t="n">
         <v>1</v>
       </c>
       <c r="CW201" s="423" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="CX201" s="424" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="CY201" s="422" t="n">
         <v>1.000000000647269</v>
       </c>
       <c r="CZ201" s="423" t="n">
-        <v>0.9999999951520931</v>
+        <v>0.999999995152093</v>
       </c>
       <c r="DA201" s="423" t="n">
         <v>1.00000001225765</v>
@@ -41775,19 +41775,19 @@
         <v>0</v>
       </c>
       <c r="AU202" s="209" t="n">
-        <v>8.638281980360059</v>
+        <v>8.638281980360063</v>
       </c>
       <c r="AV202" s="209" t="n">
-        <v>7.57157414661857</v>
+        <v>7.571574146618563</v>
       </c>
       <c r="AW202" s="209" t="n">
         <v>7.711289693800254</v>
       </c>
       <c r="AX202" s="209" t="n">
-        <v>7.910092821495514</v>
+        <v>7.910092821495521</v>
       </c>
       <c r="AY202" s="210" t="n">
-        <v>8.142790620811347</v>
+        <v>8.142790620811343</v>
       </c>
       <c r="BA202" s="111" t="inlineStr">
         <is>
@@ -41825,19 +41825,19 @@
         <v>0</v>
       </c>
       <c r="BL202" s="212" t="n">
-        <v>8.638281980360059</v>
+        <v>8.638281980360063</v>
       </c>
       <c r="BM202" s="212" t="n">
-        <v>7.57157414661857</v>
+        <v>7.571574146618563</v>
       </c>
       <c r="BN202" s="212" t="n">
         <v>7.711289693800254</v>
       </c>
       <c r="BO202" s="212" t="n">
-        <v>7.910092821495514</v>
+        <v>7.910092821495521</v>
       </c>
       <c r="BP202" s="213" t="n">
-        <v>8.142790620811347</v>
+        <v>8.142790620811343</v>
       </c>
       <c r="BR202" s="111" t="inlineStr">
         <is>
@@ -41860,19 +41860,19 @@
         <v>2.388846221863131</v>
       </c>
       <c r="BX202" s="466" t="n">
-        <v>0.2507529389389401</v>
+        <v>0.25075293893894</v>
       </c>
       <c r="BY202" s="467" t="n">
-        <v>0.2935483288405811</v>
+        <v>0.2935483288405814</v>
       </c>
       <c r="BZ202" s="467" t="n">
         <v>0.2969919734392065</v>
       </c>
       <c r="CA202" s="467" t="n">
-        <v>0.2953979877107901</v>
+        <v>0.2953979877107897</v>
       </c>
       <c r="CB202" s="468" t="n">
-        <v>0.2927736170138278</v>
+        <v>0.292773617013828</v>
       </c>
       <c r="CC202" s="212" t="n">
         <v>2.164511354735448</v>
@@ -42022,28 +42022,28 @@
         <v>0.018</v>
       </c>
       <c r="AP203" s="206" t="n">
-        <v>2.503424436626774</v>
+        <v>2.503424436626775</v>
       </c>
       <c r="AQ203" s="207" t="n">
-        <v>7.213039606631848</v>
+        <v>7.213039606631852</v>
       </c>
       <c r="AR203" s="207" t="n">
         <v>11.28042548095577</v>
       </c>
       <c r="AS203" s="207" t="n">
-        <v>16.45793616370192</v>
+        <v>16.45793616370193</v>
       </c>
       <c r="AT203" s="208" t="n">
         <v>23.15107704018713</v>
       </c>
       <c r="AU203" s="207" t="n">
-        <v>1203.393060897687</v>
+        <v>1203.393060897688</v>
       </c>
       <c r="AV203" s="207" t="n">
-        <v>2286.484107564192</v>
+        <v>2286.484107564193</v>
       </c>
       <c r="AW203" s="207" t="n">
-        <v>2629.170715726433</v>
+        <v>2629.170715726432</v>
       </c>
       <c r="AX203" s="207" t="n">
         <v>3069.789202430991</v>
@@ -42072,25 +42072,25 @@
         <v>0.018</v>
       </c>
       <c r="BG203" s="221" t="n">
-        <v>2.503424436627401</v>
+        <v>2.503424436627402</v>
       </c>
       <c r="BH203" s="222" t="n">
-        <v>7.213039606631822</v>
+        <v>7.213039606631826</v>
       </c>
       <c r="BI203" s="222" t="n">
-        <v>11.28042548095471</v>
+        <v>11.2804254809547</v>
       </c>
       <c r="BJ203" s="222" t="n">
         <v>16.45793616370397</v>
       </c>
       <c r="BK203" s="214" t="n">
-        <v>23.15107704018928</v>
+        <v>23.15107704018929</v>
       </c>
       <c r="BL203" s="222" t="n">
         <v>1203.393060897688</v>
       </c>
       <c r="BM203" s="222" t="n">
-        <v>2286.484107564191</v>
+        <v>2286.484107564193</v>
       </c>
       <c r="BN203" s="222" t="n">
         <v>2629.170715726431</v>
@@ -42099,7 +42099,7 @@
         <v>3069.789202430993</v>
       </c>
       <c r="BP203" s="214" t="n">
-        <v>3613.156016984547</v>
+        <v>3613.156016984548</v>
       </c>
       <c r="BR203" s="155" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
         </is>
       </c>
       <c r="BS203" s="271" t="n">
-        <v>893.0380461265414</v>
+        <v>893.0380461265413</v>
       </c>
       <c r="BT203" s="272" t="n">
         <v>121.1337260431404</v>
@@ -42122,22 +42122,22 @@
         <v>123.1276364700726</v>
       </c>
       <c r="BX203" s="466" t="n">
-        <v>0.7420986437243582</v>
+        <v>0.7420986437243579</v>
       </c>
       <c r="BY203" s="467" t="n">
-        <v>0.05285345344870865</v>
+        <v>0.05285345344870863</v>
       </c>
       <c r="BZ203" s="467" t="n">
-        <v>0.04781252069541411</v>
+        <v>0.04781252069541413</v>
       </c>
       <c r="CA203" s="467" t="n">
-        <v>0.04173121269132504</v>
+        <v>0.04173121269132502</v>
       </c>
       <c r="CB203" s="468" t="n">
-        <v>0.0341371604304341</v>
+        <v>0.03413716043043411</v>
       </c>
       <c r="CC203" s="212" t="n">
-        <v>887.7165358611178</v>
+        <v>887.7165358611177</v>
       </c>
       <c r="CD203" s="212" t="n">
         <v>120.8104672541025</v>
@@ -42149,7 +42149,7 @@
         <v>128.0761158842507</v>
       </c>
       <c r="CG203" s="213" t="n">
-        <v>123.3192560686691</v>
+        <v>123.3192560686692</v>
       </c>
       <c r="CW203" s="465" t="n"/>
       <c r="CX203" s="465" t="n"/>
@@ -42937,34 +42937,34 @@
         <v>108.8380665390008</v>
       </c>
       <c r="AP208" s="473" t="n">
-        <v>0.01714643719536978</v>
+        <v>0.01714643719536977</v>
       </c>
       <c r="AQ208" s="463" t="n">
-        <v>0.02757291526517473</v>
+        <v>0.02757291526517471</v>
       </c>
       <c r="AR208" s="463" t="n">
         <v>0.04166037859686424</v>
       </c>
       <c r="AS208" s="463" t="n">
-        <v>0.04139589952837092</v>
+        <v>0.04139589952837091</v>
       </c>
       <c r="AT208" s="474" t="n">
         <v>0.03921032283605078</v>
       </c>
       <c r="AU208" s="463" t="n">
-        <v>0.01514643719509404</v>
+        <v>0.01514643719509403</v>
       </c>
       <c r="AV208" s="463" t="n">
-        <v>0.02457291526493196</v>
+        <v>0.02457291526493194</v>
       </c>
       <c r="AW208" s="463" t="n">
-        <v>0.03766037859689552</v>
+        <v>0.03766037859689553</v>
       </c>
       <c r="AX208" s="463" t="n">
-        <v>0.0363958995283718</v>
+        <v>0.03639589952837179</v>
       </c>
       <c r="AY208" s="474" t="n">
-        <v>0.033210322836186</v>
+        <v>0.03321032283618599</v>
       </c>
       <c r="BA208" s="83" t="inlineStr">
         <is>
@@ -42987,31 +42987,31 @@
         <v>108.838066539</v>
       </c>
       <c r="BG208" s="462" t="n">
-        <v>0.01714643719509876</v>
+        <v>0.01714643719509875</v>
       </c>
       <c r="BH208" s="463" t="n">
-        <v>0.02757291526493865</v>
+        <v>0.02757291526493864</v>
       </c>
       <c r="BI208" s="463" t="n">
-        <v>0.04166037859689422</v>
+        <v>0.04166037859689423</v>
       </c>
       <c r="BJ208" s="463" t="n">
-        <v>0.04139589952837176</v>
+        <v>0.04139589952837175</v>
       </c>
       <c r="BK208" s="464" t="n">
         <v>0.03921032283618069</v>
       </c>
       <c r="BL208" s="475" t="n">
-        <v>0.01514643719562742</v>
+        <v>0.01514643719562741</v>
       </c>
       <c r="BM208" s="476" t="n">
-        <v>0.02457291526501374</v>
+        <v>0.02457291526501373</v>
       </c>
       <c r="BN208" s="476" t="n">
         <v>0.03766037859691106</v>
       </c>
       <c r="BO208" s="476" t="n">
-        <v>0.03639589952843713</v>
+        <v>0.03639589952843712</v>
       </c>
       <c r="BP208" s="477" t="n">
         <v>0.03321032283618126</v>
@@ -43037,13 +43037,13 @@
         <v>0</v>
       </c>
       <c r="BX208" s="462" t="n">
-        <v>0.01525386749851554</v>
+        <v>0.01525386749851553</v>
       </c>
       <c r="BY208" s="463" t="n">
-        <v>0.02457986237464999</v>
+        <v>0.02457986237464997</v>
       </c>
       <c r="BZ208" s="463" t="n">
-        <v>0.03766930330901427</v>
+        <v>0.03766930330901428</v>
       </c>
       <c r="CA208" s="463" t="n">
         <v>0.03640312575861535</v>
@@ -43192,16 +43192,16 @@
         <v>78.06602822927782</v>
       </c>
       <c r="AP209" s="473" t="n">
-        <v>0.1523289916150373</v>
+        <v>0.1523289916150374</v>
       </c>
       <c r="AQ209" s="463" t="n">
         <v>0.2203025241913979</v>
       </c>
       <c r="AR209" s="463" t="n">
-        <v>0.2764803793923835</v>
+        <v>0.2764803793923836</v>
       </c>
       <c r="AS209" s="463" t="n">
-        <v>0.2778840630926173</v>
+        <v>0.2778840630926172</v>
       </c>
       <c r="AT209" s="474" t="n">
         <v>0.2706995805829056</v>
@@ -43213,13 +43213,13 @@
         <v>0.2173025241925611</v>
       </c>
       <c r="AW209" s="463" t="n">
-        <v>0.2724803793909766</v>
+        <v>0.2724803793909767</v>
       </c>
       <c r="AX209" s="463" t="n">
-        <v>0.2728840630925904</v>
+        <v>0.2728840630925903</v>
       </c>
       <c r="AY209" s="474" t="n">
-        <v>0.2646995805824044</v>
+        <v>0.2646995805824045</v>
       </c>
       <c r="BA209" s="101" t="inlineStr">
         <is>
@@ -43248,10 +43248,10 @@
         <v>0.2203025241923049</v>
       </c>
       <c r="BI209" s="463" t="n">
-        <v>0.2764803793913656</v>
+        <v>0.2764803793913657</v>
       </c>
       <c r="BJ209" s="463" t="n">
-        <v>0.2778840630925979</v>
+        <v>0.2778840630925978</v>
       </c>
       <c r="BK209" s="464" t="n">
         <v>0.2706995805825401</v>
@@ -43263,13 +43263,13 @@
         <v>0.2173025241916721</v>
       </c>
       <c r="BN209" s="463" t="n">
-        <v>0.2724803793918447</v>
+        <v>0.2724803793918448</v>
       </c>
       <c r="BO209" s="463" t="n">
-        <v>0.2728840630935302</v>
+        <v>0.2728840630935301</v>
       </c>
       <c r="BP209" s="464" t="n">
-        <v>0.2646995805815951</v>
+        <v>0.2646995805815952</v>
       </c>
       <c r="BR209" s="101" t="inlineStr">
         <is>
@@ -43298,13 +43298,13 @@
         <v>0.2173805498142089</v>
       </c>
       <c r="BZ209" s="463" t="n">
-        <v>0.2725723608972215</v>
+        <v>0.2725723608972216</v>
       </c>
       <c r="CA209" s="463" t="n">
-        <v>0.2729707353288184</v>
+        <v>0.2729707353288183</v>
       </c>
       <c r="CB209" s="464" t="n">
-        <v>0.2647661096603218</v>
+        <v>0.2647661096603219</v>
       </c>
       <c r="CC209" s="482" t="n">
         <v>0</v>
@@ -43447,13 +43447,13 @@
         <v>66.59551889953424</v>
       </c>
       <c r="AP210" s="473" t="n">
-        <v>0.1089463898403425</v>
+        <v>0.1089463898403426</v>
       </c>
       <c r="AQ210" s="463" t="n">
         <v>0.1400788597574751</v>
       </c>
       <c r="AR210" s="463" t="n">
-        <v>0.1945564267010485</v>
+        <v>0.1945564267010486</v>
       </c>
       <c r="AS210" s="463" t="n">
         <v>0.224223874016677</v>
@@ -43474,7 +43474,7 @@
         <v>0.2192238740183018</v>
       </c>
       <c r="AY210" s="474" t="n">
-        <v>0.2325638636241365</v>
+        <v>0.2325638636241364</v>
       </c>
       <c r="BA210" s="111" t="inlineStr">
         <is>
@@ -43503,22 +43503,22 @@
         <v>0.1400788597583547</v>
       </c>
       <c r="BI210" s="463" t="n">
-        <v>0.1945564267010705</v>
+        <v>0.1945564267010706</v>
       </c>
       <c r="BJ210" s="463" t="n">
         <v>0.2242238740179375</v>
       </c>
       <c r="BK210" s="464" t="n">
-        <v>0.2385638636240841</v>
+        <v>0.238563863624084</v>
       </c>
       <c r="BL210" s="462" t="n">
-        <v>0.1069463898438242</v>
+        <v>0.1069463898438243</v>
       </c>
       <c r="BM210" s="463" t="n">
         <v>0.1370788597565229</v>
       </c>
       <c r="BN210" s="463" t="n">
-        <v>0.1905564267001822</v>
+        <v>0.1905564267001823</v>
       </c>
       <c r="BO210" s="463" t="n">
         <v>0.2192238740190105</v>
@@ -43547,19 +43547,19 @@
         <v>0</v>
       </c>
       <c r="BX210" s="462" t="n">
-        <v>0.1071326894396072</v>
+        <v>0.1071326894396073</v>
       </c>
       <c r="BY210" s="463" t="n">
         <v>0.1371297097086172</v>
       </c>
       <c r="BZ210" s="463" t="n">
-        <v>0.1906193963103959</v>
+        <v>0.190619396310396</v>
       </c>
       <c r="CA210" s="463" t="n">
         <v>0.219288702392468</v>
       </c>
       <c r="CB210" s="464" t="n">
-        <v>0.2326245716906366</v>
+        <v>0.2326245716906365</v>
       </c>
       <c r="CC210" s="482" t="n">
         <v>0</v>
@@ -43942,10 +43942,10 @@
         </is>
       </c>
       <c r="AK212" s="206" t="n">
-        <v>56.95743939637323</v>
+        <v>56.95743939637322</v>
       </c>
       <c r="AL212" s="207" t="n">
-        <v>125.4340021263682</v>
+        <v>125.4340021263681</v>
       </c>
       <c r="AM212" s="207" t="n">
         <v>198.6469442060442</v>
@@ -43957,34 +43957,34 @@
         <v>253.4996136678129</v>
       </c>
       <c r="AP212" s="500" t="n">
-        <v>0.04717803802921615</v>
+        <v>0.04717803802921614</v>
       </c>
       <c r="AQ212" s="501" t="n">
-        <v>0.05499649478149889</v>
+        <v>0.05499649478149887</v>
       </c>
       <c r="AR212" s="501" t="n">
-        <v>0.07423652969618733</v>
+        <v>0.07423652969618734</v>
       </c>
       <c r="AS212" s="501" t="n">
-        <v>0.07460714012037568</v>
+        <v>0.07460714012037567</v>
       </c>
       <c r="AT212" s="502" t="n">
-        <v>0.07154779663203438</v>
+        <v>0.07154779663203439</v>
       </c>
       <c r="AU212" s="501" t="n">
-        <v>0.04519174577476526</v>
+        <v>0.04519174577476524</v>
       </c>
       <c r="AV212" s="501" t="n">
-        <v>0.05200591248202056</v>
+        <v>0.05200591248202054</v>
       </c>
       <c r="AW212" s="501" t="n">
-        <v>0.07024743745704201</v>
+        <v>0.07024743745704203</v>
       </c>
       <c r="AX212" s="501" t="n">
-        <v>0.0696191269353978</v>
+        <v>0.06961912693539778</v>
       </c>
       <c r="AY212" s="502" t="n">
-        <v>0.06556043203285405</v>
+        <v>0.06556043203285404</v>
       </c>
       <c r="BA212" s="155" t="inlineStr">
         <is>
@@ -44007,31 +44007,31 @@
         <v>253.499613668</v>
       </c>
       <c r="BG212" s="503" t="n">
-        <v>0.04717803802920442</v>
+        <v>0.04717803802920441</v>
       </c>
       <c r="BH212" s="504" t="n">
-        <v>0.05499649478149909</v>
+        <v>0.05499649478149907</v>
       </c>
       <c r="BI212" s="504" t="n">
-        <v>0.07423652969619431</v>
+        <v>0.07423652969619432</v>
       </c>
       <c r="BJ212" s="504" t="n">
-        <v>0.07460714012036644</v>
+        <v>0.07460714012036643</v>
       </c>
       <c r="BK212" s="505" t="n">
-        <v>0.07154779663202775</v>
+        <v>0.07154779663202776</v>
       </c>
       <c r="BL212" s="504" t="n">
-        <v>0.04519174577525133</v>
+        <v>0.04519174577525131</v>
       </c>
       <c r="BM212" s="504" t="n">
-        <v>0.05200591248186811</v>
+        <v>0.05200591248186809</v>
       </c>
       <c r="BN212" s="504" t="n">
-        <v>0.07024743745703296</v>
+        <v>0.07024743745703299</v>
       </c>
       <c r="BO212" s="504" t="n">
-        <v>0.06961912693560192</v>
+        <v>0.06961912693560189</v>
       </c>
       <c r="BP212" s="505" t="n">
         <v>0.06556043203289637</v>
@@ -44057,13 +44057,13 @@
         <v>0</v>
       </c>
       <c r="BX212" s="503" t="n">
-        <v>0.04545025766084106</v>
+        <v>0.04545025766084105</v>
       </c>
       <c r="BY212" s="504" t="n">
-        <v>0.05202146612652389</v>
+        <v>0.05202146612652386</v>
       </c>
       <c r="BZ212" s="504" t="n">
-        <v>0.07026534493523189</v>
+        <v>0.0702653449352319</v>
       </c>
       <c r="CA212" s="504" t="n">
         <v>0.06963425328170651</v>
@@ -44737,13 +44737,13 @@
         <v>34513.22235879839</v>
       </c>
       <c r="AM219" s="368" t="n">
-        <v>62356.24033128741</v>
+        <v>62356.2403312874</v>
       </c>
       <c r="AN219" s="368" t="n">
-        <v>77145.27984093783</v>
+        <v>77145.27984093782</v>
       </c>
       <c r="AO219" s="380" t="n">
-        <v>89580.48173789638</v>
+        <v>89580.48173789636</v>
       </c>
       <c r="AP219" s="381" t="n">
         <v>588.3746268688296</v>
@@ -44752,13 +44752,13 @@
         <v>633.7546894283593</v>
       </c>
       <c r="AR219" s="372" t="n">
-        <v>637.7485705640689</v>
+        <v>637.7485705640688</v>
       </c>
       <c r="AS219" s="372" t="n">
-        <v>672.9999385701531</v>
+        <v>672.9999385701529</v>
       </c>
       <c r="AT219" s="382" t="n">
-        <v>697.1163277335223</v>
+        <v>697.1163277335222</v>
       </c>
       <c r="BA219" s="83" t="inlineStr">
         <is>
@@ -44772,13 +44772,13 @@
         <v>34513.22235879839</v>
       </c>
       <c r="BD219" s="375" t="n">
-        <v>62356.24033128741</v>
+        <v>62356.2403312874</v>
       </c>
       <c r="BE219" s="375" t="n">
-        <v>77145.27984093783</v>
+        <v>77145.27984093782</v>
       </c>
       <c r="BF219" s="392" t="n">
-        <v>89580.48173789638</v>
+        <v>89580.48173789636</v>
       </c>
       <c r="BG219" s="386" t="n">
         <v>588.3746268688296</v>
@@ -44787,13 +44787,13 @@
         <v>633.7546894283593</v>
       </c>
       <c r="BI219" s="372" t="n">
-        <v>637.7485705640689</v>
+        <v>637.7485705640688</v>
       </c>
       <c r="BJ219" s="372" t="n">
-        <v>672.9999385701531</v>
+        <v>672.9999385701529</v>
       </c>
       <c r="BK219" s="387" t="n">
-        <v>697.1163277335223</v>
+        <v>697.1163277335222</v>
       </c>
       <c r="BR219" s="83" t="inlineStr">
         <is>
@@ -44813,7 +44813,7 @@
         <v>67827.29415650357</v>
       </c>
       <c r="BW219" s="392" t="n">
-        <v>75872.79326328443</v>
+        <v>75872.79326328442</v>
       </c>
       <c r="BX219" s="386" t="n">
         <v>588.3746268688296</v>
@@ -44822,13 +44822,13 @@
         <v>633.7546894283593</v>
       </c>
       <c r="BZ219" s="372" t="n">
-        <v>637.7485705640689</v>
+        <v>637.7485705640688</v>
       </c>
       <c r="CA219" s="372" t="n">
-        <v>672.9999385701531</v>
+        <v>672.9999385701529</v>
       </c>
       <c r="CB219" s="387" t="n">
-        <v>697.1163277335223</v>
+        <v>697.1163277335222</v>
       </c>
       <c r="CI219" s="199" t="n">
         <v>0</v>
@@ -44926,7 +44926,7 @@
         </is>
       </c>
       <c r="AK220" s="506" t="n">
-        <v>44335.44858341061</v>
+        <v>44335.44858341062</v>
       </c>
       <c r="AL220" s="368" t="n">
         <v>90066.83119143534</v>
@@ -44941,7 +44941,7 @@
         <v>159406.5384542814</v>
       </c>
       <c r="AP220" s="381" t="n">
-        <v>1635.517697827482</v>
+        <v>1635.517697827483</v>
       </c>
       <c r="AQ220" s="372" t="n">
         <v>1816.502530212065</v>
@@ -44961,7 +44961,7 @@
         </is>
       </c>
       <c r="BB220" s="391" t="n">
-        <v>44335.44858341061</v>
+        <v>44335.44858341062</v>
       </c>
       <c r="BC220" s="375" t="n">
         <v>90066.83119143534</v>
@@ -44976,7 +44976,7 @@
         <v>159406.5384542814</v>
       </c>
       <c r="BG220" s="386" t="n">
-        <v>1635.517697827482</v>
+        <v>1635.517697827483</v>
       </c>
       <c r="BH220" s="372" t="n">
         <v>1816.502530212065</v>
@@ -45011,7 +45011,7 @@
         <v>155873.3256254396</v>
       </c>
       <c r="BX220" s="386" t="n">
-        <v>1635.517697827482</v>
+        <v>1635.517697827483</v>
       </c>
       <c r="BY220" s="372" t="n">
         <v>1816.502530212065</v>
@@ -45127,7 +45127,7 @@
         <v>49819.67164514307</v>
       </c>
       <c r="AM221" s="368" t="n">
-        <v>74511.52994761145</v>
+        <v>74511.52994761142</v>
       </c>
       <c r="AN221" s="368" t="n">
         <v>88747.26377651544</v>
@@ -45142,7 +45142,7 @@
         <v>1741.571503487291</v>
       </c>
       <c r="AR221" s="372" t="n">
-        <v>1681.277603556841</v>
+        <v>1681.27760355684</v>
       </c>
       <c r="AS221" s="372" t="n">
         <v>1555.180736841376</v>
@@ -45162,7 +45162,7 @@
         <v>49819.67164514307</v>
       </c>
       <c r="BD221" s="375" t="n">
-        <v>74511.52994761145</v>
+        <v>74511.52994761142</v>
       </c>
       <c r="BE221" s="375" t="n">
         <v>88747.26377651544</v>
@@ -45177,7 +45177,7 @@
         <v>1741.571503487291</v>
       </c>
       <c r="BI221" s="372" t="n">
-        <v>1681.277603556841</v>
+        <v>1681.27760355684</v>
       </c>
       <c r="BJ221" s="372" t="n">
         <v>1555.180736841376</v>
@@ -45191,13 +45191,13 @@
         </is>
       </c>
       <c r="BS221" s="391" t="n">
-        <v>26660.49838036938</v>
+        <v>26660.49838036939</v>
       </c>
       <c r="BT221" s="375" t="n">
         <v>48752.70825548875</v>
       </c>
       <c r="BU221" s="375" t="n">
-        <v>72979.60358100226</v>
+        <v>72979.60358100223</v>
       </c>
       <c r="BV221" s="375" t="n">
         <v>86768.27594245521</v>
@@ -45212,7 +45212,7 @@
         <v>1741.571503487291</v>
       </c>
       <c r="BZ221" s="372" t="n">
-        <v>1681.277603556841</v>
+        <v>1681.27760355684</v>
       </c>
       <c r="CA221" s="372" t="n">
         <v>1555.180736841376</v>
@@ -45511,7 +45511,7 @@
         </is>
       </c>
       <c r="AK223" s="435" t="n">
-        <v>80794.97273624105</v>
+        <v>80794.97273624106</v>
       </c>
       <c r="AL223" s="408" t="n">
         <v>174399.7251953768</v>
@@ -45546,7 +45546,7 @@
         </is>
       </c>
       <c r="BB223" s="439" t="n">
-        <v>80794.97273624105</v>
+        <v>80794.97273624106</v>
       </c>
       <c r="BC223" s="440" t="n">
         <v>174399.7251953768</v>
@@ -45587,7 +45587,7 @@
         <v>168351.1420820874</v>
       </c>
       <c r="BU223" s="440" t="n">
-        <v>256117.3214787376</v>
+        <v>256117.3214787375</v>
       </c>
       <c r="BV223" s="440" t="n">
         <v>296783.1090992133</v>
@@ -47635,13 +47635,13 @@
         <v>34513.22235879839</v>
       </c>
       <c r="AM237" s="368" t="n">
-        <v>62356.24033128741</v>
+        <v>62356.2403312874</v>
       </c>
       <c r="AN237" s="368" t="n">
-        <v>77145.27984093783</v>
+        <v>77145.27984093782</v>
       </c>
       <c r="AO237" s="380" t="n">
-        <v>89580.48173789638</v>
+        <v>89580.48173789636</v>
       </c>
       <c r="AP237" s="381" t="n">
         <v>588.3746268688296</v>
@@ -47650,13 +47650,13 @@
         <v>633.7546894283593</v>
       </c>
       <c r="AR237" s="372" t="n">
-        <v>637.7485705640689</v>
+        <v>637.7485705640688</v>
       </c>
       <c r="AS237" s="372" t="n">
-        <v>672.9999385701531</v>
+        <v>672.9999385701529</v>
       </c>
       <c r="AT237" s="382" t="n">
-        <v>697.1163277335223</v>
+        <v>697.1163277335222</v>
       </c>
       <c r="BA237" s="83" t="inlineStr">
         <is>
@@ -47670,13 +47670,13 @@
         <v>34513.22235879839</v>
       </c>
       <c r="BD237" s="375" t="n">
-        <v>62356.24033128741</v>
+        <v>62356.2403312874</v>
       </c>
       <c r="BE237" s="375" t="n">
-        <v>77145.27984093783</v>
+        <v>77145.27984093782</v>
       </c>
       <c r="BF237" s="392" t="n">
-        <v>89580.48173789638</v>
+        <v>89580.48173789636</v>
       </c>
       <c r="BG237" s="386" t="n">
         <v>588.3746268688296</v>
@@ -47685,13 +47685,13 @@
         <v>633.7546894283593</v>
       </c>
       <c r="BI237" s="372" t="n">
-        <v>637.7485705640689</v>
+        <v>637.7485705640688</v>
       </c>
       <c r="BJ237" s="372" t="n">
-        <v>672.9999385701531</v>
+        <v>672.9999385701529</v>
       </c>
       <c r="BK237" s="387" t="n">
-        <v>697.1163277335223</v>
+        <v>697.1163277335222</v>
       </c>
       <c r="BR237" s="83" t="inlineStr">
         <is>
@@ -47711,7 +47711,7 @@
         <v>67827.29415650357</v>
       </c>
       <c r="BW237" s="392" t="n">
-        <v>75872.79326328443</v>
+        <v>75872.79326328442</v>
       </c>
       <c r="BX237" s="386" t="n">
         <v>588.3746268688296</v>
@@ -47720,13 +47720,13 @@
         <v>633.7546894283593</v>
       </c>
       <c r="BZ237" s="372" t="n">
-        <v>637.7485705640689</v>
+        <v>637.7485705640688</v>
       </c>
       <c r="CA237" s="372" t="n">
-        <v>672.9999385701531</v>
+        <v>672.9999385701529</v>
       </c>
       <c r="CB237" s="387" t="n">
-        <v>697.1163277335223</v>
+        <v>697.1163277335222</v>
       </c>
       <c r="CI237" s="199" t="n">
         <v>0</v>
@@ -47824,7 +47824,7 @@
         </is>
       </c>
       <c r="AK238" s="506" t="n">
-        <v>44335.44858341061</v>
+        <v>44335.44858341062</v>
       </c>
       <c r="AL238" s="368" t="n">
         <v>90066.83119143534</v>
@@ -47839,7 +47839,7 @@
         <v>159406.5384542814</v>
       </c>
       <c r="AP238" s="381" t="n">
-        <v>1635.517697827482</v>
+        <v>1635.517697827483</v>
       </c>
       <c r="AQ238" s="372" t="n">
         <v>1816.502530212065</v>
@@ -47859,7 +47859,7 @@
         </is>
       </c>
       <c r="BB238" s="391" t="n">
-        <v>44335.44858341061</v>
+        <v>44335.44858341062</v>
       </c>
       <c r="BC238" s="375" t="n">
         <v>90066.83119143534</v>
@@ -47874,7 +47874,7 @@
         <v>159406.5384542814</v>
       </c>
       <c r="BG238" s="386" t="n">
-        <v>1635.517697827482</v>
+        <v>1635.517697827483</v>
       </c>
       <c r="BH238" s="372" t="n">
         <v>1816.502530212065</v>
@@ -47909,7 +47909,7 @@
         <v>155873.3256254396</v>
       </c>
       <c r="BX238" s="386" t="n">
-        <v>1635.517697827482</v>
+        <v>1635.517697827483</v>
       </c>
       <c r="BY238" s="372" t="n">
         <v>1816.502530212065</v>
@@ -48025,7 +48025,7 @@
         <v>49819.67164514307</v>
       </c>
       <c r="AM239" s="368" t="n">
-        <v>74511.52994761145</v>
+        <v>74511.52994761142</v>
       </c>
       <c r="AN239" s="368" t="n">
         <v>88747.26377651544</v>
@@ -48040,7 +48040,7 @@
         <v>1741.571503487291</v>
       </c>
       <c r="AR239" s="372" t="n">
-        <v>1681.277603556841</v>
+        <v>1681.27760355684</v>
       </c>
       <c r="AS239" s="372" t="n">
         <v>1555.180736841376</v>
@@ -48060,7 +48060,7 @@
         <v>49819.67164514307</v>
       </c>
       <c r="BD239" s="375" t="n">
-        <v>74511.52994761145</v>
+        <v>74511.52994761142</v>
       </c>
       <c r="BE239" s="375" t="n">
         <v>88747.26377651544</v>
@@ -48075,7 +48075,7 @@
         <v>1741.571503487291</v>
       </c>
       <c r="BI239" s="372" t="n">
-        <v>1681.277603556841</v>
+        <v>1681.27760355684</v>
       </c>
       <c r="BJ239" s="372" t="n">
         <v>1555.180736841376</v>
@@ -48089,13 +48089,13 @@
         </is>
       </c>
       <c r="BS239" s="391" t="n">
-        <v>26660.49838036938</v>
+        <v>26660.49838036939</v>
       </c>
       <c r="BT239" s="375" t="n">
         <v>48752.70825548875</v>
       </c>
       <c r="BU239" s="375" t="n">
-        <v>72979.60358100226</v>
+        <v>72979.60358100223</v>
       </c>
       <c r="BV239" s="375" t="n">
         <v>86768.27594245521</v>
@@ -48110,7 +48110,7 @@
         <v>1741.571503487291</v>
       </c>
       <c r="BZ239" s="372" t="n">
-        <v>1681.277603556841</v>
+        <v>1681.27760355684</v>
       </c>
       <c r="CA239" s="372" t="n">
         <v>1555.180736841376</v>
@@ -48409,7 +48409,7 @@
         </is>
       </c>
       <c r="AK241" s="435" t="n">
-        <v>80794.97273624105</v>
+        <v>80794.97273624106</v>
       </c>
       <c r="AL241" s="408" t="n">
         <v>174399.7251953768</v>
@@ -48444,7 +48444,7 @@
         </is>
       </c>
       <c r="BB241" s="439" t="n">
-        <v>80794.97273624105</v>
+        <v>80794.97273624106</v>
       </c>
       <c r="BC241" s="440" t="n">
         <v>174399.7251953768</v>
@@ -48485,7 +48485,7 @@
         <v>168351.1420820874</v>
       </c>
       <c r="BU241" s="440" t="n">
-        <v>256117.3214787376</v>
+        <v>256117.3214787375</v>
       </c>
       <c r="BV241" s="440" t="n">
         <v>296783.1090992133</v>
@@ -49039,31 +49039,31 @@
         <v>1088657.416548779</v>
       </c>
       <c r="AL246" s="368" t="n">
-        <v>2466821.589989233</v>
+        <v>2466821.589989234</v>
       </c>
       <c r="AM246" s="368" t="n">
-        <v>2936880.353989949</v>
+        <v>2936880.35398995</v>
       </c>
       <c r="AN246" s="368" t="n">
         <v>3491319.569659749</v>
       </c>
       <c r="AO246" s="380" t="n">
-        <v>4163875.479483539</v>
+        <v>4163875.479483536</v>
       </c>
       <c r="AP246" s="381" t="n">
         <v>1201.507088575056</v>
       </c>
       <c r="AQ246" s="372" t="n">
-        <v>1284.396332331876</v>
+        <v>1284.396332331877</v>
       </c>
       <c r="AR246" s="372" t="n">
-        <v>1305.748676164889</v>
+        <v>1305.74867616489</v>
       </c>
       <c r="AS246" s="372" t="n">
         <v>1315.265142248685</v>
       </c>
       <c r="AT246" s="382" t="n">
-        <v>1322.396479618798</v>
+        <v>1322.396479618797</v>
       </c>
       <c r="BA246" s="83" t="inlineStr">
         <is>
@@ -49074,31 +49074,31 @@
         <v>1088657.416548779</v>
       </c>
       <c r="BC246" s="375" t="n">
-        <v>2466821.589989233</v>
+        <v>2466821.589989234</v>
       </c>
       <c r="BD246" s="375" t="n">
-        <v>2936880.353989949</v>
+        <v>2936880.35398995</v>
       </c>
       <c r="BE246" s="375" t="n">
         <v>3491319.569659749</v>
       </c>
       <c r="BF246" s="392" t="n">
-        <v>4163875.479483539</v>
+        <v>4163875.479483536</v>
       </c>
       <c r="BG246" s="386" t="n">
         <v>1201.507088575056</v>
       </c>
       <c r="BH246" s="372" t="n">
-        <v>1284.396332331876</v>
+        <v>1284.396332331877</v>
       </c>
       <c r="BI246" s="372" t="n">
-        <v>1305.748676164889</v>
+        <v>1305.74867616489</v>
       </c>
       <c r="BJ246" s="372" t="n">
         <v>1315.265142248685</v>
       </c>
       <c r="BK246" s="387" t="n">
-        <v>1322.396479618798</v>
+        <v>1322.396479618797</v>
       </c>
       <c r="BR246" s="83" t="inlineStr">
         <is>
@@ -49109,31 +49109,31 @@
         <v>1083071.734338342</v>
       </c>
       <c r="BT246" s="375" t="n">
-        <v>2473714.915708589</v>
+        <v>2473714.91570859</v>
       </c>
       <c r="BU246" s="375" t="n">
-        <v>2948412.495226345</v>
+        <v>2948412.495226346</v>
       </c>
       <c r="BV246" s="375" t="n">
         <v>3508807.02959453</v>
       </c>
       <c r="BW246" s="392" t="n">
-        <v>4189168.811220649</v>
+        <v>4189168.811220646</v>
       </c>
       <c r="BX246" s="386" t="n">
         <v>1201.507088575056</v>
       </c>
       <c r="BY246" s="372" t="n">
-        <v>1284.396332331876</v>
+        <v>1284.396332331877</v>
       </c>
       <c r="BZ246" s="372" t="n">
-        <v>1305.748676164889</v>
+        <v>1305.74867616489</v>
       </c>
       <c r="CA246" s="372" t="n">
         <v>1315.265142248685</v>
       </c>
       <c r="CB246" s="387" t="n">
-        <v>1322.396479618798</v>
+        <v>1322.396479618797</v>
       </c>
       <c r="CI246" s="225" t="n"/>
       <c r="CJ246" s="225" t="n"/>
@@ -49218,31 +49218,31 @@
         <v>366788.7949176781</v>
       </c>
       <c r="AL247" s="368" t="n">
-        <v>503342.2264200604</v>
+        <v>503342.2264200606</v>
       </c>
       <c r="AM247" s="368" t="n">
         <v>541986.112140473</v>
       </c>
       <c r="AN247" s="368" t="n">
-        <v>615979.704802421</v>
+        <v>615979.7048024209</v>
       </c>
       <c r="AO247" s="380" t="n">
-        <v>708815.1061859915</v>
+        <v>708815.1061859918</v>
       </c>
       <c r="AP247" s="381" t="n">
         <v>2431.506518122066</v>
       </c>
       <c r="AQ247" s="372" t="n">
-        <v>2868.321542207703</v>
+        <v>2868.321542207704</v>
       </c>
       <c r="AR247" s="372" t="n">
         <v>3053.224011881924</v>
       </c>
       <c r="AS247" s="372" t="n">
-        <v>3182.971653306332</v>
+        <v>3182.971653306331</v>
       </c>
       <c r="AT247" s="382" t="n">
-        <v>3295.472334984287</v>
+        <v>3295.472334984288</v>
       </c>
       <c r="BA247" s="101" t="inlineStr">
         <is>
@@ -49253,31 +49253,31 @@
         <v>366788.7949176781</v>
       </c>
       <c r="BC247" s="375" t="n">
-        <v>503342.2264200604</v>
+        <v>503342.2264200606</v>
       </c>
       <c r="BD247" s="375" t="n">
         <v>541986.112140473</v>
       </c>
       <c r="BE247" s="375" t="n">
-        <v>615979.704802421</v>
+        <v>615979.7048024209</v>
       </c>
       <c r="BF247" s="392" t="n">
-        <v>708815.1061859915</v>
+        <v>708815.1061859918</v>
       </c>
       <c r="BG247" s="386" t="n">
         <v>2431.506518122066</v>
       </c>
       <c r="BH247" s="372" t="n">
-        <v>2868.321542207703</v>
+        <v>2868.321542207704</v>
       </c>
       <c r="BI247" s="372" t="n">
         <v>3053.224011881924</v>
       </c>
       <c r="BJ247" s="372" t="n">
-        <v>3182.971653306332</v>
+        <v>3182.971653306331</v>
       </c>
       <c r="BK247" s="387" t="n">
-        <v>3295.472334984287</v>
+        <v>3295.472334984288</v>
       </c>
       <c r="BR247" s="101" t="inlineStr">
         <is>
@@ -49285,34 +49285,34 @@
         </is>
       </c>
       <c r="BS247" s="391" t="n">
-        <v>366667.9285133771</v>
+        <v>366667.9285133772</v>
       </c>
       <c r="BT247" s="375" t="n">
-        <v>505047.1943934748</v>
+        <v>505047.194393475</v>
       </c>
       <c r="BU247" s="375" t="n">
         <v>544729.7106229089</v>
       </c>
       <c r="BV247" s="375" t="n">
-        <v>619973.9607562228</v>
+        <v>619973.9607562227</v>
       </c>
       <c r="BW247" s="392" t="n">
-        <v>714402.3553931729</v>
+        <v>714402.3553931732</v>
       </c>
       <c r="BX247" s="386" t="n">
         <v>2431.506518122066</v>
       </c>
       <c r="BY247" s="372" t="n">
-        <v>2868.321542207703</v>
+        <v>2868.321542207704</v>
       </c>
       <c r="BZ247" s="372" t="n">
         <v>3053.224011881924</v>
       </c>
       <c r="CA247" s="372" t="n">
-        <v>3182.971653306332</v>
+        <v>3182.971653306331</v>
       </c>
       <c r="CB247" s="387" t="n">
-        <v>3295.472334984287</v>
+        <v>3295.472334984288</v>
       </c>
       <c r="CI247" s="225" t="n"/>
       <c r="CJ247" s="225" t="n"/>
@@ -49397,31 +49397,31 @@
         <v>296582.4898489109</v>
       </c>
       <c r="AL248" s="368" t="n">
-        <v>423566.0437798895</v>
+        <v>423566.0437798894</v>
       </c>
       <c r="AM248" s="368" t="n">
         <v>467857.786612624</v>
       </c>
       <c r="AN248" s="368" t="n">
-        <v>534385.0713972368</v>
+        <v>534385.0713972369</v>
       </c>
       <c r="AO248" s="380" t="n">
-        <v>606576.7779890148</v>
+        <v>606576.777989015</v>
       </c>
       <c r="AP248" s="381" t="n">
         <v>2191.608206723806</v>
       </c>
       <c r="AQ248" s="372" t="n">
-        <v>2411.990305032362</v>
+        <v>2411.990305032361</v>
       </c>
       <c r="AR248" s="372" t="n">
         <v>2550.000522427323</v>
       </c>
       <c r="AS248" s="372" t="n">
-        <v>2706.609831188206</v>
+        <v>2706.609831188207</v>
       </c>
       <c r="AT248" s="382" t="n">
-        <v>2781.951297580738</v>
+        <v>2781.951297580739</v>
       </c>
       <c r="BA248" s="111" t="inlineStr">
         <is>
@@ -49432,31 +49432,31 @@
         <v>296582.4898489109</v>
       </c>
       <c r="BC248" s="375" t="n">
-        <v>423566.0437798895</v>
+        <v>423566.0437798894</v>
       </c>
       <c r="BD248" s="375" t="n">
         <v>467857.786612624</v>
       </c>
       <c r="BE248" s="375" t="n">
-        <v>534385.0713972368</v>
+        <v>534385.0713972369</v>
       </c>
       <c r="BF248" s="392" t="n">
-        <v>606576.7779890148</v>
+        <v>606576.777989015</v>
       </c>
       <c r="BG248" s="386" t="n">
         <v>2191.608206723806</v>
       </c>
       <c r="BH248" s="372" t="n">
-        <v>2411.990305032362</v>
+        <v>2411.990305032361</v>
       </c>
       <c r="BI248" s="372" t="n">
         <v>2550.000522427323</v>
       </c>
       <c r="BJ248" s="372" t="n">
-        <v>2706.609831188206</v>
+        <v>2706.609831188207</v>
       </c>
       <c r="BK248" s="387" t="n">
-        <v>2781.951297580738</v>
+        <v>2781.951297580739</v>
       </c>
       <c r="BR248" s="111" t="inlineStr">
         <is>
@@ -49464,7 +49464,7 @@
         </is>
       </c>
       <c r="BS248" s="391" t="n">
-        <v>296669.3752177259</v>
+        <v>296669.3752177258</v>
       </c>
       <c r="BT248" s="375" t="n">
         <v>424861.0844800866</v>
@@ -49476,22 +49476,22 @@
         <v>537625.6260895854</v>
       </c>
       <c r="BW248" s="392" t="n">
-        <v>611148.6154412832</v>
+        <v>611148.6154412836</v>
       </c>
       <c r="BX248" s="386" t="n">
         <v>2191.608206723806</v>
       </c>
       <c r="BY248" s="372" t="n">
-        <v>2411.990305032362</v>
+        <v>2411.990305032361</v>
       </c>
       <c r="BZ248" s="372" t="n">
         <v>2550.000522427323</v>
       </c>
       <c r="CA248" s="372" t="n">
-        <v>2706.609831188206</v>
+        <v>2706.609831188207</v>
       </c>
       <c r="CB248" s="387" t="n">
-        <v>2781.951297580738</v>
+        <v>2781.951297580739</v>
       </c>
       <c r="CI248" s="225" t="n"/>
       <c r="CJ248" s="225" t="n"/>
@@ -49576,7 +49576,7 @@
         <v>304574.2258339776</v>
       </c>
       <c r="AL249" s="408" t="n">
-        <v>240304.6108908951</v>
+        <v>240304.6108908952</v>
       </c>
       <c r="AM249" s="408" t="n">
         <v>248677.0846304711</v>
@@ -49585,13 +49585,13 @@
         <v>263219.0138342187</v>
       </c>
       <c r="AO249" s="409" t="n">
-        <v>280543.0734739053</v>
+        <v>280543.0734739052</v>
       </c>
       <c r="AP249" s="410" t="n">
-        <v>35258.65751305072</v>
+        <v>35258.65751305073</v>
       </c>
       <c r="AQ249" s="411" t="n">
-        <v>31737.73461442073</v>
+        <v>31737.73461442074</v>
       </c>
       <c r="AR249" s="411" t="n">
         <v>32248.44280250056</v>
@@ -49600,7 +49600,7 @@
         <v>33276.34956892231</v>
       </c>
       <c r="AT249" s="412" t="n">
-        <v>34452.93960407056</v>
+        <v>34452.93960407055</v>
       </c>
       <c r="BA249" s="111" t="inlineStr">
         <is>
@@ -49611,7 +49611,7 @@
         <v>304574.2258339776</v>
       </c>
       <c r="BC249" s="420" t="n">
-        <v>240304.6108908951</v>
+        <v>240304.6108908952</v>
       </c>
       <c r="BD249" s="420" t="n">
         <v>248677.0846304711</v>
@@ -49620,13 +49620,13 @@
         <v>263219.0138342187</v>
       </c>
       <c r="BF249" s="421" t="n">
-        <v>280543.0734739053</v>
+        <v>280543.0734739052</v>
       </c>
       <c r="BG249" s="416" t="n">
-        <v>35258.65751305072</v>
+        <v>35258.65751305073</v>
       </c>
       <c r="BH249" s="417" t="n">
-        <v>31737.73461442073</v>
+        <v>31737.73461442074</v>
       </c>
       <c r="BI249" s="417" t="n">
         <v>32248.44280250056</v>
@@ -49635,7 +49635,7 @@
         <v>33276.34956892231</v>
       </c>
       <c r="BK249" s="418" t="n">
-        <v>34452.93960407056</v>
+        <v>34452.93960407055</v>
       </c>
       <c r="BR249" s="111" t="inlineStr">
         <is>
@@ -49643,10 +49643,10 @@
         </is>
       </c>
       <c r="BS249" s="419" t="n">
-        <v>304354.4169790543</v>
+        <v>304354.4169790544</v>
       </c>
       <c r="BT249" s="420" t="n">
-        <v>240101.6117355968</v>
+        <v>240101.6117355969</v>
       </c>
       <c r="BU249" s="420" t="n">
         <v>248464.550496311</v>
@@ -49655,13 +49655,13 @@
         <v>262995.2576779632</v>
       </c>
       <c r="BW249" s="421" t="n">
-        <v>280306.7074925737</v>
+        <v>280306.7074925736</v>
       </c>
       <c r="BX249" s="416" t="n">
-        <v>35258.65751305072</v>
+        <v>35258.65751305073</v>
       </c>
       <c r="BY249" s="417" t="n">
-        <v>31737.73461442073</v>
+        <v>31737.73461442074</v>
       </c>
       <c r="BZ249" s="417" t="n">
         <v>32248.44280250056</v>
@@ -49670,7 +49670,7 @@
         <v>33276.34956892231</v>
       </c>
       <c r="CB249" s="418" t="n">
-        <v>34452.93960407056</v>
+        <v>34452.93960407055</v>
       </c>
       <c r="CI249" s="225" t="n"/>
       <c r="CJ249" s="225" t="n"/>
@@ -49755,31 +49755,31 @@
         <v>2056602.927149345</v>
       </c>
       <c r="AL250" s="408" t="n">
-        <v>3634034.471080078</v>
+        <v>3634034.471080079</v>
       </c>
       <c r="AM250" s="408" t="n">
-        <v>4195401.337373517</v>
+        <v>4195401.337373518</v>
       </c>
       <c r="AN250" s="408" t="n">
-        <v>4904903.359693625</v>
+        <v>4904903.359693626</v>
       </c>
       <c r="AO250" s="409" t="n">
-        <v>5759810.437132451</v>
+        <v>5759810.437132448</v>
       </c>
       <c r="AP250" s="436" t="n">
         <v>1712.566138225755</v>
       </c>
       <c r="AQ250" s="437" t="n">
-        <v>1594.384503961528</v>
+        <v>1594.384503961529</v>
       </c>
       <c r="AR250" s="437" t="n">
-        <v>1602.588677228671</v>
+        <v>1602.588677228672</v>
       </c>
       <c r="AS250" s="437" t="n">
         <v>1606.410484798776</v>
       </c>
       <c r="AT250" s="438" t="n">
-        <v>1604.401813781541</v>
+        <v>1604.40181378154</v>
       </c>
       <c r="BA250" s="155" t="inlineStr">
         <is>
@@ -49790,31 +49790,31 @@
         <v>2056602.927149345</v>
       </c>
       <c r="BC250" s="440" t="n">
-        <v>3634034.471080078</v>
+        <v>3634034.471080079</v>
       </c>
       <c r="BD250" s="440" t="n">
-        <v>4195401.337373517</v>
+        <v>4195401.337373518</v>
       </c>
       <c r="BE250" s="440" t="n">
-        <v>4904903.359693625</v>
+        <v>4904903.359693626</v>
       </c>
       <c r="BF250" s="441" t="n">
-        <v>5759810.437132451</v>
+        <v>5759810.437132448</v>
       </c>
       <c r="BG250" s="442" t="n">
         <v>1712.566138225755</v>
       </c>
       <c r="BH250" s="443" t="n">
-        <v>1594.384503961528</v>
+        <v>1594.384503961529</v>
       </c>
       <c r="BI250" s="443" t="n">
-        <v>1602.588677228671</v>
+        <v>1602.588677228672</v>
       </c>
       <c r="BJ250" s="443" t="n">
         <v>1606.410484798776</v>
       </c>
       <c r="BK250" s="444" t="n">
-        <v>1604.401813781541</v>
+        <v>1604.40181378154</v>
       </c>
       <c r="BR250" s="155" t="inlineStr">
         <is>
@@ -49825,16 +49825,16 @@
         <v>2050763.455048499</v>
       </c>
       <c r="BT250" s="440" t="n">
-        <v>3643724.806317748</v>
+        <v>3643724.806317749</v>
       </c>
       <c r="BU250" s="440" t="n">
-        <v>4211596.13613696</v>
+        <v>4211596.136136961</v>
       </c>
       <c r="BV250" s="440" t="n">
-        <v>4929401.874118301</v>
+        <v>4929401.874118302</v>
       </c>
       <c r="BW250" s="441" t="n">
-        <v>5795026.48954768</v>
+        <v>5795026.489547676</v>
       </c>
       <c r="BX250" s="442" t="n">
         <v>1714.36344498729</v>
@@ -49846,10 +49846,10 @@
         <v>1602.311660747569</v>
       </c>
       <c r="CA250" s="443" t="n">
-        <v>1606.153626924827</v>
+        <v>1606.153626924828</v>
       </c>
       <c r="CB250" s="444" t="n">
-        <v>1604.175659818381</v>
+        <v>1604.17565981838</v>
       </c>
       <c r="CI250" s="225" t="n"/>
       <c r="CJ250" s="225" t="n"/>
@@ -51945,31 +51945,31 @@
         <v>1088657.416548779</v>
       </c>
       <c r="AL264" s="368" t="n">
-        <v>2466821.589989233</v>
+        <v>2466821.589989234</v>
       </c>
       <c r="AM264" s="368" t="n">
-        <v>2936880.353989949</v>
+        <v>2936880.35398995</v>
       </c>
       <c r="AN264" s="368" t="n">
         <v>3491319.569659749</v>
       </c>
       <c r="AO264" s="380" t="n">
-        <v>4163875.479483539</v>
+        <v>4163875.479483536</v>
       </c>
       <c r="AP264" s="381" t="n">
-        <v>1201.507088575482</v>
+        <v>1201.507088575481</v>
       </c>
       <c r="AQ264" s="372" t="n">
         <v>1284.396332331806</v>
       </c>
       <c r="AR264" s="372" t="n">
-        <v>1305.748676164959</v>
+        <v>1305.74867616496</v>
       </c>
       <c r="AS264" s="372" t="n">
         <v>1315.265142248585</v>
       </c>
       <c r="AT264" s="382" t="n">
-        <v>1322.396479618808</v>
+        <v>1322.396479618807</v>
       </c>
       <c r="BA264" s="83" t="inlineStr">
         <is>
@@ -51980,31 +51980,31 @@
         <v>1088657.416548779</v>
       </c>
       <c r="BC264" s="375" t="n">
-        <v>2466821.589989233</v>
+        <v>2466821.589989234</v>
       </c>
       <c r="BD264" s="375" t="n">
-        <v>2936880.353989949</v>
+        <v>2936880.35398995</v>
       </c>
       <c r="BE264" s="375" t="n">
         <v>3491319.569659749</v>
       </c>
       <c r="BF264" s="392" t="n">
-        <v>4163875.479483539</v>
+        <v>4163875.479483536</v>
       </c>
       <c r="BG264" s="386" t="n">
-        <v>1201.507088575482</v>
+        <v>1201.507088575481</v>
       </c>
       <c r="BH264" s="372" t="n">
         <v>1284.396332331806</v>
       </c>
       <c r="BI264" s="372" t="n">
-        <v>1305.748676164959</v>
+        <v>1305.74867616496</v>
       </c>
       <c r="BJ264" s="372" t="n">
         <v>1315.265142248585</v>
       </c>
       <c r="BK264" s="387" t="n">
-        <v>1322.396479618808</v>
+        <v>1322.396479618807</v>
       </c>
       <c r="BR264" s="83" t="inlineStr">
         <is>
@@ -52015,31 +52015,31 @@
         <v>1083071.734338342</v>
       </c>
       <c r="BT264" s="375" t="n">
-        <v>2473714.915708589</v>
+        <v>2473714.91570859</v>
       </c>
       <c r="BU264" s="375" t="n">
-        <v>2948412.495226345</v>
+        <v>2948412.495226346</v>
       </c>
       <c r="BV264" s="375" t="n">
         <v>3508807.02959453</v>
       </c>
       <c r="BW264" s="392" t="n">
-        <v>4189168.81122065</v>
+        <v>4189168.811220647</v>
       </c>
       <c r="BX264" s="386" t="n">
-        <v>1201.507088575482</v>
+        <v>1201.507088575481</v>
       </c>
       <c r="BY264" s="372" t="n">
         <v>1284.396332331806</v>
       </c>
       <c r="BZ264" s="372" t="n">
-        <v>1305.748676164959</v>
+        <v>1305.74867616496</v>
       </c>
       <c r="CA264" s="372" t="n">
         <v>1315.265142248585</v>
       </c>
       <c r="CB264" s="387" t="n">
-        <v>1322.396479618808</v>
+        <v>1322.396479618807</v>
       </c>
       <c r="CI264" s="396" t="n">
         <v>0.9999999999543784</v>
@@ -52048,7 +52048,7 @@
         <v>1.000000000005634</v>
       </c>
       <c r="CK264" s="397" t="n">
-        <v>0.9999999999984117</v>
+        <v>0.9999999999984118</v>
       </c>
       <c r="CL264" s="397" t="n">
         <v>0.9999999999987462</v>
@@ -52060,7 +52060,7 @@
         <v>1.000000000002135</v>
       </c>
       <c r="CO264" s="103" t="n">
-        <v>0.9999999999998852</v>
+        <v>0.999999999999885</v>
       </c>
       <c r="CP264" s="103" t="n">
         <v>1.000000000000008</v>
@@ -52069,7 +52069,7 @@
         <v>1.000000000000074</v>
       </c>
       <c r="CR264" s="104" t="n">
-        <v>1.000000000000114</v>
+        <v>1.000000000000115</v>
       </c>
       <c r="CT264" s="396" t="n">
         <v>0.9999999999543784</v>
@@ -52078,7 +52078,7 @@
         <v>1.000000000005634</v>
       </c>
       <c r="CV264" s="397" t="n">
-        <v>0.9999999999984117</v>
+        <v>0.9999999999984118</v>
       </c>
       <c r="CW264" s="397" t="n">
         <v>0.9999999999987462</v>
@@ -52090,16 +52090,16 @@
         <v>1.0000000000002</v>
       </c>
       <c r="CZ264" s="103" t="n">
-        <v>0.9999999999999116</v>
+        <v>0.9999999999999115</v>
       </c>
       <c r="DA264" s="103" t="n">
-        <v>1.000000000000016</v>
+        <v>1.000000000000015</v>
       </c>
       <c r="DB264" s="103" t="n">
         <v>1.000000000000073</v>
       </c>
       <c r="DC264" s="104" t="n">
-        <v>1.000000000000138</v>
+        <v>1.000000000000139</v>
       </c>
       <c r="DE264" s="511" t="n">
         <v>0</v>
@@ -52120,16 +52120,16 @@
         <v>242214.1477819225</v>
       </c>
       <c r="DL264" s="375" t="n">
-        <v>45650.81714687863</v>
+        <v>45650.81714687862</v>
       </c>
       <c r="DM264" s="375" t="n">
-        <v>48240.8801225251</v>
+        <v>48240.88012252509</v>
       </c>
       <c r="DN264" s="375" t="n">
-        <v>47894.66624533232</v>
+        <v>47894.66624533231</v>
       </c>
       <c r="DO264" s="392" t="n">
-        <v>47466.23510528297</v>
+        <v>47466.23510528295</v>
       </c>
     </row>
     <row r="265">
@@ -52212,31 +52212,31 @@
         <v>366788.7949176781</v>
       </c>
       <c r="AL265" s="368" t="n">
-        <v>503342.2264200604</v>
+        <v>503342.2264200606</v>
       </c>
       <c r="AM265" s="368" t="n">
         <v>541986.112140473</v>
       </c>
       <c r="AN265" s="368" t="n">
-        <v>615979.704802421</v>
+        <v>615979.7048024209</v>
       </c>
       <c r="AO265" s="380" t="n">
-        <v>708815.1061859915</v>
+        <v>708815.1061859918</v>
       </c>
       <c r="AP265" s="381" t="n">
-        <v>2431.506518123448</v>
+        <v>2431.506518123449</v>
       </c>
       <c r="AQ265" s="372" t="n">
-        <v>2868.321542209979</v>
+        <v>2868.32154220998</v>
       </c>
       <c r="AR265" s="372" t="n">
-        <v>3053.224011875301</v>
+        <v>3053.224011875303</v>
       </c>
       <c r="AS265" s="372" t="n">
-        <v>3182.971653306722</v>
+        <v>3182.971653306719</v>
       </c>
       <c r="AT265" s="382" t="n">
-        <v>3295.472334986085</v>
+        <v>3295.472334986088</v>
       </c>
       <c r="BA265" s="101" t="inlineStr">
         <is>
@@ -52247,31 +52247,31 @@
         <v>366788.7949176781</v>
       </c>
       <c r="BC265" s="375" t="n">
-        <v>503342.2264200604</v>
+        <v>503342.2264200606</v>
       </c>
       <c r="BD265" s="375" t="n">
         <v>541986.112140473</v>
       </c>
       <c r="BE265" s="375" t="n">
-        <v>615979.704802421</v>
+        <v>615979.7048024209</v>
       </c>
       <c r="BF265" s="392" t="n">
-        <v>708815.1061859915</v>
+        <v>708815.1061859918</v>
       </c>
       <c r="BG265" s="386" t="n">
-        <v>2431.506518123448</v>
+        <v>2431.506518123449</v>
       </c>
       <c r="BH265" s="372" t="n">
-        <v>2868.321542209979</v>
+        <v>2868.32154220998</v>
       </c>
       <c r="BI265" s="372" t="n">
-        <v>3053.224011875301</v>
+        <v>3053.224011875303</v>
       </c>
       <c r="BJ265" s="372" t="n">
-        <v>3182.971653306722</v>
+        <v>3182.971653306719</v>
       </c>
       <c r="BK265" s="387" t="n">
-        <v>3295.472334986085</v>
+        <v>3295.472334986088</v>
       </c>
       <c r="BR265" s="101" t="inlineStr">
         <is>
@@ -52279,34 +52279,34 @@
         </is>
       </c>
       <c r="BS265" s="391" t="n">
-        <v>366667.9285133771</v>
+        <v>366667.9285133772</v>
       </c>
       <c r="BT265" s="375" t="n">
-        <v>505047.1943934748</v>
+        <v>505047.194393475</v>
       </c>
       <c r="BU265" s="375" t="n">
-        <v>544729.7106229089</v>
+        <v>544729.7106229088</v>
       </c>
       <c r="BV265" s="375" t="n">
-        <v>619973.9607562228</v>
+        <v>619973.9607562227</v>
       </c>
       <c r="BW265" s="392" t="n">
-        <v>714402.3553931729</v>
+        <v>714402.3553931733</v>
       </c>
       <c r="BX265" s="386" t="n">
-        <v>2431.506518123448</v>
+        <v>2431.506518123449</v>
       </c>
       <c r="BY265" s="372" t="n">
-        <v>2868.321542209979</v>
+        <v>2868.32154220998</v>
       </c>
       <c r="BZ265" s="372" t="n">
-        <v>3053.224011875301</v>
+        <v>3053.224011875303</v>
       </c>
       <c r="CA265" s="372" t="n">
-        <v>3182.971653306722</v>
+        <v>3182.971653306719</v>
       </c>
       <c r="CB265" s="387" t="n">
-        <v>3295.472334986085</v>
+        <v>3295.472334986088</v>
       </c>
       <c r="CI265" s="396" t="n">
         <v>0.9999999999987477</v>
@@ -52336,7 +52336,7 @@
         <v>1.000000000002753</v>
       </c>
       <c r="CR265" s="104" t="n">
-        <v>0.9999999999983076</v>
+        <v>0.9999999999983072</v>
       </c>
       <c r="CT265" s="396" t="n">
         <v>0.9999999999987477</v>
@@ -52366,7 +52366,7 @@
         <v>1.000000000003774</v>
       </c>
       <c r="DC265" s="104" t="n">
-        <v>0.9999999999979813</v>
+        <v>0.9999999999979809</v>
       </c>
       <c r="DE265" s="391" t="n">
         <v>0</v>
@@ -52387,16 +52387,16 @@
         <v>63581.39137306195</v>
       </c>
       <c r="DL265" s="375" t="n">
-        <v>36840.47335040205</v>
+        <v>36840.47335040204</v>
       </c>
       <c r="DM265" s="375" t="n">
         <v>41783.40242293903</v>
       </c>
       <c r="DN265" s="375" t="n">
-        <v>47538.68160706646</v>
+        <v>47538.68160706644</v>
       </c>
       <c r="DO265" s="392" t="n">
-        <v>52637.13038060635</v>
+        <v>52637.13038060634</v>
       </c>
     </row>
     <row r="266">
@@ -52479,16 +52479,16 @@
         <v>296582.4898489109</v>
       </c>
       <c r="AL266" s="368" t="n">
-        <v>423566.0437798895</v>
+        <v>423566.0437798894</v>
       </c>
       <c r="AM266" s="368" t="n">
         <v>467857.786612624</v>
       </c>
       <c r="AN266" s="368" t="n">
-        <v>534385.0713972368</v>
+        <v>534385.0713972369</v>
       </c>
       <c r="AO266" s="380" t="n">
-        <v>606576.7779890148</v>
+        <v>606576.777989015</v>
       </c>
       <c r="AP266" s="381" t="n">
         <v>2191.60820672207</v>
@@ -52497,10 +52497,10 @@
         <v>2411.990305032699</v>
       </c>
       <c r="AR266" s="372" t="n">
-        <v>2550.000522421598</v>
+        <v>2550.000522421599</v>
       </c>
       <c r="AS266" s="372" t="n">
-        <v>2706.609831179765</v>
+        <v>2706.609831179766</v>
       </c>
       <c r="AT266" s="382" t="n">
         <v>2781.951297584706</v>
@@ -52514,16 +52514,16 @@
         <v>296582.4898489109</v>
       </c>
       <c r="BC266" s="375" t="n">
-        <v>423566.0437798895</v>
+        <v>423566.0437798894</v>
       </c>
       <c r="BD266" s="375" t="n">
         <v>467857.786612624</v>
       </c>
       <c r="BE266" s="375" t="n">
-        <v>534385.0713972368</v>
+        <v>534385.0713972369</v>
       </c>
       <c r="BF266" s="392" t="n">
-        <v>606576.7779890148</v>
+        <v>606576.777989015</v>
       </c>
       <c r="BG266" s="386" t="n">
         <v>2191.60820672207</v>
@@ -52532,10 +52532,10 @@
         <v>2411.990305032699</v>
       </c>
       <c r="BI266" s="372" t="n">
-        <v>2550.000522421598</v>
+        <v>2550.000522421599</v>
       </c>
       <c r="BJ266" s="372" t="n">
-        <v>2706.609831179765</v>
+        <v>2706.609831179766</v>
       </c>
       <c r="BK266" s="387" t="n">
         <v>2781.951297584706</v>
@@ -52546,19 +52546,19 @@
         </is>
       </c>
       <c r="BS266" s="391" t="n">
-        <v>296669.3752177259</v>
+        <v>296669.3752177258</v>
       </c>
       <c r="BT266" s="375" t="n">
-        <v>424861.0844800867</v>
+        <v>424861.0844800866</v>
       </c>
       <c r="BU266" s="375" t="n">
         <v>469989.379791395</v>
       </c>
       <c r="BV266" s="375" t="n">
-        <v>537625.6260895854</v>
+        <v>537625.6260895855</v>
       </c>
       <c r="BW266" s="392" t="n">
-        <v>611148.6154412832</v>
+        <v>611148.6154412834</v>
       </c>
       <c r="BX266" s="386" t="n">
         <v>2191.60820672207</v>
@@ -52567,22 +52567,22 @@
         <v>2411.990305032699</v>
       </c>
       <c r="BZ266" s="372" t="n">
-        <v>2550.000522421598</v>
+        <v>2550.000522421599</v>
       </c>
       <c r="CA266" s="372" t="n">
-        <v>2706.609831179765</v>
+        <v>2706.609831179766</v>
       </c>
       <c r="CB266" s="387" t="n">
         <v>2781.951297584706</v>
       </c>
       <c r="CI266" s="396" t="n">
-        <v>0.9999999999538679</v>
+        <v>0.9999999999538677</v>
       </c>
       <c r="CJ266" s="397" t="n">
         <v>1.000000000055153</v>
       </c>
       <c r="CK266" s="397" t="n">
-        <v>1.000000000025335</v>
+        <v>1.000000000025336</v>
       </c>
       <c r="CL266" s="397" t="n">
         <v>0.999999999993972</v>
@@ -52603,16 +52603,16 @@
         <v>0.9999999999994595</v>
       </c>
       <c r="CR266" s="104" t="n">
-        <v>1.000000000000588</v>
+        <v>1.000000000000587</v>
       </c>
       <c r="CT266" s="396" t="n">
-        <v>0.9999999999538679</v>
+        <v>0.9999999999538677</v>
       </c>
       <c r="CU266" s="397" t="n">
         <v>1.000000000055153</v>
       </c>
       <c r="CV266" s="397" t="n">
-        <v>1.000000000025335</v>
+        <v>1.000000000025336</v>
       </c>
       <c r="CW266" s="397" t="n">
         <v>0.999999999993972</v>
@@ -52621,7 +52621,7 @@
         <v>1.000000000000732</v>
       </c>
       <c r="CY266" s="102" t="n">
-        <v>0.9999999999997449</v>
+        <v>0.9999999999997451</v>
       </c>
       <c r="CZ266" s="103" t="n">
         <v>1.000000000001241</v>
@@ -52633,7 +52633,7 @@
         <v>0.9999999999995079</v>
       </c>
       <c r="DC266" s="104" t="n">
-        <v>1.000000000000643</v>
+        <v>1.000000000000642</v>
       </c>
       <c r="DE266" s="391" t="n">
         <v>0</v>
@@ -52651,10 +52651,10 @@
         <v>0</v>
       </c>
       <c r="DK266" s="391" t="n">
-        <v>104062.9869430569</v>
+        <v>104062.9869430568</v>
       </c>
       <c r="DL266" s="375" t="n">
-        <v>98115.6543567936</v>
+        <v>98115.65435679362</v>
       </c>
       <c r="DM266" s="375" t="n">
         <v>117890.7061657368</v>
@@ -52663,7 +52663,7 @@
         <v>143492.4846285013</v>
       </c>
       <c r="DO266" s="392" t="n">
-        <v>167538.8087529283</v>
+        <v>167538.8087529282</v>
       </c>
     </row>
     <row r="267" ht="15.75" customHeight="1" thickBot="1">
@@ -52746,7 +52746,7 @@
         <v>304574.2258339776</v>
       </c>
       <c r="AL267" s="408" t="n">
-        <v>240304.6108908951</v>
+        <v>240304.6108908952</v>
       </c>
       <c r="AM267" s="408" t="n">
         <v>248677.0846304711</v>
@@ -52755,19 +52755,19 @@
         <v>263219.0138342187</v>
       </c>
       <c r="AO267" s="409" t="n">
-        <v>280543.0734739053</v>
+        <v>280543.0734739052</v>
       </c>
       <c r="AP267" s="410" t="n">
-        <v>35258.65751158107</v>
+        <v>35258.65751158106</v>
       </c>
       <c r="AQ267" s="411" t="n">
-        <v>31737.73461601958</v>
+        <v>31737.73461601962</v>
       </c>
       <c r="AR267" s="411" t="n">
         <v>32248.4428033359</v>
       </c>
       <c r="AS267" s="411" t="n">
-        <v>33276.34956683776</v>
+        <v>33276.34956683773</v>
       </c>
       <c r="AT267" s="412" t="n">
         <v>34452.93960486878</v>
@@ -52781,7 +52781,7 @@
         <v>304574.2258339776</v>
       </c>
       <c r="BC267" s="420" t="n">
-        <v>240304.6108908951</v>
+        <v>240304.6108908952</v>
       </c>
       <c r="BD267" s="420" t="n">
         <v>248677.0846304711</v>
@@ -52790,19 +52790,19 @@
         <v>263219.0138342187</v>
       </c>
       <c r="BF267" s="421" t="n">
-        <v>280543.0734739053</v>
+        <v>280543.0734739052</v>
       </c>
       <c r="BG267" s="416" t="n">
-        <v>35258.65751158107</v>
+        <v>35258.65751158106</v>
       </c>
       <c r="BH267" s="417" t="n">
-        <v>31737.73461601958</v>
+        <v>31737.73461601962</v>
       </c>
       <c r="BI267" s="417" t="n">
         <v>32248.4428033359</v>
       </c>
       <c r="BJ267" s="417" t="n">
-        <v>33276.34956683776</v>
+        <v>33276.34956683773</v>
       </c>
       <c r="BK267" s="418" t="n">
         <v>34452.93960486878</v>
@@ -52816,7 +52816,7 @@
         <v>304354.4169790543</v>
       </c>
       <c r="BT267" s="420" t="n">
-        <v>240101.6117355968</v>
+        <v>240101.6117355969</v>
       </c>
       <c r="BU267" s="420" t="n">
         <v>248464.550496311</v>
@@ -52825,19 +52825,19 @@
         <v>262995.2576779632</v>
       </c>
       <c r="BW267" s="421" t="n">
-        <v>280306.7074925737</v>
+        <v>280306.7074925736</v>
       </c>
       <c r="BX267" s="416" t="n">
-        <v>35258.65751158107</v>
+        <v>35258.65751158106</v>
       </c>
       <c r="BY267" s="417" t="n">
-        <v>31737.73461601958</v>
+        <v>31737.73461601962</v>
       </c>
       <c r="BZ267" s="417" t="n">
         <v>32248.4428033359</v>
       </c>
       <c r="CA267" s="417" t="n">
-        <v>33276.34956683776</v>
+        <v>33276.34956683773</v>
       </c>
       <c r="CB267" s="418" t="n">
         <v>34452.93960486878</v>
@@ -52861,7 +52861,7 @@
         <v>1.000000000001715</v>
       </c>
       <c r="CO267" s="133" t="n">
-        <v>0.9999999999840644</v>
+        <v>0.9999999999840642</v>
       </c>
       <c r="CP267" s="133" t="n">
         <v>1.000000000032071</v>
@@ -52870,10 +52870,10 @@
         <v>1.000000000018369</v>
       </c>
       <c r="CR267" s="134" t="n">
-        <v>1.000000000039605</v>
+        <v>1.000000000039606</v>
       </c>
       <c r="CT267" s="422" t="n">
-        <v>0.9999999999999997</v>
+        <v>1</v>
       </c>
       <c r="CU267" s="423" t="n">
         <v>1</v>
@@ -52897,7 +52897,7 @@
         <v>0.9999999999991662</v>
       </c>
       <c r="DB267" s="133" t="n">
-        <v>0.9999999999995822</v>
+        <v>0.999999999999582</v>
       </c>
       <c r="DC267" s="134" t="n">
         <v>1.000000000000172</v>
@@ -52918,19 +52918,19 @@
         <v>0</v>
       </c>
       <c r="DK267" s="419" t="n">
-        <v>4415.545846790802</v>
+        <v>4415.545846790801</v>
       </c>
       <c r="DL267" s="420" t="n">
-        <v>4762.243435281963</v>
+        <v>4762.243435281962</v>
       </c>
       <c r="DM267" s="420" t="n">
-        <v>5162.602074403597</v>
+        <v>5162.602074403596</v>
       </c>
       <c r="DN267" s="420" t="n">
-        <v>5542.300576433675</v>
+        <v>5542.300576433674</v>
       </c>
       <c r="DO267" s="421" t="n">
-        <v>5946.330721239719</v>
+        <v>5946.330721239718</v>
       </c>
     </row>
     <row r="268" ht="15.75" customHeight="1" thickBot="1">
@@ -53013,19 +53013,19 @@
         <v>2056602.927149345</v>
       </c>
       <c r="AL268" s="408" t="n">
-        <v>3634034.471080078</v>
+        <v>3634034.471080079</v>
       </c>
       <c r="AM268" s="408" t="n">
-        <v>4195401.337373517</v>
+        <v>4195401.337373518</v>
       </c>
       <c r="AN268" s="408" t="n">
-        <v>4904903.359693625</v>
+        <v>4904903.359693626</v>
       </c>
       <c r="AO268" s="409" t="n">
-        <v>5759810.437132451</v>
+        <v>5759810.437132448</v>
       </c>
       <c r="AP268" s="436" t="n">
-        <v>1712.566138225669</v>
+        <v>1712.566138225668</v>
       </c>
       <c r="AQ268" s="437" t="n">
         <v>1594.384503961836</v>
@@ -53037,7 +53037,7 @@
         <v>1606.410484798098</v>
       </c>
       <c r="AT268" s="438" t="n">
-        <v>1604.401813781828</v>
+        <v>1604.401813781827</v>
       </c>
       <c r="BA268" s="155" t="inlineStr">
         <is>
@@ -53048,19 +53048,19 @@
         <v>2056602.927149345</v>
       </c>
       <c r="BC268" s="440" t="n">
-        <v>3634034.471080078</v>
+        <v>3634034.471080079</v>
       </c>
       <c r="BD268" s="440" t="n">
-        <v>4195401.337373517</v>
+        <v>4195401.337373518</v>
       </c>
       <c r="BE268" s="440" t="n">
-        <v>4904903.359693625</v>
+        <v>4904903.359693626</v>
       </c>
       <c r="BF268" s="441" t="n">
-        <v>5759810.437132451</v>
+        <v>5759810.437132448</v>
       </c>
       <c r="BG268" s="442" t="n">
-        <v>1712.566138225669</v>
+        <v>1712.566138225668</v>
       </c>
       <c r="BH268" s="443" t="n">
         <v>1594.384503961836</v>
@@ -53072,7 +53072,7 @@
         <v>1606.410484798098</v>
       </c>
       <c r="BK268" s="444" t="n">
-        <v>1604.401813781828</v>
+        <v>1604.401813781827</v>
       </c>
       <c r="BR268" s="155" t="inlineStr">
         <is>
@@ -53083,19 +53083,19 @@
         <v>2050763.455048499</v>
       </c>
       <c r="BT268" s="440" t="n">
-        <v>3643724.806317747</v>
+        <v>3643724.806317749</v>
       </c>
       <c r="BU268" s="440" t="n">
         <v>4211596.136136961</v>
       </c>
       <c r="BV268" s="440" t="n">
-        <v>4929401.874118301</v>
+        <v>4929401.874118302</v>
       </c>
       <c r="BW268" s="441" t="n">
-        <v>5795026.48954768</v>
+        <v>5795026.489547676</v>
       </c>
       <c r="BX268" s="442" t="n">
-        <v>1714.363444987201</v>
+        <v>1714.3634449872</v>
       </c>
       <c r="BY268" s="443" t="n">
         <v>1594.095642603188</v>
@@ -53107,7 +53107,7 @@
         <v>1606.153626924151</v>
       </c>
       <c r="CB268" s="444" t="n">
-        <v>1604.175659818667</v>
+        <v>1604.175659818666</v>
       </c>
       <c r="DE268" s="419" t="n">
         <v>0</v>
@@ -53125,13 +53125,13 @@
         <v>0</v>
       </c>
       <c r="DK268" s="439" t="n">
-        <v>414274.0719448322</v>
+        <v>414274.0719448321</v>
       </c>
       <c r="DL268" s="440" t="n">
         <v>185369.1882893562</v>
       </c>
       <c r="DM268" s="440" t="n">
-        <v>213077.5907856046</v>
+        <v>213077.5907856045</v>
       </c>
       <c r="DN268" s="440" t="n">
         <v>244468.1330573338</v>
@@ -54159,31 +54159,31 @@
         <v>0</v>
       </c>
       <c r="BX276" s="197" t="n">
-        <v>23.94490471180374</v>
+        <v>23.94490471180373</v>
       </c>
       <c r="BY276" s="190" t="n">
         <v>17.77149025158941</v>
       </c>
       <c r="BZ276" s="190" t="n">
-        <v>17.53795164492137</v>
+        <v>17.53795164492138</v>
       </c>
       <c r="CA276" s="190" t="n">
-        <v>17.291081220829</v>
+        <v>17.29108122082901</v>
       </c>
       <c r="CB276" s="198" t="n">
         <v>17.0569220667346</v>
       </c>
       <c r="CC276" s="199" t="n">
-        <v>23.94490471180374</v>
+        <v>23.94490471180373</v>
       </c>
       <c r="CD276" s="200" t="n">
         <v>17.77149025158941</v>
       </c>
       <c r="CE276" s="200" t="n">
-        <v>17.53795164492137</v>
+        <v>17.53795164492138</v>
       </c>
       <c r="CF276" s="200" t="n">
-        <v>17.291081220829</v>
+        <v>17.29108122082901</v>
       </c>
       <c r="CG276" s="201" t="n">
         <v>17.0569220667346</v>
@@ -54619,34 +54619,34 @@
         <v>0</v>
       </c>
       <c r="AP278" s="194" t="n">
-        <v>80.90117486016302</v>
+        <v>80.90117486016304</v>
       </c>
       <c r="AQ278" s="179" t="n">
         <v>80.37340786516275</v>
       </c>
       <c r="AR278" s="179" t="n">
-        <v>80.40871203656</v>
+        <v>80.40871203655999</v>
       </c>
       <c r="AS278" s="179" t="n">
         <v>81.20637098159588</v>
       </c>
       <c r="AT278" s="195" t="n">
-        <v>83.35011217207141</v>
+        <v>83.35011217207139</v>
       </c>
       <c r="AU278" s="190" t="n">
-        <v>80.90117486016302</v>
+        <v>80.90117486016304</v>
       </c>
       <c r="AV278" s="190" t="n">
         <v>80.37340786516275</v>
       </c>
       <c r="AW278" s="190" t="n">
-        <v>80.40871203656</v>
+        <v>80.40871203655999</v>
       </c>
       <c r="AX278" s="190" t="n">
         <v>81.20637098159588</v>
       </c>
       <c r="AY278" s="196" t="n">
-        <v>83.35011217207141</v>
+        <v>83.35011217207139</v>
       </c>
       <c r="BA278" s="111" t="inlineStr">
         <is>
@@ -54669,34 +54669,34 @@
         <v>0</v>
       </c>
       <c r="BG278" s="197" t="n">
-        <v>80.90117486016302</v>
+        <v>80.90117486016304</v>
       </c>
       <c r="BH278" s="190" t="n">
         <v>80.37340786516275</v>
       </c>
       <c r="BI278" s="190" t="n">
-        <v>80.40871203656</v>
+        <v>80.40871203655999</v>
       </c>
       <c r="BJ278" s="190" t="n">
         <v>81.20637098159588</v>
       </c>
       <c r="BK278" s="198" t="n">
-        <v>83.35011217207141</v>
+        <v>83.35011217207139</v>
       </c>
       <c r="BL278" s="197" t="n">
-        <v>80.90117486016302</v>
+        <v>80.90117486016304</v>
       </c>
       <c r="BM278" s="190" t="n">
         <v>80.37340786516275</v>
       </c>
       <c r="BN278" s="190" t="n">
-        <v>80.40871203656</v>
+        <v>80.40871203655999</v>
       </c>
       <c r="BO278" s="190" t="n">
         <v>81.20637098159588</v>
       </c>
       <c r="BP278" s="198" t="n">
-        <v>83.35011217207141</v>
+        <v>83.35011217207139</v>
       </c>
       <c r="BR278" s="111" t="inlineStr">
         <is>
@@ -54719,34 +54719,34 @@
         <v>0</v>
       </c>
       <c r="BX278" s="197" t="n">
-        <v>81.16527501751209</v>
+        <v>81.1652750175121</v>
       </c>
       <c r="BY278" s="190" t="n">
         <v>80.4491340264792</v>
       </c>
       <c r="BZ278" s="190" t="n">
-        <v>80.48396132297766</v>
+        <v>80.48396132297765</v>
       </c>
       <c r="CA278" s="190" t="n">
         <v>81.28160965353055</v>
       </c>
       <c r="CB278" s="198" t="n">
-        <v>83.424841930694</v>
+        <v>83.42484193069399</v>
       </c>
       <c r="CC278" s="197" t="n">
-        <v>81.16527501751209</v>
+        <v>81.1652750175121</v>
       </c>
       <c r="CD278" s="190" t="n">
         <v>80.4491340264792</v>
       </c>
       <c r="CE278" s="190" t="n">
-        <v>80.48396132297766</v>
+        <v>80.48396132297765</v>
       </c>
       <c r="CF278" s="190" t="n">
         <v>81.28160965353055</v>
       </c>
       <c r="CG278" s="198" t="n">
-        <v>83.424841930694</v>
+        <v>83.42484193069399</v>
       </c>
       <c r="CI278" s="197" t="n">
         <v>0</v>
@@ -54884,10 +54884,10 @@
         </is>
       </c>
       <c r="AK279" s="206" t="n">
-        <v>5.447342876795428</v>
+        <v>5.447342876795427</v>
       </c>
       <c r="AL279" s="207" t="n">
-        <v>7.015258528875047</v>
+        <v>7.015258528875048</v>
       </c>
       <c r="AM279" s="207" t="n">
         <v>13.59238996021134</v>
@@ -54896,19 +54896,19 @@
         <v>17.11580126467504</v>
       </c>
       <c r="AO279" s="208" t="n">
-        <v>17.86531224755396</v>
+        <v>17.86531224755395</v>
       </c>
       <c r="AP279" s="206" t="n">
         <v>22.20506035477361</v>
       </c>
       <c r="AQ279" s="207" t="n">
-        <v>22.66169298432294</v>
+        <v>22.66169298432295</v>
       </c>
       <c r="AR279" s="207" t="n">
         <v>17.12983713988109</v>
       </c>
       <c r="AS279" s="207" t="n">
-        <v>14.41977593173059</v>
+        <v>14.41977593173058</v>
       </c>
       <c r="AT279" s="208" t="n">
         <v>14.55215704610523</v>
@@ -54917,13 +54917,13 @@
         <v>27.65240323156904</v>
       </c>
       <c r="AV279" s="209" t="n">
-        <v>29.67695151319799</v>
+        <v>29.676951513198</v>
       </c>
       <c r="AW279" s="209" t="n">
         <v>30.72222710009243</v>
       </c>
       <c r="AX279" s="209" t="n">
-        <v>31.53557719640563</v>
+        <v>31.53557719640562</v>
       </c>
       <c r="AY279" s="210" t="n">
         <v>32.41746929365918</v>
@@ -54934,10 +54934,10 @@
         </is>
       </c>
       <c r="BB279" s="211" t="n">
-        <v>5.447342876795428</v>
+        <v>5.447342876795427</v>
       </c>
       <c r="BC279" s="212" t="n">
-        <v>7.015258528875047</v>
+        <v>7.015258528875048</v>
       </c>
       <c r="BD279" s="212" t="n">
         <v>13.59238996021134</v>
@@ -54946,19 +54946,19 @@
         <v>17.11580126467504</v>
       </c>
       <c r="BF279" s="213" t="n">
-        <v>17.86531224755396</v>
+        <v>17.86531224755395</v>
       </c>
       <c r="BG279" s="211" t="n">
         <v>22.20506035477361</v>
       </c>
       <c r="BH279" s="212" t="n">
-        <v>22.66169298432294</v>
+        <v>22.66169298432295</v>
       </c>
       <c r="BI279" s="212" t="n">
         <v>17.12983713988109</v>
       </c>
       <c r="BJ279" s="212" t="n">
-        <v>14.41977593173059</v>
+        <v>14.41977593173058</v>
       </c>
       <c r="BK279" s="213" t="n">
         <v>14.55215704610523</v>
@@ -54967,13 +54967,13 @@
         <v>27.65240323156904</v>
       </c>
       <c r="BM279" s="212" t="n">
-        <v>29.67695151319799</v>
+        <v>29.676951513198</v>
       </c>
       <c r="BN279" s="212" t="n">
         <v>30.72222710009243</v>
       </c>
       <c r="BO279" s="212" t="n">
-        <v>31.53557719640563</v>
+        <v>31.53557719640562</v>
       </c>
       <c r="BP279" s="213" t="n">
         <v>32.41746929365918</v>
@@ -54984,10 +54984,10 @@
         </is>
       </c>
       <c r="BS279" s="211" t="n">
-        <v>5.39203807033229</v>
+        <v>5.392038070332289</v>
       </c>
       <c r="BT279" s="212" t="n">
-        <v>6.926227674335453</v>
+        <v>6.926227674335454</v>
       </c>
       <c r="BU279" s="212" t="n">
         <v>13.46950105181097</v>
@@ -54999,7 +54999,7 @@
         <v>17.670807431792</v>
       </c>
       <c r="BX279" s="211" t="n">
-        <v>22.26659934229855</v>
+        <v>22.26659934229856</v>
       </c>
       <c r="BY279" s="212" t="n">
         <v>22.75711998394832</v>
@@ -55014,7 +55014,7 @@
         <v>14.75352240799307</v>
       </c>
       <c r="CC279" s="212" t="n">
-        <v>27.65863741263084</v>
+        <v>27.65863741263085</v>
       </c>
       <c r="CD279" s="212" t="n">
         <v>29.68334765828378</v>
@@ -55164,10 +55164,10 @@
         </is>
       </c>
       <c r="AK280" s="206" t="n">
-        <v>5.447342876795428</v>
+        <v>5.447342876795427</v>
       </c>
       <c r="AL280" s="207" t="n">
-        <v>7.015258528875047</v>
+        <v>7.015258528875048</v>
       </c>
       <c r="AM280" s="207" t="n">
         <v>13.59238996021134</v>
@@ -55176,7 +55176,7 @@
         <v>17.11580126467504</v>
       </c>
       <c r="AO280" s="208" t="n">
-        <v>17.86531224755396</v>
+        <v>17.86531224755395</v>
       </c>
       <c r="AP280" s="206" t="n">
         <v>134.4108517895829</v>
@@ -55194,7 +55194,7 @@
         <v>126.0462685012848</v>
       </c>
       <c r="AU280" s="207" t="n">
-        <v>139.8581946663783</v>
+        <v>139.8581946663784</v>
       </c>
       <c r="AV280" s="207" t="n">
         <v>140.5583731904682</v>
@@ -55214,10 +55214,10 @@
         </is>
       </c>
       <c r="BB280" s="221" t="n">
-        <v>5.447342876795428</v>
+        <v>5.447342876795427</v>
       </c>
       <c r="BC280" s="222" t="n">
-        <v>7.015258528875047</v>
+        <v>7.015258528875048</v>
       </c>
       <c r="BD280" s="222" t="n">
         <v>13.59238996021134</v>
@@ -55226,7 +55226,7 @@
         <v>17.11580126467504</v>
       </c>
       <c r="BF280" s="214" t="n">
-        <v>17.86531224755396</v>
+        <v>17.86531224755395</v>
       </c>
       <c r="BG280" s="221" t="n">
         <v>134.4108517895829</v>
@@ -55244,7 +55244,7 @@
         <v>126.0462685012848</v>
       </c>
       <c r="BL280" s="222" t="n">
-        <v>139.8581946663783</v>
+        <v>139.8581946663784</v>
       </c>
       <c r="BM280" s="222" t="n">
         <v>140.5583731904682</v>
@@ -55264,10 +55264,10 @@
         </is>
       </c>
       <c r="BS280" s="221" t="n">
-        <v>5.39203807033229</v>
+        <v>5.392038070332289</v>
       </c>
       <c r="BT280" s="222" t="n">
-        <v>6.926227674335453</v>
+        <v>6.926227674335454</v>
       </c>
       <c r="BU280" s="222" t="n">
         <v>13.46950105181097</v>
@@ -58406,31 +58406,31 @@
         <v>0</v>
       </c>
       <c r="BX294" s="197" t="n">
-        <v>23.94490471180374</v>
+        <v>23.94490471180373</v>
       </c>
       <c r="BY294" s="190" t="n">
         <v>17.77149025158941</v>
       </c>
       <c r="BZ294" s="190" t="n">
-        <v>17.53795164492137</v>
+        <v>17.53795164492138</v>
       </c>
       <c r="CA294" s="190" t="n">
-        <v>17.291081220829</v>
+        <v>17.29108122082901</v>
       </c>
       <c r="CB294" s="198" t="n">
         <v>17.0569220667346</v>
       </c>
       <c r="CC294" s="199" t="n">
-        <v>23.94490471180374</v>
+        <v>23.94490471180373</v>
       </c>
       <c r="CD294" s="200" t="n">
         <v>17.77149025158941</v>
       </c>
       <c r="CE294" s="200" t="n">
-        <v>17.53795164492137</v>
+        <v>17.53795164492138</v>
       </c>
       <c r="CF294" s="200" t="n">
-        <v>17.291081220829</v>
+        <v>17.29108122082901</v>
       </c>
       <c r="CG294" s="201" t="n">
         <v>17.0569220667346</v>
@@ -58463,13 +58463,13 @@
         <v>500</v>
       </c>
       <c r="CW294" s="199" t="n">
-        <v>6.492663762398207</v>
+        <v>6.492663762398206</v>
       </c>
       <c r="CX294" s="200" t="n">
         <v>0.5582212223740151</v>
       </c>
       <c r="CY294" s="200" t="n">
-        <v>0.5560499977934461</v>
+        <v>0.5560499977934462</v>
       </c>
       <c r="CZ294" s="200" t="n">
         <v>0.5496802400906827</v>
@@ -58770,7 +58770,7 @@
         <v>0.08509236834482972</v>
       </c>
       <c r="DA295" s="198" t="n">
-        <v>0.07410678027584618</v>
+        <v>0.07410678027584619</v>
       </c>
     </row>
     <row r="296">
@@ -58896,34 +58896,34 @@
         <v>0</v>
       </c>
       <c r="AP296" s="194" t="n">
-        <v>80.90117486016302</v>
+        <v>80.90117486016304</v>
       </c>
       <c r="AQ296" s="179" t="n">
         <v>80.37340786516275</v>
       </c>
       <c r="AR296" s="179" t="n">
-        <v>80.40871203656</v>
+        <v>80.40871203655999</v>
       </c>
       <c r="AS296" s="179" t="n">
         <v>81.20637098159588</v>
       </c>
       <c r="AT296" s="195" t="n">
-        <v>83.35011217207141</v>
+        <v>83.35011217207139</v>
       </c>
       <c r="AU296" s="190" t="n">
-        <v>80.90117486016302</v>
+        <v>80.90117486016304</v>
       </c>
       <c r="AV296" s="190" t="n">
         <v>80.37340786516275</v>
       </c>
       <c r="AW296" s="190" t="n">
-        <v>80.40871203656</v>
+        <v>80.40871203655999</v>
       </c>
       <c r="AX296" s="190" t="n">
         <v>81.20637098159588</v>
       </c>
       <c r="AY296" s="196" t="n">
-        <v>83.35011217207141</v>
+        <v>83.35011217207139</v>
       </c>
       <c r="BA296" s="111" t="inlineStr">
         <is>
@@ -58946,34 +58946,34 @@
         <v>0</v>
       </c>
       <c r="BG296" s="197" t="n">
-        <v>80.90117486016302</v>
+        <v>80.90117486016304</v>
       </c>
       <c r="BH296" s="190" t="n">
         <v>80.37340786516275</v>
       </c>
       <c r="BI296" s="190" t="n">
-        <v>80.40871203656</v>
+        <v>80.40871203655999</v>
       </c>
       <c r="BJ296" s="190" t="n">
         <v>81.20637098159588</v>
       </c>
       <c r="BK296" s="198" t="n">
-        <v>83.35011217207141</v>
+        <v>83.35011217207139</v>
       </c>
       <c r="BL296" s="197" t="n">
-        <v>80.90117486016302</v>
+        <v>80.90117486016304</v>
       </c>
       <c r="BM296" s="190" t="n">
         <v>80.37340786516275</v>
       </c>
       <c r="BN296" s="190" t="n">
-        <v>80.40871203656</v>
+        <v>80.40871203655999</v>
       </c>
       <c r="BO296" s="190" t="n">
         <v>81.20637098159588</v>
       </c>
       <c r="BP296" s="198" t="n">
-        <v>83.35011217207141</v>
+        <v>83.35011217207139</v>
       </c>
       <c r="BR296" s="111" t="inlineStr">
         <is>
@@ -58996,34 +58996,34 @@
         <v>0</v>
       </c>
       <c r="BX296" s="197" t="n">
-        <v>81.16527501751209</v>
+        <v>81.1652750175121</v>
       </c>
       <c r="BY296" s="190" t="n">
         <v>80.4491340264792</v>
       </c>
       <c r="BZ296" s="190" t="n">
-        <v>80.48396132297768</v>
+        <v>80.48396132297766</v>
       </c>
       <c r="CA296" s="190" t="n">
         <v>81.28160965353057</v>
       </c>
       <c r="CB296" s="198" t="n">
-        <v>83.424841930694</v>
+        <v>83.42484193069399</v>
       </c>
       <c r="CC296" s="197" t="n">
-        <v>81.16527501751209</v>
+        <v>81.1652750175121</v>
       </c>
       <c r="CD296" s="190" t="n">
         <v>80.4491340264792</v>
       </c>
       <c r="CE296" s="190" t="n">
-        <v>80.48396132297768</v>
+        <v>80.48396132297766</v>
       </c>
       <c r="CF296" s="190" t="n">
         <v>81.28160965353057</v>
       </c>
       <c r="CG296" s="198" t="n">
-        <v>83.424841930694</v>
+        <v>83.42484193069399</v>
       </c>
       <c r="CI296" s="197" t="n">
         <v>0</v>
@@ -59053,7 +59053,7 @@
         <v>7464</v>
       </c>
       <c r="CW296" s="197" t="n">
-        <v>0.2641001573490654</v>
+        <v>0.2641001573490653</v>
       </c>
       <c r="CX296" s="190" t="n">
         <v>0.07572616131645396</v>
@@ -59176,10 +59176,10 @@
         </is>
       </c>
       <c r="AK297" s="206" t="n">
-        <v>5.447342876795428</v>
+        <v>5.447342876795427</v>
       </c>
       <c r="AL297" s="207" t="n">
-        <v>7.015258528875047</v>
+        <v>7.015258528875048</v>
       </c>
       <c r="AM297" s="207" t="n">
         <v>13.59238996021134</v>
@@ -59188,19 +59188,19 @@
         <v>17.11580126467504</v>
       </c>
       <c r="AO297" s="208" t="n">
-        <v>17.86531224755396</v>
+        <v>17.86531224755395</v>
       </c>
       <c r="AP297" s="206" t="n">
         <v>22.20506035477361</v>
       </c>
       <c r="AQ297" s="207" t="n">
-        <v>22.66169298432294</v>
+        <v>22.66169298432295</v>
       </c>
       <c r="AR297" s="207" t="n">
         <v>17.12983713988109</v>
       </c>
       <c r="AS297" s="207" t="n">
-        <v>14.41977593173059</v>
+        <v>14.41977593173058</v>
       </c>
       <c r="AT297" s="208" t="n">
         <v>14.55215704610523</v>
@@ -59209,13 +59209,13 @@
         <v>27.65240323156904</v>
       </c>
       <c r="AV297" s="209" t="n">
-        <v>29.67695151319799</v>
+        <v>29.676951513198</v>
       </c>
       <c r="AW297" s="209" t="n">
         <v>30.72222710009243</v>
       </c>
       <c r="AX297" s="209" t="n">
-        <v>31.53557719640563</v>
+        <v>31.53557719640562</v>
       </c>
       <c r="AY297" s="210" t="n">
         <v>32.41746929365918</v>
@@ -59226,10 +59226,10 @@
         </is>
       </c>
       <c r="BB297" s="211" t="n">
-        <v>5.447342876795428</v>
+        <v>5.447342876795427</v>
       </c>
       <c r="BC297" s="212" t="n">
-        <v>7.015258528875047</v>
+        <v>7.015258528875048</v>
       </c>
       <c r="BD297" s="212" t="n">
         <v>13.59238996021134</v>
@@ -59238,19 +59238,19 @@
         <v>17.11580126467504</v>
       </c>
       <c r="BF297" s="213" t="n">
-        <v>17.86531224755396</v>
+        <v>17.86531224755395</v>
       </c>
       <c r="BG297" s="211" t="n">
         <v>22.20506035477361</v>
       </c>
       <c r="BH297" s="212" t="n">
-        <v>22.66169298432294</v>
+        <v>22.66169298432295</v>
       </c>
       <c r="BI297" s="212" t="n">
         <v>17.12983713988109</v>
       </c>
       <c r="BJ297" s="212" t="n">
-        <v>14.41977593173059</v>
+        <v>14.41977593173058</v>
       </c>
       <c r="BK297" s="213" t="n">
         <v>14.55215704610523</v>
@@ -59259,13 +59259,13 @@
         <v>27.65240323156904</v>
       </c>
       <c r="BM297" s="212" t="n">
-        <v>29.67695151319799</v>
+        <v>29.676951513198</v>
       </c>
       <c r="BN297" s="212" t="n">
         <v>30.72222710009243</v>
       </c>
       <c r="BO297" s="212" t="n">
-        <v>31.53557719640563</v>
+        <v>31.53557719640562</v>
       </c>
       <c r="BP297" s="213" t="n">
         <v>32.41746929365918</v>
@@ -59276,10 +59276,10 @@
         </is>
       </c>
       <c r="BS297" s="211" t="n">
-        <v>5.39203807033229</v>
+        <v>5.392038070332289</v>
       </c>
       <c r="BT297" s="212" t="n">
-        <v>6.926227674335453</v>
+        <v>6.926227674335454</v>
       </c>
       <c r="BU297" s="212" t="n">
         <v>13.46950105181097</v>
@@ -59291,10 +59291,10 @@
         <v>17.670807431792</v>
       </c>
       <c r="BX297" s="211" t="n">
-        <v>22.26659934229855</v>
+        <v>22.26659934229856</v>
       </c>
       <c r="BY297" s="212" t="n">
-        <v>22.75711998394832</v>
+        <v>22.75711998394833</v>
       </c>
       <c r="BZ297" s="212" t="n">
         <v>17.25931657221641</v>
@@ -59306,7 +59306,7 @@
         <v>14.75352240799307</v>
       </c>
       <c r="CC297" s="212" t="n">
-        <v>27.65863741263084</v>
+        <v>27.65863741263085</v>
       </c>
       <c r="CD297" s="212" t="n">
         <v>29.68334765828378</v>
@@ -59348,19 +59348,19 @@
         <v>1590</v>
       </c>
       <c r="CW297" s="211" t="n">
-        <v>0.00623418106180267</v>
+        <v>0.006234181061802453</v>
       </c>
       <c r="CX297" s="212" t="n">
-        <v>0.006396145085788303</v>
+        <v>0.00639614508578808</v>
       </c>
       <c r="CY297" s="212" t="n">
-        <v>0.006590523934945408</v>
+        <v>0.006590523934945179</v>
       </c>
       <c r="CZ297" s="212" t="n">
-        <v>0.006724179760346102</v>
+        <v>0.006724179760345868</v>
       </c>
       <c r="DA297" s="213" t="n">
-        <v>0.006860546125885922</v>
+        <v>0.006860546125885682</v>
       </c>
     </row>
     <row r="298" ht="15.75" customHeight="1" thickBot="1">
@@ -59471,10 +59471,10 @@
         </is>
       </c>
       <c r="AK298" s="206" t="n">
-        <v>5.447342876795428</v>
+        <v>5.447342876795427</v>
       </c>
       <c r="AL298" s="207" t="n">
-        <v>7.015258528875047</v>
+        <v>7.015258528875048</v>
       </c>
       <c r="AM298" s="207" t="n">
         <v>13.59238996021134</v>
@@ -59483,7 +59483,7 @@
         <v>17.11580126467504</v>
       </c>
       <c r="AO298" s="208" t="n">
-        <v>17.86531224755396</v>
+        <v>17.86531224755395</v>
       </c>
       <c r="AP298" s="206" t="n">
         <v>134.4108517895829</v>
@@ -59501,7 +59501,7 @@
         <v>126.0462685012848</v>
       </c>
       <c r="AU298" s="207" t="n">
-        <v>139.8581946663783</v>
+        <v>139.8581946663784</v>
       </c>
       <c r="AV298" s="207" t="n">
         <v>140.5583731904682</v>
@@ -59521,10 +59521,10 @@
         </is>
       </c>
       <c r="BB298" s="221" t="n">
-        <v>5.447342876795428</v>
+        <v>5.447342876795427</v>
       </c>
       <c r="BC298" s="222" t="n">
-        <v>7.015258528875047</v>
+        <v>7.015258528875048</v>
       </c>
       <c r="BD298" s="222" t="n">
         <v>13.59238996021134</v>
@@ -59533,7 +59533,7 @@
         <v>17.11580126467504</v>
       </c>
       <c r="BF298" s="214" t="n">
-        <v>17.86531224755396</v>
+        <v>17.86531224755395</v>
       </c>
       <c r="BG298" s="221" t="n">
         <v>134.4108517895829</v>
@@ -59551,7 +59551,7 @@
         <v>126.0462685012848</v>
       </c>
       <c r="BL298" s="222" t="n">
-        <v>139.8581946663783</v>
+        <v>139.8581946663784</v>
       </c>
       <c r="BM298" s="222" t="n">
         <v>140.5583731904682</v>
@@ -59571,10 +59571,10 @@
         </is>
       </c>
       <c r="BS298" s="221" t="n">
-        <v>5.39203807033229</v>
+        <v>5.392038070332289</v>
       </c>
       <c r="BT298" s="222" t="n">
-        <v>6.926227674335453</v>
+        <v>6.926227674335454</v>
       </c>
       <c r="BU298" s="222" t="n">
         <v>13.46950105181097</v>
@@ -59643,19 +59643,19 @@
         <v>10886</v>
       </c>
       <c r="CW298" s="211" t="n">
-        <v>7.168619082312015</v>
+        <v>7.168619082312014</v>
       </c>
       <c r="CX298" s="212" t="n">
-        <v>0.7211276419349758</v>
+        <v>0.7211276419349756</v>
       </c>
       <c r="CY298" s="212" t="n">
-        <v>0.7206836192045893</v>
+        <v>0.7206836192045892</v>
       </c>
       <c r="CZ298" s="212" t="n">
-        <v>0.7167354601305401</v>
+        <v>0.7167354601305398</v>
       </c>
       <c r="DA298" s="213" t="n">
-        <v>0.6922234603787643</v>
+        <v>0.692223460378764</v>
       </c>
     </row>
     <row r="299" ht="15.75" customHeight="1" thickBot="1">
@@ -60522,7 +60522,7 @@
         <v>0</v>
       </c>
       <c r="BX303" s="462" t="n">
-        <v>-0.5924191829311919</v>
+        <v>-0.5924191829311917</v>
       </c>
       <c r="BY303" s="463" t="n">
         <v>-0.0335166388501578</v>
@@ -60531,19 +60531,19 @@
         <v>-0.03385212588450325</v>
       </c>
       <c r="CA303" s="463" t="n">
-        <v>-0.03394822878279808</v>
+        <v>-0.03394822878279807</v>
       </c>
       <c r="CB303" s="464" t="n">
-        <v>-0.0335667393636979</v>
+        <v>-0.03356673936369789</v>
       </c>
       <c r="CC303" s="199" t="n">
-        <v>-14.18542088473202</v>
+        <v>-14.18542088473201</v>
       </c>
       <c r="CD303" s="200" t="n">
         <v>-0.595640620591622</v>
       </c>
       <c r="CE303" s="200" t="n">
-        <v>-0.5936969468402091</v>
+        <v>-0.5936969468402092</v>
       </c>
       <c r="CF303" s="200" t="n">
         <v>-0.5870015811866466</v>
@@ -60777,16 +60777,16 @@
         <v>-0.03016497231113221</v>
       </c>
       <c r="BY304" s="463" t="n">
-        <v>-0.006113542727863165</v>
+        <v>-0.006113542727863166</v>
       </c>
       <c r="BZ304" s="463" t="n">
-        <v>-0.006542854605148969</v>
+        <v>-0.006542854605148968</v>
       </c>
       <c r="CA304" s="463" t="n">
         <v>-0.007043310795919782</v>
       </c>
       <c r="CB304" s="464" t="n">
-        <v>-0.006416450992251358</v>
+        <v>-0.006416450992251359</v>
       </c>
       <c r="CC304" s="197" t="n">
         <v>-0.4300920728546407</v>
@@ -60801,7 +60801,7 @@
         <v>-0.08629103233805677</v>
       </c>
       <c r="CG304" s="198" t="n">
-        <v>-0.07505778532351319</v>
+        <v>-0.0750577853235132</v>
       </c>
     </row>
     <row r="305">
@@ -60941,19 +60941,19 @@
         <v>0</v>
       </c>
       <c r="AU305" s="190" t="n">
-        <v>80.90117486016302</v>
+        <v>80.90117486016304</v>
       </c>
       <c r="AV305" s="190" t="n">
         <v>80.37340786516275</v>
       </c>
       <c r="AW305" s="190" t="n">
-        <v>80.40871203656</v>
+        <v>80.40871203655999</v>
       </c>
       <c r="AX305" s="190" t="n">
         <v>81.20637098159588</v>
       </c>
       <c r="AY305" s="196" t="n">
-        <v>83.35011217207141</v>
+        <v>83.35011217207139</v>
       </c>
       <c r="BA305" s="111" t="inlineStr">
         <is>
@@ -60991,19 +60991,19 @@
         <v>0</v>
       </c>
       <c r="BL305" s="197" t="n">
-        <v>80.90117486016302</v>
+        <v>80.90117486016304</v>
       </c>
       <c r="BM305" s="190" t="n">
         <v>80.37340786516275</v>
       </c>
       <c r="BN305" s="190" t="n">
-        <v>80.40871203656</v>
+        <v>80.40871203655999</v>
       </c>
       <c r="BO305" s="190" t="n">
         <v>81.20637098159588</v>
       </c>
       <c r="BP305" s="198" t="n">
-        <v>83.35011217207141</v>
+        <v>83.35011217207139</v>
       </c>
       <c r="BR305" s="111" t="inlineStr">
         <is>
@@ -61026,13 +61026,13 @@
         <v>15.05560425447307</v>
       </c>
       <c r="BX305" s="462" t="n">
-        <v>0.04532650984064247</v>
+        <v>0.04532650984064246</v>
       </c>
       <c r="BY305" s="463" t="n">
         <v>0.06738687802945442</v>
       </c>
       <c r="BZ305" s="463" t="n">
-        <v>0.09468260417601566</v>
+        <v>0.09468260417601568</v>
       </c>
       <c r="CA305" s="463" t="n">
         <v>0.1316235095328876</v>
@@ -61178,10 +61178,10 @@
         <v>0.006</v>
       </c>
       <c r="AP306" s="220" t="n">
-        <v>0.05530480646313807</v>
+        <v>0.05530480646313809</v>
       </c>
       <c r="AQ306" s="209" t="n">
-        <v>0.08903085453959397</v>
+        <v>0.08903085453959399</v>
       </c>
       <c r="AR306" s="209" t="n">
         <v>0.1228889084003697</v>
@@ -61202,7 +61202,7 @@
         <v>17.25272604828146</v>
       </c>
       <c r="AX306" s="209" t="n">
-        <v>14.57745381771262</v>
+        <v>14.57745381771261</v>
       </c>
       <c r="AY306" s="210" t="n">
         <v>14.74666186186718</v>
@@ -61228,10 +61228,10 @@
         <v>0.006</v>
       </c>
       <c r="BG306" s="211" t="n">
-        <v>0.05530480646313807</v>
+        <v>0.05530480646313809</v>
       </c>
       <c r="BH306" s="212" t="n">
-        <v>0.08903085453959397</v>
+        <v>0.08903085453959399</v>
       </c>
       <c r="BI306" s="212" t="n">
         <v>0.1228889084003697</v>
@@ -61252,7 +61252,7 @@
         <v>17.25272604828146</v>
       </c>
       <c r="BO306" s="212" t="n">
-        <v>14.57745381771262</v>
+        <v>14.57745381771261</v>
       </c>
       <c r="BP306" s="213" t="n">
         <v>14.74666186186718</v>
@@ -61278,34 +61278,34 @@
         <v>0</v>
       </c>
       <c r="BX306" s="466" t="n">
-        <v>-0.000280135902289619</v>
+        <v>-0.0002801359022896091</v>
       </c>
       <c r="BY306" s="467" t="n">
-        <v>-0.0002812193515633527</v>
+        <v>-0.0002812193515633428</v>
       </c>
       <c r="BZ306" s="467" t="n">
-        <v>-0.0003821449695580503</v>
+        <v>-0.000382144969558037</v>
       </c>
       <c r="CA306" s="467" t="n">
-        <v>-0.0004614854525082726</v>
+        <v>-0.0004614854525082566</v>
       </c>
       <c r="CB306" s="468" t="n">
-        <v>-0.0004654435958074439</v>
+        <v>-0.0004654435958074276</v>
       </c>
       <c r="CC306" s="212" t="n">
-        <v>-0.006237673897676241</v>
+        <v>-0.006237673897676023</v>
       </c>
       <c r="CD306" s="212" t="n">
-        <v>-0.006399742525335365</v>
+        <v>-0.006399742525335139</v>
       </c>
       <c r="CE306" s="212" t="n">
-        <v>-0.006595561006082391</v>
+        <v>-0.006595561006082162</v>
       </c>
       <c r="CF306" s="212" t="n">
-        <v>-0.006730385982625002</v>
+        <v>-0.006730385982624768</v>
       </c>
       <c r="CG306" s="213" t="n">
-        <v>-0.006866932520401992</v>
+        <v>-0.006866932520401752</v>
       </c>
     </row>
     <row r="307" ht="15.75" customHeight="1" thickBot="1">
@@ -61430,10 +61430,10 @@
         <v>0.006</v>
       </c>
       <c r="AP307" s="206" t="n">
-        <v>0.05530480646313807</v>
+        <v>0.05530480646313809</v>
       </c>
       <c r="AQ307" s="207" t="n">
-        <v>0.08903085453959397</v>
+        <v>0.08903085453959399</v>
       </c>
       <c r="AR307" s="207" t="n">
         <v>0.1228889084003697</v>
@@ -61445,7 +61445,7 @@
         <v>0.1945048157619551</v>
       </c>
       <c r="AU307" s="207" t="n">
-        <v>134.466156596046</v>
+        <v>134.4661565960461</v>
       </c>
       <c r="AV307" s="207" t="n">
         <v>133.6321455161328</v>
@@ -61457,7 +61457,7 @@
         <v>124.6916206509199</v>
       </c>
       <c r="AY307" s="208" t="n">
-        <v>126.2407733170468</v>
+        <v>126.2407733170467</v>
       </c>
       <c r="BA307" s="155" t="inlineStr">
         <is>
@@ -61480,10 +61480,10 @@
         <v>0.006</v>
       </c>
       <c r="BG307" s="221" t="n">
-        <v>0.05530480646313807</v>
+        <v>0.05530480646313809</v>
       </c>
       <c r="BH307" s="222" t="n">
-        <v>0.08903085453959397</v>
+        <v>0.08903085453959399</v>
       </c>
       <c r="BI307" s="222" t="n">
         <v>0.1228889084003697</v>
@@ -61495,7 +61495,7 @@
         <v>0.1945048157619551</v>
       </c>
       <c r="BL307" s="222" t="n">
-        <v>134.466156596046</v>
+        <v>134.4661565960461</v>
       </c>
       <c r="BM307" s="222" t="n">
         <v>133.6321455161328</v>
@@ -61507,7 +61507,7 @@
         <v>124.6916206509199</v>
       </c>
       <c r="BP307" s="214" t="n">
-        <v>126.2407733170468</v>
+        <v>126.2407733170467</v>
       </c>
       <c r="BR307" s="155" t="inlineStr">
         <is>
@@ -61530,7 +61530,7 @@
         <v>15.05560425447307</v>
       </c>
       <c r="BX307" s="466" t="n">
-        <v>-0.0772607711790706</v>
+        <v>-0.07726077117907054</v>
       </c>
       <c r="BY307" s="467" t="n">
         <v>0.03526079893947397</v>
@@ -61539,13 +61539,13 @@
         <v>0.05414685943907789</v>
       </c>
       <c r="CA307" s="467" t="n">
-        <v>0.07988740171907742</v>
+        <v>0.07988740171907741</v>
       </c>
       <c r="CB307" s="468" t="n">
         <v>0.1130777023617176</v>
       </c>
       <c r="CC307" s="212" t="n">
-        <v>-10.94281199468462</v>
+        <v>-10.94281199468461</v>
       </c>
       <c r="CD307" s="212" t="n">
         <v>4.737403751686853</v>
@@ -63063,10 +63063,10 @@
         </is>
       </c>
       <c r="AK315" s="220" t="n">
-        <v>5.39203807033229</v>
+        <v>5.392038070332289</v>
       </c>
       <c r="AL315" s="209" t="n">
-        <v>6.926227674335453</v>
+        <v>6.926227674335454</v>
       </c>
       <c r="AM315" s="209" t="n">
         <v>13.46950105181097</v>
@@ -63078,7 +63078,7 @@
         <v>17.670807431792</v>
       </c>
       <c r="AP315" s="489" t="n">
-        <v>0.196993470374992</v>
+        <v>0.1969934703749919</v>
       </c>
       <c r="AQ315" s="490" t="n">
         <v>0.236387437764799</v>
@@ -63087,13 +63087,13 @@
         <v>0.442428536053965</v>
       </c>
       <c r="AS315" s="490" t="n">
-        <v>0.5427457743385102</v>
+        <v>0.5427457743385103</v>
       </c>
       <c r="AT315" s="491" t="n">
-        <v>0.5511013856670295</v>
+        <v>0.5511013856670294</v>
       </c>
       <c r="AU315" s="490" t="n">
-        <v>0.194993470374992</v>
+        <v>0.1949934703749919</v>
       </c>
       <c r="AV315" s="490" t="n">
         <v>0.233387437764799</v>
@@ -63105,7 +63105,7 @@
         <v>0.5377457743385102</v>
       </c>
       <c r="AY315" s="491" t="n">
-        <v>0.5451013856670295</v>
+        <v>0.5451013856670294</v>
       </c>
       <c r="BA315" s="111" t="inlineStr">
         <is>
@@ -63113,10 +63113,10 @@
         </is>
       </c>
       <c r="BB315" s="211" t="n">
-        <v>5.39203807033229</v>
+        <v>5.392038070332289</v>
       </c>
       <c r="BC315" s="212" t="n">
-        <v>6.926227674335453</v>
+        <v>6.926227674335454</v>
       </c>
       <c r="BD315" s="212" t="n">
         <v>13.46950105181097</v>
@@ -63128,7 +63128,7 @@
         <v>17.670807431792</v>
       </c>
       <c r="BG315" s="466" t="n">
-        <v>0.196993470374992</v>
+        <v>0.1969934703749919</v>
       </c>
       <c r="BH315" s="467" t="n">
         <v>0.236387437764799</v>
@@ -63137,13 +63137,13 @@
         <v>0.442428536053965</v>
       </c>
       <c r="BJ315" s="467" t="n">
-        <v>0.5427457743385102</v>
+        <v>0.5427457743385103</v>
       </c>
       <c r="BK315" s="468" t="n">
-        <v>0.5511013856670295</v>
+        <v>0.5511013856670294</v>
       </c>
       <c r="BL315" s="467" t="n">
-        <v>0.194993470374992</v>
+        <v>0.1949934703749919</v>
       </c>
       <c r="BM315" s="467" t="n">
         <v>0.233387437764799</v>
@@ -63155,7 +63155,7 @@
         <v>0.5377457743385102</v>
       </c>
       <c r="BP315" s="468" t="n">
-        <v>0.5451013856670295</v>
+        <v>0.5451013856670294</v>
       </c>
       <c r="BR315" s="111" t="inlineStr">
         <is>
@@ -63178,7 +63178,7 @@
         <v>0</v>
       </c>
       <c r="BX315" s="466" t="n">
-        <v>0.1949495193812373</v>
+        <v>0.1949495193812372</v>
       </c>
       <c r="BY315" s="467" t="n">
         <v>0.2333371476179352</v>
@@ -63187,10 +63187,10 @@
         <v>0.4383345046533436</v>
       </c>
       <c r="CA315" s="467" t="n">
-        <v>0.5376311378315256</v>
+        <v>0.5376311378315257</v>
       </c>
       <c r="CB315" s="468" t="n">
-        <v>0.5449860496456489</v>
+        <v>0.5449860496456488</v>
       </c>
       <c r="CC315" s="492" t="n">
         <v>0</v>
@@ -63236,10 +63236,10 @@
         <v>0.03894904327765471</v>
       </c>
       <c r="I316" s="495" t="n">
-        <v>0.04990992972982684</v>
+        <v>0.04990992972982685</v>
       </c>
       <c r="J316" s="495" t="n">
-        <v>0.09650278609956181</v>
+        <v>0.09650278609956182</v>
       </c>
       <c r="K316" s="495" t="n">
         <v>0.1208318545291325</v>
@@ -63248,13 +63248,13 @@
         <v>0.1241408936973136</v>
       </c>
       <c r="M316" s="495" t="n">
-        <v>0.03855360841168162</v>
+        <v>0.03855360841168161</v>
       </c>
       <c r="N316" s="495" t="n">
-        <v>0.04927652132790297</v>
+        <v>0.04927652132790298</v>
       </c>
       <c r="O316" s="495" t="n">
-        <v>0.0956303036239939</v>
+        <v>0.09563030362399393</v>
       </c>
       <c r="P316" s="495" t="n">
         <v>0.119718701186977</v>
@@ -63286,10 +63286,10 @@
         <v>0.03894904327765471</v>
       </c>
       <c r="Z316" s="498" t="n">
-        <v>0.04990992972982684</v>
+        <v>0.04990992972982685</v>
       </c>
       <c r="AA316" s="498" t="n">
-        <v>0.09650278609956181</v>
+        <v>0.09650278609956182</v>
       </c>
       <c r="AB316" s="498" t="n">
         <v>0.1208318545291325</v>
@@ -63298,13 +63298,13 @@
         <v>0.1241408936973136</v>
       </c>
       <c r="AD316" s="498" t="n">
-        <v>0.03855360841168162</v>
+        <v>0.03855360841168161</v>
       </c>
       <c r="AE316" s="498" t="n">
-        <v>0.04927652132790297</v>
+        <v>0.04927652132790298</v>
       </c>
       <c r="AF316" s="498" t="n">
-        <v>0.0956303036239939</v>
+        <v>0.09563030362399393</v>
       </c>
       <c r="AG316" s="498" t="n">
         <v>0.119718701186977</v>
@@ -63318,10 +63318,10 @@
         </is>
       </c>
       <c r="AK316" s="206" t="n">
-        <v>5.39203807033229</v>
+        <v>5.392038070332289</v>
       </c>
       <c r="AL316" s="207" t="n">
-        <v>6.926227674335453</v>
+        <v>6.926227674335454</v>
       </c>
       <c r="AM316" s="207" t="n">
         <v>13.46950105181097</v>
@@ -63333,13 +63333,13 @@
         <v>17.670807431792</v>
       </c>
       <c r="AP316" s="500" t="n">
-        <v>0.03894904327765472</v>
+        <v>0.0389490432776547</v>
       </c>
       <c r="AQ316" s="501" t="n">
-        <v>0.04990992972982684</v>
+        <v>0.04990992972982685</v>
       </c>
       <c r="AR316" s="501" t="n">
-        <v>0.09650278609956181</v>
+        <v>0.09650278609956182</v>
       </c>
       <c r="AS316" s="501" t="n">
         <v>0.1208318545291325</v>
@@ -63348,16 +63348,16 @@
         <v>0.1241408936973136</v>
       </c>
       <c r="AU316" s="501" t="n">
-        <v>0.03855360841168162</v>
+        <v>0.0385536084116816</v>
       </c>
       <c r="AV316" s="501" t="n">
         <v>0.04927652132790297</v>
       </c>
       <c r="AW316" s="501" t="n">
-        <v>0.0956303036239939</v>
+        <v>0.09563030362399393</v>
       </c>
       <c r="AX316" s="501" t="n">
-        <v>0.1197187011869771</v>
+        <v>0.119718701186977</v>
       </c>
       <c r="AY316" s="502" t="n">
         <v>0.1227893359230896</v>
@@ -63368,10 +63368,10 @@
         </is>
       </c>
       <c r="BB316" s="221" t="n">
-        <v>5.39203807033229</v>
+        <v>5.392038070332289</v>
       </c>
       <c r="BC316" s="222" t="n">
-        <v>6.926227674335453</v>
+        <v>6.926227674335454</v>
       </c>
       <c r="BD316" s="222" t="n">
         <v>13.46950105181097</v>
@@ -63383,13 +63383,13 @@
         <v>17.670807431792</v>
       </c>
       <c r="BG316" s="503" t="n">
-        <v>0.03894904327765472</v>
+        <v>0.0389490432776547</v>
       </c>
       <c r="BH316" s="504" t="n">
-        <v>0.04990992972982684</v>
+        <v>0.04990992972982685</v>
       </c>
       <c r="BI316" s="504" t="n">
-        <v>0.09650278609956181</v>
+        <v>0.09650278609956182</v>
       </c>
       <c r="BJ316" s="504" t="n">
         <v>0.1208318545291325</v>
@@ -63398,16 +63398,16 @@
         <v>0.1241408936973136</v>
       </c>
       <c r="BL316" s="504" t="n">
-        <v>0.03855360841168162</v>
+        <v>0.0385536084116816</v>
       </c>
       <c r="BM316" s="504" t="n">
         <v>0.04927652132790297</v>
       </c>
       <c r="BN316" s="504" t="n">
-        <v>0.0956303036239939</v>
+        <v>0.09563030362399393</v>
       </c>
       <c r="BO316" s="504" t="n">
-        <v>0.1197187011869771</v>
+        <v>0.119718701186977</v>
       </c>
       <c r="BP316" s="505" t="n">
         <v>0.1227893359230896</v>
@@ -63433,13 +63433,13 @@
         <v>0</v>
       </c>
       <c r="BX316" s="503" t="n">
-        <v>0.03667384154531689</v>
+        <v>0.03667384154531688</v>
       </c>
       <c r="BY316" s="504" t="n">
-        <v>0.04902500103360277</v>
+        <v>0.04902500103360278</v>
       </c>
       <c r="BZ316" s="504" t="n">
-        <v>0.09514348438928937</v>
+        <v>0.09514348438928938</v>
       </c>
       <c r="CA316" s="504" t="n">
         <v>0.1191159846016613</v>
@@ -64692,7 +64692,7 @@
         </is>
       </c>
       <c r="AK326" s="435" t="n">
-        <v>98753.83280399092</v>
+        <v>98753.83280399091</v>
       </c>
       <c r="AL326" s="408" t="n">
         <v>182926.8615295583</v>
@@ -64716,10 +64716,10 @@
         <v>23846.44159897525</v>
       </c>
       <c r="AS326" s="411" t="n">
-        <v>24329.20990562129</v>
+        <v>24329.2099056213</v>
       </c>
       <c r="AT326" s="412" t="n">
-        <v>25263.26545607488</v>
+        <v>25263.26545607489</v>
       </c>
       <c r="BA326" s="111" t="inlineStr">
         <is>
@@ -64727,7 +64727,7 @@
         </is>
       </c>
       <c r="BB326" s="419" t="n">
-        <v>98753.83280399092</v>
+        <v>98753.83280399091</v>
       </c>
       <c r="BC326" s="420" t="n">
         <v>182926.8615295583</v>
@@ -64751,10 +64751,10 @@
         <v>23846.44159897525</v>
       </c>
       <c r="BJ326" s="417" t="n">
-        <v>24329.20990562129</v>
+        <v>24329.2099056213</v>
       </c>
       <c r="BK326" s="418" t="n">
-        <v>25263.26545607488</v>
+        <v>25263.26545607489</v>
       </c>
       <c r="BR326" s="111" t="inlineStr">
         <is>
@@ -64762,7 +64762,7 @@
         </is>
       </c>
       <c r="BS326" s="419" t="n">
-        <v>97751.22258938832</v>
+        <v>97751.22258938829</v>
       </c>
       <c r="BT326" s="420" t="n">
         <v>180605.331291836</v>
@@ -64774,7 +64774,7 @@
         <v>412577.743285646</v>
       </c>
       <c r="BW326" s="421" t="n">
-        <v>446422.2989725421</v>
+        <v>446422.2989725422</v>
       </c>
       <c r="BX326" s="416" t="n">
         <v>18128.807941329</v>
@@ -64786,10 +64786,10 @@
         <v>23846.44159897525</v>
       </c>
       <c r="CA326" s="417" t="n">
-        <v>24329.20990562129</v>
+        <v>24329.2099056213</v>
       </c>
       <c r="CB326" s="418" t="n">
-        <v>25263.26545607488</v>
+        <v>25263.26545607489</v>
       </c>
       <c r="CI326" s="211" t="n">
         <v>0</v>
@@ -64887,7 +64887,7 @@
         </is>
       </c>
       <c r="AK327" s="435" t="n">
-        <v>98753.83280399092</v>
+        <v>98753.83280399091</v>
       </c>
       <c r="AL327" s="408" t="n">
         <v>182926.8615295583</v>
@@ -64911,10 +64911,10 @@
         <v>23846.44159897525</v>
       </c>
       <c r="AS327" s="437" t="n">
-        <v>24329.20990562129</v>
+        <v>24329.2099056213</v>
       </c>
       <c r="AT327" s="438" t="n">
-        <v>25263.26545607488</v>
+        <v>25263.26545607489</v>
       </c>
       <c r="BA327" s="155" t="inlineStr">
         <is>
@@ -64922,7 +64922,7 @@
         </is>
       </c>
       <c r="BB327" s="439" t="n">
-        <v>98753.83280399092</v>
+        <v>98753.83280399091</v>
       </c>
       <c r="BC327" s="440" t="n">
         <v>182926.8615295583</v>
@@ -64946,10 +64946,10 @@
         <v>23846.44159897525</v>
       </c>
       <c r="BJ327" s="443" t="n">
-        <v>24329.20990562129</v>
+        <v>24329.2099056213</v>
       </c>
       <c r="BK327" s="444" t="n">
-        <v>25263.26545607488</v>
+        <v>25263.26545607489</v>
       </c>
       <c r="BR327" s="155" t="inlineStr">
         <is>
@@ -64957,7 +64957,7 @@
         </is>
       </c>
       <c r="BS327" s="439" t="n">
-        <v>97751.22258938832</v>
+        <v>97751.22258938829</v>
       </c>
       <c r="BT327" s="440" t="n">
         <v>180605.331291836</v>
@@ -64969,7 +64969,7 @@
         <v>412577.743285646</v>
       </c>
       <c r="BW327" s="441" t="n">
-        <v>446422.2989725421</v>
+        <v>446422.2989725422</v>
       </c>
       <c r="BX327" s="442" t="n">
         <v>18128.807941329</v>
@@ -64981,10 +64981,10 @@
         <v>23846.44159897525</v>
       </c>
       <c r="CA327" s="443" t="n">
-        <v>24329.20990562129</v>
+        <v>24329.2099056213</v>
       </c>
       <c r="CB327" s="444" t="n">
-        <v>25263.26545607488</v>
+        <v>25263.26545607489</v>
       </c>
       <c r="CI327" s="349" t="n">
         <v>0</v>
@@ -67590,7 +67590,7 @@
         </is>
       </c>
       <c r="AK344" s="435" t="n">
-        <v>98753.83280399092</v>
+        <v>98753.83280399091</v>
       </c>
       <c r="AL344" s="408" t="n">
         <v>182926.8615295583</v>
@@ -67614,10 +67614,10 @@
         <v>23846.44159897525</v>
       </c>
       <c r="AS344" s="411" t="n">
-        <v>24329.20990562129</v>
+        <v>24329.2099056213</v>
       </c>
       <c r="AT344" s="412" t="n">
-        <v>25263.26545607488</v>
+        <v>25263.26545607489</v>
       </c>
       <c r="BA344" s="111" t="inlineStr">
         <is>
@@ -67625,7 +67625,7 @@
         </is>
       </c>
       <c r="BB344" s="419" t="n">
-        <v>98753.83280399092</v>
+        <v>98753.83280399091</v>
       </c>
       <c r="BC344" s="420" t="n">
         <v>182926.8615295583</v>
@@ -67649,10 +67649,10 @@
         <v>23846.44159897525</v>
       </c>
       <c r="BJ344" s="417" t="n">
-        <v>24329.20990562129</v>
+        <v>24329.2099056213</v>
       </c>
       <c r="BK344" s="418" t="n">
-        <v>25263.26545607488</v>
+        <v>25263.26545607489</v>
       </c>
       <c r="BR344" s="111" t="inlineStr">
         <is>
@@ -67660,7 +67660,7 @@
         </is>
       </c>
       <c r="BS344" s="419" t="n">
-        <v>97751.22258938832</v>
+        <v>97751.22258938829</v>
       </c>
       <c r="BT344" s="420" t="n">
         <v>180605.331291836</v>
@@ -67672,7 +67672,7 @@
         <v>412577.743285646</v>
       </c>
       <c r="BW344" s="421" t="n">
-        <v>446422.2989725421</v>
+        <v>446422.2989725422</v>
       </c>
       <c r="BX344" s="416" t="n">
         <v>18128.807941329</v>
@@ -67684,10 +67684,10 @@
         <v>23846.44159897525</v>
       </c>
       <c r="CA344" s="417" t="n">
-        <v>24329.20990562129</v>
+        <v>24329.2099056213</v>
       </c>
       <c r="CB344" s="418" t="n">
-        <v>25263.26545607488</v>
+        <v>25263.26545607489</v>
       </c>
       <c r="CI344" s="211" t="n">
         <v>0</v>
@@ -67785,7 +67785,7 @@
         </is>
       </c>
       <c r="AK345" s="435" t="n">
-        <v>98753.83280399092</v>
+        <v>98753.83280399091</v>
       </c>
       <c r="AL345" s="408" t="n">
         <v>182926.8615295583</v>
@@ -67809,10 +67809,10 @@
         <v>23846.44159897525</v>
       </c>
       <c r="AS345" s="437" t="n">
-        <v>24329.20990562129</v>
+        <v>24329.2099056213</v>
       </c>
       <c r="AT345" s="438" t="n">
-        <v>25263.26545607488</v>
+        <v>25263.26545607489</v>
       </c>
       <c r="BA345" s="155" t="inlineStr">
         <is>
@@ -67820,7 +67820,7 @@
         </is>
       </c>
       <c r="BB345" s="439" t="n">
-        <v>98753.83280399092</v>
+        <v>98753.83280399091</v>
       </c>
       <c r="BC345" s="440" t="n">
         <v>182926.8615295583</v>
@@ -67844,10 +67844,10 @@
         <v>23846.44159897525</v>
       </c>
       <c r="BJ345" s="443" t="n">
-        <v>24329.20990562129</v>
+        <v>24329.2099056213</v>
       </c>
       <c r="BK345" s="444" t="n">
-        <v>25263.26545607488</v>
+        <v>25263.26545607489</v>
       </c>
       <c r="BR345" s="155" t="inlineStr">
         <is>
@@ -67855,7 +67855,7 @@
         </is>
       </c>
       <c r="BS345" s="439" t="n">
-        <v>97751.22258938832</v>
+        <v>97751.22258938829</v>
       </c>
       <c r="BT345" s="440" t="n">
         <v>180605.331291836</v>
@@ -67867,7 +67867,7 @@
         <v>412577.743285646</v>
       </c>
       <c r="BW345" s="441" t="n">
-        <v>446422.2989725421</v>
+        <v>446422.2989725422</v>
       </c>
       <c r="BX345" s="442" t="n">
         <v>18128.807941329</v>
@@ -67879,10 +67879,10 @@
         <v>23846.44159897525</v>
       </c>
       <c r="CA345" s="443" t="n">
-        <v>24329.20990562129</v>
+        <v>24329.2099056213</v>
       </c>
       <c r="CB345" s="444" t="n">
-        <v>25263.26545607488</v>
+        <v>25263.26545607489</v>
       </c>
       <c r="CI345" s="349" t="n">
         <v>0</v>
@@ -68425,16 +68425,16 @@
         <v>3204.861308971688</v>
       </c>
       <c r="AL350" s="368" t="n">
-        <v>3254.321893974604</v>
+        <v>3254.321893974605</v>
       </c>
       <c r="AM350" s="368" t="n">
         <v>3301.672431208349</v>
       </c>
       <c r="AN350" s="368" t="n">
-        <v>3345.010306312381</v>
+        <v>3345.010306312382</v>
       </c>
       <c r="AO350" s="380" t="n">
-        <v>3391.381220487522</v>
+        <v>3391.381220487523</v>
       </c>
       <c r="AP350" s="381" t="n">
         <v>183.6360911050139</v>
@@ -68460,16 +68460,16 @@
         <v>3204.861308971688</v>
       </c>
       <c r="BC350" s="375" t="n">
-        <v>3254.321893974604</v>
+        <v>3254.321893974605</v>
       </c>
       <c r="BD350" s="375" t="n">
         <v>3301.672431208349</v>
       </c>
       <c r="BE350" s="375" t="n">
-        <v>3345.010306312381</v>
+        <v>3345.010306312382</v>
       </c>
       <c r="BF350" s="392" t="n">
-        <v>3391.381220487522</v>
+        <v>3391.381220487523</v>
       </c>
       <c r="BG350" s="386" t="n">
         <v>183.6360911050139</v>
@@ -68495,19 +68495,19 @@
         <v>11005.84284323029</v>
       </c>
       <c r="BT350" s="375" t="n">
-        <v>3971.299184621567</v>
+        <v>3971.299184621568</v>
       </c>
       <c r="BU350" s="375" t="n">
-        <v>4027.73397970867</v>
+        <v>4027.733979708671</v>
       </c>
       <c r="BV350" s="375" t="n">
-        <v>4067.985565486489</v>
+        <v>4067.98556548649</v>
       </c>
       <c r="BW350" s="392" t="n">
         <v>4100.881810478877</v>
       </c>
       <c r="BX350" s="386" t="n">
-        <v>459.6319332106141</v>
+        <v>459.6319332106139</v>
       </c>
       <c r="BY350" s="372" t="n">
         <v>223.4646126126869</v>
@@ -68601,7 +68601,7 @@
         </is>
       </c>
       <c r="AK351" s="506" t="n">
-        <v>2074.032206997822</v>
+        <v>2074.032206997823</v>
       </c>
       <c r="AL351" s="368" t="n">
         <v>2111.869947368715</v>
@@ -68616,10 +68616,10 @@
         <v>2160.882642602675</v>
       </c>
       <c r="AP351" s="381" t="n">
-        <v>149.7239363924464</v>
+        <v>149.7239363924465</v>
       </c>
       <c r="AQ351" s="372" t="n">
-        <v>158.8499803385697</v>
+        <v>158.8499803385698</v>
       </c>
       <c r="AR351" s="372" t="n">
         <v>167.8732314029652</v>
@@ -68636,7 +68636,7 @@
         </is>
       </c>
       <c r="BB351" s="391" t="n">
-        <v>2074.032206997822</v>
+        <v>2074.032206997823</v>
       </c>
       <c r="BC351" s="375" t="n">
         <v>2111.869947368715</v>
@@ -68651,10 +68651,10 @@
         <v>2160.882642602675</v>
       </c>
       <c r="BG351" s="386" t="n">
-        <v>149.7239363924464</v>
+        <v>149.7239363924465</v>
       </c>
       <c r="BH351" s="372" t="n">
-        <v>158.8499803385697</v>
+        <v>158.8499803385698</v>
       </c>
       <c r="BI351" s="372" t="n">
         <v>167.8732314029652</v>
@@ -68671,10 +68671,10 @@
         </is>
       </c>
       <c r="BS351" s="391" t="n">
-        <v>3060.302267409851</v>
+        <v>3060.302267409852</v>
       </c>
       <c r="BT351" s="375" t="n">
-        <v>2343.584759410195</v>
+        <v>2343.584759410196</v>
       </c>
       <c r="BU351" s="375" t="n">
         <v>2390.968356595467</v>
@@ -68689,7 +68689,7 @@
         <v>214.637606658035</v>
       </c>
       <c r="BY351" s="372" t="n">
-        <v>175.2143618113035</v>
+        <v>175.2143618113036</v>
       </c>
       <c r="BZ351" s="372" t="n">
         <v>186.507815298339</v>
@@ -68698,7 +68698,7 @@
         <v>197.5546038198526</v>
       </c>
       <c r="CB351" s="387" t="n">
-        <v>205.6042943747987</v>
+        <v>205.6042943747988</v>
       </c>
       <c r="CI351" s="225" t="n"/>
       <c r="CJ351" s="225" t="n"/>
@@ -68789,22 +68789,22 @@
         <v>42128.44967839478</v>
       </c>
       <c r="AN352" s="368" t="n">
-        <v>51798.10656705894</v>
+        <v>51798.10656705895</v>
       </c>
       <c r="AO352" s="380" t="n">
-        <v>65974.12315801576</v>
+        <v>65974.12315801575</v>
       </c>
       <c r="AP352" s="381" t="n">
-        <v>378.4351032632466</v>
+        <v>378.4351032632464</v>
       </c>
       <c r="AQ352" s="372" t="n">
         <v>440.3801403055851</v>
       </c>
       <c r="AR352" s="372" t="n">
-        <v>523.9289202796823</v>
+        <v>523.9289202796824</v>
       </c>
       <c r="AS352" s="372" t="n">
-        <v>637.8576697978308</v>
+        <v>637.8576697978309</v>
       </c>
       <c r="AT352" s="382" t="n">
         <v>791.5301064240449</v>
@@ -68824,22 +68824,22 @@
         <v>42128.44967839478</v>
       </c>
       <c r="BE352" s="375" t="n">
-        <v>51798.10656705894</v>
+        <v>51798.10656705895</v>
       </c>
       <c r="BF352" s="392" t="n">
-        <v>65974.12315801576</v>
+        <v>65974.12315801575</v>
       </c>
       <c r="BG352" s="386" t="n">
-        <v>378.4351032632466</v>
+        <v>378.4351032632464</v>
       </c>
       <c r="BH352" s="372" t="n">
         <v>440.3801403055851</v>
       </c>
       <c r="BI352" s="372" t="n">
-        <v>523.9289202796823</v>
+        <v>523.9289202796824</v>
       </c>
       <c r="BJ352" s="372" t="n">
-        <v>637.8576697978308</v>
+        <v>637.8576697978309</v>
       </c>
       <c r="BK352" s="387" t="n">
         <v>791.5301064240449</v>
@@ -68859,13 +68859,13 @@
         <v>42320.33539807169</v>
       </c>
       <c r="BV352" s="375" t="n">
-        <v>52001.74829620225</v>
+        <v>52001.74829620226</v>
       </c>
       <c r="BW352" s="392" t="n">
-        <v>66182.01770698407</v>
+        <v>66182.01770698406</v>
       </c>
       <c r="BX352" s="386" t="n">
-        <v>384.3349083439446</v>
+        <v>384.3349083439444</v>
       </c>
       <c r="BY352" s="372" t="n">
         <v>442.2360020397605</v>
@@ -68874,10 +68874,10 @@
         <v>525.8232162336361</v>
       </c>
       <c r="CA352" s="372" t="n">
-        <v>639.7726191430498</v>
+        <v>639.77261914305</v>
       </c>
       <c r="CB352" s="387" t="n">
-        <v>793.3130728849978</v>
+        <v>793.3130728849977</v>
       </c>
       <c r="CI352" s="225" t="n"/>
       <c r="CJ352" s="225" t="n"/>
@@ -68977,7 +68977,7 @@
         <v>17639.01218549907</v>
       </c>
       <c r="AQ353" s="411" t="n">
-        <v>18384.23602279761</v>
+        <v>18384.2360227976</v>
       </c>
       <c r="AR353" s="411" t="n">
         <v>18338.57521310579</v>
@@ -69012,7 +69012,7 @@
         <v>17639.01218549907</v>
       </c>
       <c r="BH353" s="417" t="n">
-        <v>18384.23602279761</v>
+        <v>18384.2360227976</v>
       </c>
       <c r="BI353" s="417" t="n">
         <v>18338.57521310579</v>
@@ -69029,7 +69029,7 @@
         </is>
       </c>
       <c r="BS353" s="419" t="n">
-        <v>392870.6611876372</v>
+        <v>392870.6611876373</v>
       </c>
       <c r="BT353" s="420" t="n">
         <v>418457.6758984351</v>
@@ -69044,16 +69044,16 @@
         <v>270025.4799898149</v>
       </c>
       <c r="BX353" s="416" t="n">
-        <v>17643.94531684612</v>
+        <v>17643.94531684611</v>
       </c>
       <c r="BY353" s="417" t="n">
-        <v>18387.98917409555</v>
+        <v>18387.98917409554</v>
       </c>
       <c r="BZ353" s="417" t="n">
         <v>18343.88673948644</v>
       </c>
       <c r="CA353" s="417" t="n">
-        <v>17860.9990542155</v>
+        <v>17860.99905421551</v>
       </c>
       <c r="CB353" s="418" t="n">
         <v>18302.44144567959</v>
@@ -69071,7 +69071,7 @@
         <v>427119.3209384317</v>
       </c>
       <c r="D354" s="425" t="n">
-        <v>457098.1422544294</v>
+        <v>457098.1422544293</v>
       </c>
       <c r="E354" s="425" t="n">
         <v>361598.9702909656</v>
@@ -69106,7 +69106,7 @@
         <v>427119.3209384317</v>
       </c>
       <c r="U354" s="430" t="n">
-        <v>457098.1422544294</v>
+        <v>457098.1422544293</v>
       </c>
       <c r="V354" s="430" t="n">
         <v>361598.9702909656</v>
@@ -69138,31 +69138,31 @@
         </is>
       </c>
       <c r="AK354" s="435" t="n">
-        <v>427570.0681558872</v>
+        <v>427570.0681558873</v>
       </c>
       <c r="AL354" s="408" t="n">
-        <v>457378.9569738114</v>
+        <v>457378.9569738113</v>
       </c>
       <c r="AM354" s="408" t="n">
         <v>361705.1091922024</v>
       </c>
       <c r="AN354" s="408" t="n">
-        <v>314741.6778722474</v>
+        <v>314741.6778722473</v>
       </c>
       <c r="AO354" s="409" t="n">
-        <v>337757.0494690707</v>
+        <v>337757.0494690706</v>
       </c>
       <c r="AP354" s="436" t="n">
-        <v>3181.068064543169</v>
+        <v>3181.068064543168</v>
       </c>
       <c r="AQ354" s="437" t="n">
-        <v>3424.953492606781</v>
+        <v>3424.95349260678</v>
       </c>
       <c r="AR354" s="437" t="n">
         <v>2842.312675205743</v>
       </c>
       <c r="AS354" s="437" t="n">
-        <v>2527.356565481375</v>
+        <v>2527.356565481374</v>
       </c>
       <c r="AT354" s="438" t="n">
         <v>2679.627516824331</v>
@@ -69173,31 +69173,31 @@
         </is>
       </c>
       <c r="BB354" s="439" t="n">
-        <v>427570.0681558872</v>
+        <v>427570.0681558873</v>
       </c>
       <c r="BC354" s="440" t="n">
-        <v>457378.9569738114</v>
+        <v>457378.9569738113</v>
       </c>
       <c r="BD354" s="440" t="n">
         <v>361705.1091922024</v>
       </c>
       <c r="BE354" s="440" t="n">
-        <v>314741.6778722474</v>
+        <v>314741.6778722473</v>
       </c>
       <c r="BF354" s="441" t="n">
-        <v>337757.0494690707</v>
+        <v>337757.0494690706</v>
       </c>
       <c r="BG354" s="442" t="n">
-        <v>3181.068064543169</v>
+        <v>3181.068064543168</v>
       </c>
       <c r="BH354" s="443" t="n">
-        <v>3424.953492606781</v>
+        <v>3424.95349260678</v>
       </c>
       <c r="BI354" s="443" t="n">
         <v>2842.312675205743</v>
       </c>
       <c r="BJ354" s="443" t="n">
-        <v>2527.356565481375</v>
+        <v>2527.356565481374</v>
       </c>
       <c r="BK354" s="444" t="n">
         <v>2679.627516824331</v>
@@ -69214,7 +69214,7 @@
         <v>460350.0632418979</v>
       </c>
       <c r="BU354" s="440" t="n">
-        <v>365341.986136055</v>
+        <v>365341.9861360549</v>
       </c>
       <c r="BV354" s="440" t="n">
         <v>318978.0609888115</v>
@@ -69232,10 +69232,10 @@
         <v>2851.98614413195</v>
       </c>
       <c r="CA354" s="443" t="n">
-        <v>2543.515208080338</v>
+        <v>2543.515208080339</v>
       </c>
       <c r="CB354" s="444" t="n">
-        <v>2699.955785295573</v>
+        <v>2699.955785295574</v>
       </c>
       <c r="CI354" s="225" t="n"/>
       <c r="CJ354" s="225" t="n"/>
@@ -71116,16 +71116,16 @@
         <v>3204.861308971688</v>
       </c>
       <c r="AL368" s="368" t="n">
-        <v>3254.321893974604</v>
+        <v>3254.321893974605</v>
       </c>
       <c r="AM368" s="368" t="n">
         <v>3301.672431208349</v>
       </c>
       <c r="AN368" s="368" t="n">
-        <v>3345.010306312381</v>
+        <v>3345.010306312382</v>
       </c>
       <c r="AO368" s="380" t="n">
-        <v>3391.381220487522</v>
+        <v>3391.381220487523</v>
       </c>
       <c r="AP368" s="381" t="n">
         <v>183.6360911050139</v>
@@ -71151,16 +71151,16 @@
         <v>3204.861308971688</v>
       </c>
       <c r="BC368" s="375" t="n">
-        <v>3254.321893974604</v>
+        <v>3254.321893974605</v>
       </c>
       <c r="BD368" s="375" t="n">
         <v>3301.672431208349</v>
       </c>
       <c r="BE368" s="375" t="n">
-        <v>3345.010306312381</v>
+        <v>3345.010306312382</v>
       </c>
       <c r="BF368" s="392" t="n">
-        <v>3391.381220487522</v>
+        <v>3391.381220487523</v>
       </c>
       <c r="BG368" s="386" t="n">
         <v>183.6360911050139</v>
@@ -71186,19 +71186,19 @@
         <v>11005.84284323029</v>
       </c>
       <c r="BT368" s="375" t="n">
-        <v>3971.299184621567</v>
+        <v>3971.299184621568</v>
       </c>
       <c r="BU368" s="375" t="n">
-        <v>4027.73397970867</v>
+        <v>4027.733979708671</v>
       </c>
       <c r="BV368" s="375" t="n">
-        <v>4067.985565486489</v>
+        <v>4067.98556548649</v>
       </c>
       <c r="BW368" s="392" t="n">
         <v>4100.881810478877</v>
       </c>
       <c r="BX368" s="386" t="n">
-        <v>459.6319332106141</v>
+        <v>459.6319332106139</v>
       </c>
       <c r="BY368" s="372" t="n">
         <v>223.4646126126869</v>
@@ -71213,19 +71213,19 @@
         <v>240.4233187227052</v>
       </c>
       <c r="CW368" s="511" t="n">
-        <v>7800.981534258606</v>
+        <v>7800.981534258599</v>
       </c>
       <c r="CX368" s="512" t="n">
-        <v>716.9772906469626</v>
+        <v>716.9772906469625</v>
       </c>
       <c r="CY368" s="512" t="n">
-        <v>726.0615485003207</v>
+        <v>726.0615485003212</v>
       </c>
       <c r="CZ368" s="512" t="n">
         <v>722.9752591741083</v>
       </c>
       <c r="DA368" s="513" t="n">
-        <v>709.500589991355</v>
+        <v>709.5005899913544</v>
       </c>
     </row>
     <row r="369">
@@ -71305,7 +71305,7 @@
         </is>
       </c>
       <c r="AK369" s="506" t="n">
-        <v>2074.032206997822</v>
+        <v>2074.032206997823</v>
       </c>
       <c r="AL369" s="368" t="n">
         <v>2111.869947368715</v>
@@ -71320,10 +71320,10 @@
         <v>2160.882642602675</v>
       </c>
       <c r="AP369" s="381" t="n">
-        <v>149.7239363924464</v>
+        <v>149.7239363924465</v>
       </c>
       <c r="AQ369" s="372" t="n">
-        <v>158.8499803385697</v>
+        <v>158.8499803385698</v>
       </c>
       <c r="AR369" s="372" t="n">
         <v>167.8732314029652</v>
@@ -71340,7 +71340,7 @@
         </is>
       </c>
       <c r="BB369" s="391" t="n">
-        <v>2074.032206997822</v>
+        <v>2074.032206997823</v>
       </c>
       <c r="BC369" s="375" t="n">
         <v>2111.869947368715</v>
@@ -71355,10 +71355,10 @@
         <v>2160.882642602675</v>
       </c>
       <c r="BG369" s="386" t="n">
-        <v>149.7239363924464</v>
+        <v>149.7239363924465</v>
       </c>
       <c r="BH369" s="372" t="n">
-        <v>158.8499803385697</v>
+        <v>158.8499803385698</v>
       </c>
       <c r="BI369" s="372" t="n">
         <v>167.8732314029652</v>
@@ -71375,7 +71375,7 @@
         </is>
       </c>
       <c r="BS369" s="391" t="n">
-        <v>3060.302267409851</v>
+        <v>3060.302267409852</v>
       </c>
       <c r="BT369" s="375" t="n">
         <v>2343.584759410196</v>
@@ -71393,7 +71393,7 @@
         <v>214.637606658035</v>
       </c>
       <c r="BY369" s="372" t="n">
-        <v>175.2143618113035</v>
+        <v>175.2143618113036</v>
       </c>
       <c r="BZ369" s="372" t="n">
         <v>186.507815298339</v>
@@ -71402,22 +71402,22 @@
         <v>197.5546038198526</v>
       </c>
       <c r="CB369" s="387" t="n">
-        <v>205.6042943747987</v>
+        <v>205.6042943747988</v>
       </c>
       <c r="CW369" s="391" t="n">
-        <v>986.2700604120286</v>
+        <v>986.2700604120289</v>
       </c>
       <c r="CX369" s="375" t="n">
-        <v>231.7148120414808</v>
+        <v>231.7148120414809</v>
       </c>
       <c r="CY369" s="375" t="n">
-        <v>252.7880519585568</v>
+        <v>252.788051958557</v>
       </c>
       <c r="CZ369" s="375" t="n">
-        <v>270.8465963543272</v>
+        <v>270.846596354327</v>
       </c>
       <c r="DA369" s="392" t="n">
-        <v>244.2168442339436</v>
+        <v>244.2168442339438</v>
       </c>
     </row>
     <row r="370">
@@ -71506,22 +71506,22 @@
         <v>42128.44967839478</v>
       </c>
       <c r="AN370" s="368" t="n">
-        <v>51798.10656705894</v>
+        <v>51798.10656705895</v>
       </c>
       <c r="AO370" s="380" t="n">
-        <v>65974.12315801576</v>
+        <v>65974.12315801575</v>
       </c>
       <c r="AP370" s="381" t="n">
-        <v>378.4351032632466</v>
+        <v>378.4351032632464</v>
       </c>
       <c r="AQ370" s="372" t="n">
         <v>440.3801403055851</v>
       </c>
       <c r="AR370" s="372" t="n">
-        <v>523.9289202796823</v>
+        <v>523.9289202796824</v>
       </c>
       <c r="AS370" s="372" t="n">
-        <v>637.8576697978308</v>
+        <v>637.8576697978309</v>
       </c>
       <c r="AT370" s="382" t="n">
         <v>791.5301064240449</v>
@@ -71541,22 +71541,22 @@
         <v>42128.44967839478</v>
       </c>
       <c r="BE370" s="375" t="n">
-        <v>51798.10656705894</v>
+        <v>51798.10656705895</v>
       </c>
       <c r="BF370" s="392" t="n">
-        <v>65974.12315801576</v>
+        <v>65974.12315801575</v>
       </c>
       <c r="BG370" s="386" t="n">
-        <v>378.4351032632466</v>
+        <v>378.4351032632464</v>
       </c>
       <c r="BH370" s="372" t="n">
         <v>440.3801403055851</v>
       </c>
       <c r="BI370" s="372" t="n">
-        <v>523.9289202796823</v>
+        <v>523.9289202796824</v>
       </c>
       <c r="BJ370" s="372" t="n">
-        <v>637.8576697978308</v>
+        <v>637.8576697978309</v>
       </c>
       <c r="BK370" s="387" t="n">
         <v>791.5301064240449</v>
@@ -71573,16 +71573,16 @@
         <v>35577.50339943102</v>
       </c>
       <c r="BU370" s="375" t="n">
-        <v>42320.3353980717</v>
+        <v>42320.33539807169</v>
       </c>
       <c r="BV370" s="375" t="n">
         <v>52001.74829620226</v>
       </c>
       <c r="BW370" s="392" t="n">
-        <v>66182.01770698407</v>
+        <v>66182.01770698406</v>
       </c>
       <c r="BX370" s="386" t="n">
-        <v>384.3349083439446</v>
+        <v>384.3349083439444</v>
       </c>
       <c r="BY370" s="372" t="n">
         <v>442.2360020397605</v>
@@ -71591,10 +71591,10 @@
         <v>525.8232162336361</v>
       </c>
       <c r="CA370" s="372" t="n">
-        <v>639.7726191430498</v>
+        <v>639.77261914305</v>
       </c>
       <c r="CB370" s="387" t="n">
-        <v>793.3130728849978</v>
+        <v>793.3130728849977</v>
       </c>
       <c r="CW370" s="391" t="n">
         <v>578.8040722428017</v>
@@ -71603,13 +71603,13 @@
         <v>182.6507669326292</v>
       </c>
       <c r="CY370" s="375" t="n">
-        <v>191.8857196769169</v>
+        <v>191.885719676917</v>
       </c>
       <c r="CZ370" s="375" t="n">
-        <v>203.6417291433182</v>
+        <v>203.6417291433183</v>
       </c>
       <c r="DA370" s="392" t="n">
-        <v>207.8945489683032</v>
+        <v>207.8945489683033</v>
       </c>
     </row>
     <row r="371" ht="15.75" customHeight="1" thickBot="1">
@@ -71707,7 +71707,7 @@
         <v>17639.01218549907</v>
       </c>
       <c r="AQ371" s="411" t="n">
-        <v>18384.23602279761</v>
+        <v>18384.2360227976</v>
       </c>
       <c r="AR371" s="411" t="n">
         <v>18338.57521310579</v>
@@ -71742,7 +71742,7 @@
         <v>17639.01218549907</v>
       </c>
       <c r="BH371" s="417" t="n">
-        <v>18384.23602279761</v>
+        <v>18384.2360227976</v>
       </c>
       <c r="BI371" s="417" t="n">
         <v>18338.57521310579</v>
@@ -71759,10 +71759,10 @@
         </is>
       </c>
       <c r="BS371" s="419" t="n">
-        <v>392870.6611876372</v>
+        <v>392870.6611876373</v>
       </c>
       <c r="BT371" s="420" t="n">
-        <v>418457.6758984353</v>
+        <v>418457.6758984352</v>
       </c>
       <c r="BU371" s="420" t="n">
         <v>316602.9484016791</v>
@@ -71774,10 +71774,10 @@
         <v>270025.4799898149</v>
       </c>
       <c r="BX371" s="416" t="n">
-        <v>17643.94531684612</v>
+        <v>17643.94531684611</v>
       </c>
       <c r="BY371" s="417" t="n">
-        <v>18387.98917409555</v>
+        <v>18387.98917409554</v>
       </c>
       <c r="BZ371" s="417" t="n">
         <v>18343.88673948644</v>
@@ -71789,19 +71789,19 @@
         <v>18302.44144567959</v>
       </c>
       <c r="CW371" s="419" t="n">
-        <v>219.8088549232852</v>
+        <v>219.8088549232775</v>
       </c>
       <c r="CX371" s="420" t="n">
-        <v>202.999155298307</v>
+        <v>202.9991552983001</v>
       </c>
       <c r="CY371" s="420" t="n">
-        <v>212.5341341601032</v>
+        <v>212.5341341600958</v>
       </c>
       <c r="CZ371" s="420" t="n">
-        <v>223.7561562555322</v>
+        <v>223.7561562555242</v>
       </c>
       <c r="DA371" s="421" t="n">
-        <v>236.3659813315641</v>
+        <v>236.3659813315559</v>
       </c>
     </row>
     <row r="372" ht="15.75" customHeight="1" thickBot="1">
@@ -71814,7 +71814,7 @@
         <v>427119.3209384317</v>
       </c>
       <c r="D372" s="425" t="n">
-        <v>457098.1422544294</v>
+        <v>457098.1422544293</v>
       </c>
       <c r="E372" s="425" t="n">
         <v>361598.9702909656</v>
@@ -71849,7 +71849,7 @@
         <v>427119.3209384317</v>
       </c>
       <c r="U372" s="430" t="n">
-        <v>457098.1422544294</v>
+        <v>457098.1422544293</v>
       </c>
       <c r="V372" s="430" t="n">
         <v>361598.9702909656</v>
@@ -71881,31 +71881,31 @@
         </is>
       </c>
       <c r="AK372" s="435" t="n">
-        <v>427570.0681558872</v>
+        <v>427570.0681558873</v>
       </c>
       <c r="AL372" s="408" t="n">
-        <v>457378.9569738114</v>
+        <v>457378.9569738113</v>
       </c>
       <c r="AM372" s="408" t="n">
         <v>361705.1091922024</v>
       </c>
       <c r="AN372" s="408" t="n">
-        <v>314741.6778722474</v>
+        <v>314741.6778722473</v>
       </c>
       <c r="AO372" s="409" t="n">
-        <v>337757.0494690707</v>
+        <v>337757.0494690706</v>
       </c>
       <c r="AP372" s="436" t="n">
-        <v>3181.068064543169</v>
+        <v>3181.068064543168</v>
       </c>
       <c r="AQ372" s="437" t="n">
-        <v>3424.953492606781</v>
+        <v>3424.95349260678</v>
       </c>
       <c r="AR372" s="437" t="n">
         <v>2842.312675205743</v>
       </c>
       <c r="AS372" s="437" t="n">
-        <v>2527.356565481375</v>
+        <v>2527.356565481374</v>
       </c>
       <c r="AT372" s="438" t="n">
         <v>2679.627516824331</v>
@@ -71916,31 +71916,31 @@
         </is>
       </c>
       <c r="BB372" s="439" t="n">
-        <v>427570.0681558872</v>
+        <v>427570.0681558873</v>
       </c>
       <c r="BC372" s="440" t="n">
-        <v>457378.9569738114</v>
+        <v>457378.9569738113</v>
       </c>
       <c r="BD372" s="440" t="n">
         <v>361705.1091922024</v>
       </c>
       <c r="BE372" s="440" t="n">
-        <v>314741.6778722474</v>
+        <v>314741.6778722473</v>
       </c>
       <c r="BF372" s="441" t="n">
-        <v>337757.0494690707</v>
+        <v>337757.0494690706</v>
       </c>
       <c r="BG372" s="442" t="n">
-        <v>3181.068064543169</v>
+        <v>3181.068064543168</v>
       </c>
       <c r="BH372" s="443" t="n">
-        <v>3424.953492606781</v>
+        <v>3424.95349260678</v>
       </c>
       <c r="BI372" s="443" t="n">
         <v>2842.312675205743</v>
       </c>
       <c r="BJ372" s="443" t="n">
-        <v>2527.356565481375</v>
+        <v>2527.356565481374</v>
       </c>
       <c r="BK372" s="444" t="n">
         <v>2679.627516824331</v>
@@ -71954,7 +71954,7 @@
         <v>438131.454832844</v>
       </c>
       <c r="BT372" s="440" t="n">
-        <v>460350.0632418981</v>
+        <v>460350.063241898</v>
       </c>
       <c r="BU372" s="440" t="n">
         <v>365341.986136055</v>
@@ -71969,7 +71969,7 @@
         <v>3093.388983986585</v>
       </c>
       <c r="BY372" s="443" t="n">
-        <v>3426.414946365262</v>
+        <v>3426.41494636526</v>
       </c>
       <c r="BZ372" s="443" t="n">
         <v>2851.98614413195</v>
@@ -71978,22 +71978,22 @@
         <v>2543.515208080338</v>
       </c>
       <c r="CB372" s="444" t="n">
-        <v>2699.955785295573</v>
+        <v>2699.955785295574</v>
       </c>
       <c r="CW372" s="419" t="n">
-        <v>9585.864521836722</v>
+        <v>9585.864521836707</v>
       </c>
       <c r="CX372" s="420" t="n">
-        <v>1334.34202491938</v>
+        <v>1334.342024919373</v>
       </c>
       <c r="CY372" s="420" t="n">
-        <v>1383.269454295898</v>
+        <v>1383.269454295891</v>
       </c>
       <c r="CZ372" s="420" t="n">
-        <v>1421.219740927286</v>
+        <v>1421.219740927278</v>
       </c>
       <c r="DA372" s="421" t="n">
-        <v>1397.977964525166</v>
+        <v>1397.977964525157</v>
       </c>
     </row>
     <row r="375">
